--- a/results_test/MC_Dist=Exp_n=300_LT=0.1_C=0.2_Gamma=0_0_B=1000.xlsx
+++ b/results_test/MC_Dist=Exp_n=300_LT=0.1_C=0.2_Gamma=0_0_B=1000.xlsx
@@ -557,7 +557,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>2.35552552735692</v>
+        <v>2.35552552731637</v>
       </c>
       <c r="C2" t="n">
         <v>0.706</v>
@@ -568,7 +568,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>3.43114986781054</v>
+        <v>3.43114986776023</v>
       </c>
       <c r="C3" t="n">
         <v>0.329</v>
@@ -579,7 +579,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>6.28924038223462</v>
+        <v>6.28924038217941</v>
       </c>
       <c r="C4" t="n">
         <v>0.085</v>
@@ -601,7 +601,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>4.13005682057694</v>
+        <v>4.13005682056884</v>
       </c>
       <c r="C6" t="n">
         <v>0.278</v>
@@ -612,7 +612,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>3.81627981259664</v>
+        <v>3.81627981278237</v>
       </c>
       <c r="C7" t="n">
         <v>0.274</v>
@@ -634,7 +634,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>2.57855801000892</v>
+        <v>2.57855801001162</v>
       </c>
       <c r="C9" t="n">
         <v>0.497</v>
@@ -645,7 +645,7 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>3.44964390286721</v>
+        <v>3.44964390281526</v>
       </c>
       <c r="C10" t="n">
         <v>0.474</v>
@@ -656,7 +656,7 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>2.38971023026548</v>
+        <v>2.38971023026032</v>
       </c>
       <c r="C11" t="n">
         <v>0.716</v>
@@ -667,7 +667,7 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>2.25201283329399</v>
+        <v>2.25201283330806</v>
       </c>
       <c r="C12" t="n">
         <v>0.651</v>
@@ -678,7 +678,7 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>1.99994961009296</v>
+        <v>1.99994961009298</v>
       </c>
       <c r="C13" t="n">
         <v>0.848</v>
@@ -700,7 +700,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>2.00305277436015</v>
+        <v>2.00305277435809</v>
       </c>
       <c r="C15" t="n">
         <v>0.848</v>
@@ -711,7 +711,7 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>3.6660644404707</v>
+        <v>3.6660644406795</v>
       </c>
       <c r="C16" t="n">
         <v>0.382</v>
@@ -722,7 +722,7 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>5.05579053293123</v>
+        <v>5.05579053289578</v>
       </c>
       <c r="C17" t="n">
         <v>0.095</v>
@@ -733,7 +733,7 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>2.84590646302598</v>
+        <v>2.8459064626815</v>
       </c>
       <c r="C18" t="n">
         <v>0.374</v>
@@ -744,7 +744,7 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>1.69405176453265</v>
+        <v>1.69405176460173</v>
       </c>
       <c r="C19" t="n">
         <v>0.993</v>
@@ -755,7 +755,7 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>3.68544165068381</v>
+        <v>3.68544165072917</v>
       </c>
       <c r="C20" t="n">
         <v>0.442</v>
@@ -766,7 +766,7 @@
         <v>20</v>
       </c>
       <c r="B21" t="n">
-        <v>4.18714898646156</v>
+        <v>4.18714898645138</v>
       </c>
       <c r="C21" t="n">
         <v>0.284</v>
@@ -777,7 +777,7 @@
         <v>21</v>
       </c>
       <c r="B22" t="n">
-        <v>2.17609769104611</v>
+        <v>2.17609769098902</v>
       </c>
       <c r="C22" t="n">
         <v>0.549</v>
@@ -788,7 +788,7 @@
         <v>22</v>
       </c>
       <c r="B23" t="n">
-        <v>2.91914936266689</v>
+        <v>2.91914936268459</v>
       </c>
       <c r="C23" t="n">
         <v>0.642</v>
@@ -799,7 +799,7 @@
         <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>2.19630300915521</v>
+        <v>2.19630300918062</v>
       </c>
       <c r="C24" t="n">
         <v>0.578</v>
@@ -810,7 +810,7 @@
         <v>24</v>
       </c>
       <c r="B25" t="n">
-        <v>6.14130001231073</v>
+        <v>6.14130001237849</v>
       </c>
       <c r="C25" t="n">
         <v>0.071</v>
@@ -821,7 +821,7 @@
         <v>25</v>
       </c>
       <c r="B26" t="n">
-        <v>2.0105459797513</v>
+        <v>2.01054597975069</v>
       </c>
       <c r="C26" t="n">
         <v>0.766</v>
@@ -832,7 +832,7 @@
         <v>26</v>
       </c>
       <c r="B27" t="n">
-        <v>2.25433607376829</v>
+        <v>2.25433607376197</v>
       </c>
       <c r="C27" t="n">
         <v>0.742</v>
@@ -843,7 +843,7 @@
         <v>27</v>
       </c>
       <c r="B28" t="n">
-        <v>3.07737002077437</v>
+        <v>3.07737002077187</v>
       </c>
       <c r="C28" t="n">
         <v>0.567</v>
@@ -854,7 +854,7 @@
         <v>28</v>
       </c>
       <c r="B29" t="n">
-        <v>3.73401443666678</v>
+        <v>3.73401443653844</v>
       </c>
       <c r="C29" t="n">
         <v>0.387</v>
@@ -865,7 +865,7 @@
         <v>29</v>
       </c>
       <c r="B30" t="n">
-        <v>6.29626238299317</v>
+        <v>6.2962623829485</v>
       </c>
       <c r="C30" t="n">
         <v>0.052</v>
@@ -876,7 +876,7 @@
         <v>30</v>
       </c>
       <c r="B31" t="n">
-        <v>2.68538308510343</v>
+        <v>2.68538308436197</v>
       </c>
       <c r="C31" t="n">
         <v>0.737</v>
@@ -887,7 +887,7 @@
         <v>31</v>
       </c>
       <c r="B32" t="n">
-        <v>5.76266231604018</v>
+        <v>5.76266231581841</v>
       </c>
       <c r="C32" t="n">
         <v>0.059</v>
@@ -898,7 +898,7 @@
         <v>32</v>
       </c>
       <c r="B33" t="n">
-        <v>2.06032136537129</v>
+        <v>2.06032136545892</v>
       </c>
       <c r="C33" t="n">
         <v>0.743</v>
@@ -909,7 +909,7 @@
         <v>33</v>
       </c>
       <c r="B34" t="n">
-        <v>2.56815731557232</v>
+        <v>2.56815731556952</v>
       </c>
       <c r="C34" t="n">
         <v>0.71</v>
@@ -920,7 +920,7 @@
         <v>34</v>
       </c>
       <c r="B35" t="n">
-        <v>3.4531480082309</v>
+        <v>3.45314800823808</v>
       </c>
       <c r="C35" t="n">
         <v>0.395</v>
@@ -931,7 +931,7 @@
         <v>35</v>
       </c>
       <c r="B36" t="n">
-        <v>5.48682592963393</v>
+        <v>5.48682592966272</v>
       </c>
       <c r="C36" t="n">
         <v>0.113</v>
@@ -942,7 +942,7 @@
         <v>36</v>
       </c>
       <c r="B37" t="n">
-        <v>2.47579690668471</v>
+        <v>2.47579690669993</v>
       </c>
       <c r="C37" t="n">
         <v>0.63</v>
@@ -953,7 +953,7 @@
         <v>37</v>
       </c>
       <c r="B38" t="n">
-        <v>2.84415207819264</v>
+        <v>2.84415210766979</v>
       </c>
       <c r="C38" t="n">
         <v>0.56</v>
@@ -975,7 +975,7 @@
         <v>39</v>
       </c>
       <c r="B40" t="n">
-        <v>5.15245567940212</v>
+        <v>5.15245567945013</v>
       </c>
       <c r="C40" t="n">
         <v>0.187</v>
@@ -986,7 +986,7 @@
         <v>40</v>
       </c>
       <c r="B41" t="n">
-        <v>3.23234749610704</v>
+        <v>3.2323474961168</v>
       </c>
       <c r="C41" t="n">
         <v>0.394</v>
@@ -997,7 +997,7 @@
         <v>41</v>
       </c>
       <c r="B42" t="n">
-        <v>1.3548482452189</v>
+        <v>1.35484824522739</v>
       </c>
       <c r="C42" t="n">
         <v>0.892</v>
@@ -1008,7 +1008,7 @@
         <v>42</v>
       </c>
       <c r="B43" t="n">
-        <v>1.09045929300602</v>
+        <v>1.09045929309465</v>
       </c>
       <c r="C43" t="n">
         <v>0.945</v>
@@ -1019,7 +1019,7 @@
         <v>43</v>
       </c>
       <c r="B44" t="n">
-        <v>2.9902479279714</v>
+        <v>2.99024792797893</v>
       </c>
       <c r="C44" t="n">
         <v>0.461</v>
@@ -1030,7 +1030,7 @@
         <v>44</v>
       </c>
       <c r="B45" t="n">
-        <v>2.96167310286896</v>
+        <v>2.9616731029155</v>
       </c>
       <c r="C45" t="n">
         <v>0.472</v>
@@ -1041,7 +1041,7 @@
         <v>45</v>
       </c>
       <c r="B46" t="n">
-        <v>1.90837301802277</v>
+        <v>1.90837301801556</v>
       </c>
       <c r="C46" t="n">
         <v>0.854</v>
@@ -1052,7 +1052,7 @@
         <v>46</v>
       </c>
       <c r="B47" t="n">
-        <v>4.2257133643591</v>
+        <v>4.22571336438498</v>
       </c>
       <c r="C47" t="n">
         <v>0.239</v>
@@ -1063,7 +1063,7 @@
         <v>47</v>
       </c>
       <c r="B48" t="n">
-        <v>1.58801044645876</v>
+        <v>1.58801044647492</v>
       </c>
       <c r="C48" t="n">
         <v>0.898</v>
@@ -1074,7 +1074,7 @@
         <v>48</v>
       </c>
       <c r="B49" t="n">
-        <v>1.77866431097312</v>
+        <v>1.77866431097783</v>
       </c>
       <c r="C49" t="n">
         <v>0.858</v>
@@ -1085,7 +1085,7 @@
         <v>49</v>
       </c>
       <c r="B50" t="n">
-        <v>1.77089944916222</v>
+        <v>1.77089944916326</v>
       </c>
       <c r="C50" t="n">
         <v>0.745</v>
@@ -1096,7 +1096,7 @@
         <v>50</v>
       </c>
       <c r="B51" t="n">
-        <v>7.37915144532048</v>
+        <v>7.37915144531365</v>
       </c>
       <c r="C51" t="n">
         <v>0.046</v>
@@ -1107,7 +1107,7 @@
         <v>51</v>
       </c>
       <c r="B52" t="n">
-        <v>3.31057321971016</v>
+        <v>3.31057321974298</v>
       </c>
       <c r="C52" t="n">
         <v>0.422</v>
@@ -1118,7 +1118,7 @@
         <v>52</v>
       </c>
       <c r="B53" t="n">
-        <v>3.008230067281</v>
+        <v>3.00823006732554</v>
       </c>
       <c r="C53" t="n">
         <v>0.509</v>
@@ -1129,7 +1129,7 @@
         <v>53</v>
       </c>
       <c r="B54" t="n">
-        <v>6.95105910825319</v>
+        <v>6.95105910811266</v>
       </c>
       <c r="C54" t="n">
         <v>0.043</v>
@@ -1140,7 +1140,7 @@
         <v>54</v>
       </c>
       <c r="B55" t="n">
-        <v>3.24772049492847</v>
+        <v>3.24772049496109</v>
       </c>
       <c r="C55" t="n">
         <v>0.409</v>
@@ -1151,7 +1151,7 @@
         <v>55</v>
       </c>
       <c r="B56" t="n">
-        <v>2.74647866569722</v>
+        <v>2.74647866569793</v>
       </c>
       <c r="C56" t="n">
         <v>0.551</v>
@@ -1162,7 +1162,7 @@
         <v>56</v>
       </c>
       <c r="B57" t="n">
-        <v>5.26576889801696</v>
+        <v>5.26576889845718</v>
       </c>
       <c r="C57" t="n">
         <v>0.155</v>
@@ -1173,7 +1173,7 @@
         <v>57</v>
       </c>
       <c r="B58" t="n">
-        <v>1.7613288445245</v>
+        <v>1.76132884461125</v>
       </c>
       <c r="C58" t="n">
         <v>0.835</v>
@@ -1184,7 +1184,7 @@
         <v>58</v>
       </c>
       <c r="B59" t="n">
-        <v>2.74583329378303</v>
+        <v>2.74583329377835</v>
       </c>
       <c r="C59" t="n">
         <v>0.594</v>
@@ -1195,7 +1195,7 @@
         <v>59</v>
       </c>
       <c r="B60" t="n">
-        <v>2.07938558627194</v>
+        <v>2.07938558625029</v>
       </c>
       <c r="C60" t="n">
         <v>0.748</v>
@@ -1206,7 +1206,7 @@
         <v>60</v>
       </c>
       <c r="B61" t="n">
-        <v>2.32256623811028</v>
+        <v>2.32256623808168</v>
       </c>
       <c r="C61" t="n">
         <v>0.587</v>
@@ -1217,7 +1217,7 @@
         <v>61</v>
       </c>
       <c r="B62" t="n">
-        <v>5.95804284806376</v>
+        <v>5.95804284826989</v>
       </c>
       <c r="C62" t="n">
         <v>0.055</v>
@@ -1228,7 +1228,7 @@
         <v>62</v>
       </c>
       <c r="B63" t="n">
-        <v>6.1828531886559</v>
+        <v>6.18285318863868</v>
       </c>
       <c r="C63" t="n">
         <v>0.074</v>
@@ -1239,7 +1239,7 @@
         <v>63</v>
       </c>
       <c r="B64" t="n">
-        <v>2.93310297686535</v>
+        <v>2.93310297688901</v>
       </c>
       <c r="C64" t="n">
         <v>0.46</v>
@@ -1250,7 +1250,7 @@
         <v>64</v>
       </c>
       <c r="B65" t="n">
-        <v>1.42175629132439</v>
+        <v>1.42175629118423</v>
       </c>
       <c r="C65" t="n">
         <v>0.909</v>
@@ -1261,7 +1261,7 @@
         <v>65</v>
       </c>
       <c r="B66" t="n">
-        <v>1.55777931402117</v>
+        <v>1.5577793140425</v>
       </c>
       <c r="C66" t="n">
         <v>0.841</v>
@@ -1272,7 +1272,7 @@
         <v>66</v>
       </c>
       <c r="B67" t="n">
-        <v>3.51841282878174</v>
+        <v>3.51841282878802</v>
       </c>
       <c r="C67" t="n">
         <v>0.298</v>
@@ -1283,7 +1283,7 @@
         <v>67</v>
       </c>
       <c r="B68" t="n">
-        <v>6.26198686661963</v>
+        <v>6.26198686687208</v>
       </c>
       <c r="C68" t="n">
         <v>0.083</v>
@@ -1294,7 +1294,7 @@
         <v>68</v>
       </c>
       <c r="B69" t="n">
-        <v>6.95946917889939</v>
+        <v>6.95946917891433</v>
       </c>
       <c r="C69" t="n">
         <v>0.035</v>
@@ -1305,7 +1305,7 @@
         <v>69</v>
       </c>
       <c r="B70" t="n">
-        <v>2.10180454437105</v>
+        <v>2.10180454435874</v>
       </c>
       <c r="C70" t="n">
         <v>0.608</v>
@@ -1316,7 +1316,7 @@
         <v>70</v>
       </c>
       <c r="B71" t="n">
-        <v>2.36439522705026</v>
+        <v>2.36439522691408</v>
       </c>
       <c r="C71" t="n">
         <v>0.68</v>
@@ -1338,7 +1338,7 @@
         <v>72</v>
       </c>
       <c r="B73" t="n">
-        <v>1.56485629337192</v>
+        <v>1.5648562933082</v>
       </c>
       <c r="C73" t="n">
         <v>0.875</v>
@@ -1349,7 +1349,7 @@
         <v>73</v>
       </c>
       <c r="B74" t="n">
-        <v>2.30402847369486</v>
+        <v>2.30402847371007</v>
       </c>
       <c r="C74" t="n">
         <v>0.588</v>
@@ -1360,7 +1360,7 @@
         <v>74</v>
       </c>
       <c r="B75" t="n">
-        <v>3.29874684278306</v>
+        <v>3.29874684280708</v>
       </c>
       <c r="C75" t="n">
         <v>0.362</v>
@@ -1371,7 +1371,7 @@
         <v>75</v>
       </c>
       <c r="B76" t="n">
-        <v>5.8081987662359</v>
+        <v>5.80819876626659</v>
       </c>
       <c r="C76" t="n">
         <v>0.099</v>
@@ -1382,7 +1382,7 @@
         <v>76</v>
       </c>
       <c r="B77" t="n">
-        <v>3.28436764771134</v>
+        <v>3.28436764674408</v>
       </c>
       <c r="C77" t="n">
         <v>0.458</v>
@@ -1393,7 +1393,7 @@
         <v>77</v>
       </c>
       <c r="B78" t="n">
-        <v>5.37460496379361</v>
+        <v>5.37460496382693</v>
       </c>
       <c r="C78" t="n">
         <v>0.217</v>
@@ -1404,7 +1404,7 @@
         <v>78</v>
       </c>
       <c r="B79" t="n">
-        <v>5.21866487277598</v>
+        <v>5.21866487277862</v>
       </c>
       <c r="C79" t="n">
         <v>0.151</v>
@@ -1426,7 +1426,7 @@
         <v>80</v>
       </c>
       <c r="B81" t="n">
-        <v>5.48415117704631</v>
+        <v>5.48415117705369</v>
       </c>
       <c r="C81" t="n">
         <v>0.111</v>
@@ -1437,7 +1437,7 @@
         <v>81</v>
       </c>
       <c r="B82" t="n">
-        <v>1.99991663408815</v>
+        <v>1.99991663408812</v>
       </c>
       <c r="C82" t="n">
         <v>0.919</v>
@@ -1448,7 +1448,7 @@
         <v>82</v>
       </c>
       <c r="B83" t="n">
-        <v>7.11039846489772</v>
+        <v>7.1103984649093</v>
       </c>
       <c r="C83" t="n">
         <v>0.069</v>
@@ -1459,7 +1459,7 @@
         <v>83</v>
       </c>
       <c r="B84" t="n">
-        <v>3.24414351886881</v>
+        <v>3.24414351878863</v>
       </c>
       <c r="C84" t="n">
         <v>0.298</v>
@@ -1470,7 +1470,7 @@
         <v>84</v>
       </c>
       <c r="B85" t="n">
-        <v>1.99812661762802</v>
+        <v>1.99812661762813</v>
       </c>
       <c r="C85" t="n">
         <v>0.971</v>
@@ -1481,7 +1481,7 @@
         <v>85</v>
       </c>
       <c r="B86" t="n">
-        <v>5.2037597893296</v>
+        <v>5.20375978933179</v>
       </c>
       <c r="C86" t="n">
         <v>0.125</v>
@@ -1492,7 +1492,7 @@
         <v>86</v>
       </c>
       <c r="B87" t="n">
-        <v>4.51881536093466</v>
+        <v>4.5188153611359</v>
       </c>
       <c r="C87" t="n">
         <v>0.254</v>
@@ -1503,7 +1503,7 @@
         <v>87</v>
       </c>
       <c r="B88" t="n">
-        <v>4.38922620120471</v>
+        <v>4.38922620119426</v>
       </c>
       <c r="C88" t="n">
         <v>0.217</v>
@@ -1514,7 +1514,7 @@
         <v>88</v>
       </c>
       <c r="B89" t="n">
-        <v>1.22617186594711</v>
+        <v>1.22617186659669</v>
       </c>
       <c r="C89" t="n">
         <v>0.902</v>
@@ -1525,7 +1525,7 @@
         <v>89</v>
       </c>
       <c r="B90" t="n">
-        <v>2.68203976190218</v>
+        <v>2.68203976189983</v>
       </c>
       <c r="C90" t="n">
         <v>0.785</v>
@@ -1536,7 +1536,7 @@
         <v>90</v>
       </c>
       <c r="B91" t="n">
-        <v>3.37843321692511</v>
+        <v>3.37843321677418</v>
       </c>
       <c r="C91" t="n">
         <v>0.385</v>
@@ -1547,7 +1547,7 @@
         <v>91</v>
       </c>
       <c r="B92" t="n">
-        <v>1.9994334560941</v>
+        <v>1.99943345609409</v>
       </c>
       <c r="C92" t="n">
         <v>0.936</v>
@@ -1558,7 +1558,7 @@
         <v>92</v>
       </c>
       <c r="B93" t="n">
-        <v>3.32490118780415</v>
+        <v>3.32490118774763</v>
       </c>
       <c r="C93" t="n">
         <v>0.324</v>
@@ -1569,7 +1569,7 @@
         <v>93</v>
       </c>
       <c r="B94" t="n">
-        <v>6.26899184046459</v>
+        <v>6.26899184044466</v>
       </c>
       <c r="C94" t="n">
         <v>0.068</v>
@@ -1580,7 +1580,7 @@
         <v>94</v>
       </c>
       <c r="B95" t="n">
-        <v>1.19615316705501</v>
+        <v>1.19615316711013</v>
       </c>
       <c r="C95" t="n">
         <v>0.887</v>
@@ -1591,7 +1591,7 @@
         <v>95</v>
       </c>
       <c r="B96" t="n">
-        <v>2.43401704074567</v>
+        <v>2.43401704093828</v>
       </c>
       <c r="C96" t="n">
         <v>0.504</v>
@@ -1602,7 +1602,7 @@
         <v>96</v>
       </c>
       <c r="B97" t="n">
-        <v>2.13425601876671</v>
+        <v>2.13425601874235</v>
       </c>
       <c r="C97" t="n">
         <v>0.614</v>
@@ -1613,7 +1613,7 @@
         <v>97</v>
       </c>
       <c r="B98" t="n">
-        <v>3.48291360130944</v>
+        <v>3.48291360147698</v>
       </c>
       <c r="C98" t="n">
         <v>0.357</v>
@@ -1624,7 +1624,7 @@
         <v>98</v>
       </c>
       <c r="B99" t="n">
-        <v>2.92824885468837</v>
+        <v>2.92824885363369</v>
       </c>
       <c r="C99" t="n">
         <v>0.516</v>
@@ -1635,7 +1635,7 @@
         <v>99</v>
       </c>
       <c r="B100" t="n">
-        <v>2.66656517081212</v>
+        <v>2.66656517081691</v>
       </c>
       <c r="C100" t="n">
         <v>0.469</v>
@@ -1646,7 +1646,7 @@
         <v>100</v>
       </c>
       <c r="B101" t="n">
-        <v>5.26425829929376</v>
+        <v>5.26425829933241</v>
       </c>
       <c r="C101" t="n">
         <v>0.132</v>
@@ -1657,7 +1657,7 @@
         <v>101</v>
       </c>
       <c r="B102" t="n">
-        <v>3.16678401104535</v>
+        <v>3.16678401102444</v>
       </c>
       <c r="C102" t="n">
         <v>0.442</v>
@@ -1668,7 +1668,7 @@
         <v>102</v>
       </c>
       <c r="B103" t="n">
-        <v>3.22862650228429</v>
+        <v>3.22862650225946</v>
       </c>
       <c r="C103" t="n">
         <v>0.413</v>
@@ -1679,7 +1679,7 @@
         <v>103</v>
       </c>
       <c r="B104" t="n">
-        <v>1.8311690879394</v>
+        <v>1.83116908790396</v>
       </c>
       <c r="C104" t="n">
         <v>0.656</v>
@@ -1690,7 +1690,7 @@
         <v>104</v>
       </c>
       <c r="B105" t="n">
-        <v>2.49550410412014</v>
+        <v>2.49550410406301</v>
       </c>
       <c r="C105" t="n">
         <v>0.595</v>
@@ -1701,7 +1701,7 @@
         <v>105</v>
       </c>
       <c r="B106" t="n">
-        <v>3.88459478127153</v>
+        <v>3.88459478128922</v>
       </c>
       <c r="C106" t="n">
         <v>0.306</v>
@@ -1712,7 +1712,7 @@
         <v>106</v>
       </c>
       <c r="B107" t="n">
-        <v>3.18159401353283</v>
+        <v>3.18159401353824</v>
       </c>
       <c r="C107" t="n">
         <v>0.431</v>
@@ -1723,7 +1723,7 @@
         <v>107</v>
       </c>
       <c r="B108" t="n">
-        <v>1.99996727269088</v>
+        <v>1.99996727269089</v>
       </c>
       <c r="C108" t="n">
         <v>0.882</v>
@@ -1734,7 +1734,7 @@
         <v>108</v>
       </c>
       <c r="B109" t="n">
-        <v>2.58090700527169</v>
+        <v>2.58090700558817</v>
       </c>
       <c r="C109" t="n">
         <v>0.576</v>
@@ -1745,7 +1745,7 @@
         <v>109</v>
       </c>
       <c r="B110" t="n">
-        <v>1.99888696079274</v>
+        <v>1.99888696079264</v>
       </c>
       <c r="C110" t="n">
         <v>0.972</v>
@@ -1756,7 +1756,7 @@
         <v>110</v>
       </c>
       <c r="B111" t="n">
-        <v>1.99499304085854</v>
+        <v>1.99499304085844</v>
       </c>
       <c r="C111" t="n">
         <v>0.988</v>
@@ -1767,7 +1767,7 @@
         <v>111</v>
       </c>
       <c r="B112" t="n">
-        <v>2.11338479952621</v>
+        <v>2.11338479950871</v>
       </c>
       <c r="C112" t="n">
         <v>0.657</v>
@@ -1789,7 +1789,7 @@
         <v>113</v>
       </c>
       <c r="B114" t="n">
-        <v>2.28220742024471</v>
+        <v>2.28220742031237</v>
       </c>
       <c r="C114" t="n">
         <v>0.675</v>
@@ -1800,7 +1800,7 @@
         <v>114</v>
       </c>
       <c r="B115" t="n">
-        <v>3.02583077199687</v>
+        <v>3.02583077198194</v>
       </c>
       <c r="C115" t="n">
         <v>0.485</v>
@@ -1811,7 +1811,7 @@
         <v>115</v>
       </c>
       <c r="B116" t="n">
-        <v>2.15102517380978</v>
+        <v>2.15102517381293</v>
       </c>
       <c r="C116" t="n">
         <v>0.69</v>
@@ -1822,7 +1822,7 @@
         <v>116</v>
       </c>
       <c r="B117" t="n">
-        <v>4.06096431172832</v>
+        <v>4.06096431197897</v>
       </c>
       <c r="C117" t="n">
         <v>0.279</v>
@@ -1833,7 +1833,7 @@
         <v>117</v>
       </c>
       <c r="B118" t="n">
-        <v>2.53732011071549</v>
+        <v>2.53732011067168</v>
       </c>
       <c r="C118" t="n">
         <v>0.622</v>
@@ -1844,7 +1844,7 @@
         <v>118</v>
       </c>
       <c r="B119" t="n">
-        <v>1.80484764760343</v>
+        <v>1.80484764760371</v>
       </c>
       <c r="C119" t="n">
         <v>0.789</v>
@@ -1855,7 +1855,7 @@
         <v>119</v>
       </c>
       <c r="B120" t="n">
-        <v>6.09991878455209</v>
+        <v>6.09991878511574</v>
       </c>
       <c r="C120" t="n">
         <v>0.092</v>
@@ -1866,7 +1866,7 @@
         <v>120</v>
       </c>
       <c r="B121" t="n">
-        <v>4.9092230365965</v>
+        <v>4.90922303650472</v>
       </c>
       <c r="C121" t="n">
         <v>0.116</v>
@@ -1877,7 +1877,7 @@
         <v>121</v>
       </c>
       <c r="B122" t="n">
-        <v>4.38317124146888</v>
+        <v>4.38317124151103</v>
       </c>
       <c r="C122" t="n">
         <v>0.3</v>
@@ -1888,7 +1888,7 @@
         <v>122</v>
       </c>
       <c r="B123" t="n">
-        <v>1.94860434449929</v>
+        <v>1.94860434450768</v>
       </c>
       <c r="C123" t="n">
         <v>0.683</v>
@@ -1899,7 +1899,7 @@
         <v>123</v>
       </c>
       <c r="B124" t="n">
-        <v>1.23391625135858</v>
+        <v>1.23391625133481</v>
       </c>
       <c r="C124" t="n">
         <v>0.805</v>
@@ -1910,7 +1910,7 @@
         <v>124</v>
       </c>
       <c r="B125" t="n">
-        <v>3.71862268876724</v>
+        <v>3.71862268875316</v>
       </c>
       <c r="C125" t="n">
         <v>0.401</v>
@@ -1921,7 +1921,7 @@
         <v>125</v>
       </c>
       <c r="B126" t="n">
-        <v>4.98694193552392</v>
+        <v>4.98694193553277</v>
       </c>
       <c r="C126" t="n">
         <v>0.139</v>
@@ -1932,7 +1932,7 @@
         <v>126</v>
       </c>
       <c r="B127" t="n">
-        <v>1.6477364354749</v>
+        <v>1.64773643546136</v>
       </c>
       <c r="C127" t="n">
         <v>0.878</v>
@@ -1943,7 +1943,7 @@
         <v>127</v>
       </c>
       <c r="B128" t="n">
-        <v>5.33361805770796</v>
+        <v>5.33361805763479</v>
       </c>
       <c r="C128" t="n">
         <v>0.104</v>
@@ -1954,7 +1954,7 @@
         <v>128</v>
       </c>
       <c r="B129" t="n">
-        <v>1.9017247505556</v>
+        <v>1.90172475023459</v>
       </c>
       <c r="C129" t="n">
         <v>0.824</v>
@@ -1965,7 +1965,7 @@
         <v>129</v>
       </c>
       <c r="B130" t="n">
-        <v>1.69670864190563</v>
+        <v>1.6967086419204</v>
       </c>
       <c r="C130" t="n">
         <v>0.819</v>
@@ -1976,7 +1976,7 @@
         <v>130</v>
       </c>
       <c r="B131" t="n">
-        <v>2.75151876217941</v>
+        <v>2.75151876237549</v>
       </c>
       <c r="C131" t="n">
         <v>0.599</v>
@@ -1987,7 +1987,7 @@
         <v>131</v>
       </c>
       <c r="B132" t="n">
-        <v>1.9990392826502</v>
+        <v>1.99903928265019</v>
       </c>
       <c r="C132" t="n">
         <v>0.963</v>
@@ -1998,7 +1998,7 @@
         <v>132</v>
       </c>
       <c r="B133" t="n">
-        <v>1.99708856656712</v>
+        <v>1.99708856656717</v>
       </c>
       <c r="C133" t="n">
         <v>0.97</v>
@@ -2009,7 +2009,7 @@
         <v>133</v>
       </c>
       <c r="B134" t="n">
-        <v>4.42893059814435</v>
+        <v>4.42893059822064</v>
       </c>
       <c r="C134" t="n">
         <v>0.25</v>
@@ -2020,7 +2020,7 @@
         <v>134</v>
       </c>
       <c r="B135" t="n">
-        <v>2.73013364104835</v>
+        <v>2.7301336410693</v>
       </c>
       <c r="C135" t="n">
         <v>0.552</v>
@@ -2031,7 +2031,7 @@
         <v>135</v>
       </c>
       <c r="B136" t="n">
-        <v>4.98300966597259</v>
+        <v>4.98300966569219</v>
       </c>
       <c r="C136" t="n">
         <v>0.175</v>
@@ -2042,7 +2042,7 @@
         <v>136</v>
       </c>
       <c r="B137" t="n">
-        <v>5.75369778654731</v>
+        <v>5.75369778636018</v>
       </c>
       <c r="C137" t="n">
         <v>0.123</v>
@@ -2053,7 +2053,7 @@
         <v>137</v>
       </c>
       <c r="B138" t="n">
-        <v>3.41597552174465</v>
+        <v>3.41597552165436</v>
       </c>
       <c r="C138" t="n">
         <v>0.401</v>
@@ -2064,7 +2064,7 @@
         <v>138</v>
       </c>
       <c r="B139" t="n">
-        <v>2.89188490691417</v>
+        <v>2.89188490691363</v>
       </c>
       <c r="C139" t="n">
         <v>0.552</v>
@@ -2075,7 +2075,7 @@
         <v>139</v>
       </c>
       <c r="B140" t="n">
-        <v>3.65728540237148</v>
+        <v>3.65728540236232</v>
       </c>
       <c r="C140" t="n">
         <v>0.363</v>
@@ -2086,7 +2086,7 @@
         <v>140</v>
       </c>
       <c r="B141" t="n">
-        <v>2.89768958475145</v>
+        <v>2.89768958472787</v>
       </c>
       <c r="C141" t="n">
         <v>0.579</v>
@@ -2097,7 +2097,7 @@
         <v>141</v>
       </c>
       <c r="B142" t="n">
-        <v>2.51664430495847</v>
+        <v>2.51664430496064</v>
       </c>
       <c r="C142" t="n">
         <v>0.6</v>
@@ -2108,7 +2108,7 @@
         <v>142</v>
       </c>
       <c r="B143" t="n">
-        <v>1.82510289390585</v>
+        <v>1.82510289391699</v>
       </c>
       <c r="C143" t="n">
         <v>0.623</v>
@@ -2119,7 +2119,7 @@
         <v>143</v>
       </c>
       <c r="B144" t="n">
-        <v>2.41908489732678</v>
+        <v>2.41908489731082</v>
       </c>
       <c r="C144" t="n">
         <v>0.483</v>
@@ -2130,7 +2130,7 @@
         <v>144</v>
       </c>
       <c r="B145" t="n">
-        <v>8.04487630062762</v>
+        <v>8.04487630093092</v>
       </c>
       <c r="C145" t="n">
         <v>0.067</v>
@@ -2141,7 +2141,7 @@
         <v>145</v>
       </c>
       <c r="B146" t="n">
-        <v>2.58533477385692</v>
+        <v>2.58533477385185</v>
       </c>
       <c r="C146" t="n">
         <v>0.641</v>
@@ -2152,7 +2152,7 @@
         <v>146</v>
       </c>
       <c r="B147" t="n">
-        <v>1.49156018050124</v>
+        <v>1.49156018052229</v>
       </c>
       <c r="C147" t="n">
         <v>0.797</v>
@@ -2163,7 +2163,7 @@
         <v>147</v>
       </c>
       <c r="B148" t="n">
-        <v>6.14061342469063</v>
+        <v>6.14061342460371</v>
       </c>
       <c r="C148" t="n">
         <v>0.047</v>
@@ -2174,7 +2174,7 @@
         <v>148</v>
       </c>
       <c r="B149" t="n">
-        <v>2.39010260657137</v>
+        <v>2.39010260655543</v>
       </c>
       <c r="C149" t="n">
         <v>0.619</v>
@@ -2185,7 +2185,7 @@
         <v>149</v>
       </c>
       <c r="B150" t="n">
-        <v>4.23091326035163</v>
+        <v>4.23091326033689</v>
       </c>
       <c r="C150" t="n">
         <v>0.246</v>
@@ -2196,7 +2196,7 @@
         <v>150</v>
       </c>
       <c r="B151" t="n">
-        <v>1.53795407634467</v>
+        <v>1.53795407627897</v>
       </c>
       <c r="C151" t="n">
         <v>0.79</v>
@@ -2207,7 +2207,7 @@
         <v>151</v>
       </c>
       <c r="B152" t="n">
-        <v>1.22211522725216</v>
+        <v>1.22211522723412</v>
       </c>
       <c r="C152" t="n">
         <v>0.872</v>
@@ -2218,7 +2218,7 @@
         <v>152</v>
       </c>
       <c r="B153" t="n">
-        <v>3.49678403499742</v>
+        <v>3.49678403504006</v>
       </c>
       <c r="C153" t="n">
         <v>0.38</v>
@@ -2240,7 +2240,7 @@
         <v>154</v>
       </c>
       <c r="B155" t="n">
-        <v>2.95048623406602</v>
+        <v>2.95048623411378</v>
       </c>
       <c r="C155" t="n">
         <v>0.536</v>
@@ -2251,7 +2251,7 @@
         <v>155</v>
       </c>
       <c r="B156" t="n">
-        <v>2.9615358811196</v>
+        <v>2.96153588112552</v>
       </c>
       <c r="C156" t="n">
         <v>0.449</v>
@@ -2262,7 +2262,7 @@
         <v>156</v>
       </c>
       <c r="B157" t="n">
-        <v>2.44009701623538</v>
+        <v>2.44009701624536</v>
       </c>
       <c r="C157" t="n">
         <v>0.534</v>
@@ -2284,7 +2284,7 @@
         <v>158</v>
       </c>
       <c r="B159" t="n">
-        <v>1.67704823630128</v>
+        <v>1.67704823631073</v>
       </c>
       <c r="C159" t="n">
         <v>0.786</v>
@@ -2295,7 +2295,7 @@
         <v>159</v>
       </c>
       <c r="B160" t="n">
-        <v>5.9348685813923</v>
+        <v>5.93486858131905</v>
       </c>
       <c r="C160" t="n">
         <v>0.082</v>
@@ -2306,7 +2306,7 @@
         <v>160</v>
       </c>
       <c r="B161" t="n">
-        <v>1.48790238941581</v>
+        <v>1.48790238944633</v>
       </c>
       <c r="C161" t="n">
         <v>0.905</v>
@@ -2317,7 +2317,7 @@
         <v>161</v>
       </c>
       <c r="B162" t="n">
-        <v>2.63004906778887</v>
+        <v>2.63004906778015</v>
       </c>
       <c r="C162" t="n">
         <v>0.449</v>
@@ -2328,7 +2328,7 @@
         <v>162</v>
       </c>
       <c r="B163" t="n">
-        <v>2.46716600989648</v>
+        <v>2.4671660098985</v>
       </c>
       <c r="C163" t="n">
         <v>0.664</v>
@@ -2339,7 +2339,7 @@
         <v>163</v>
       </c>
       <c r="B164" t="n">
-        <v>2.71853179155141</v>
+        <v>2.71853179155518</v>
       </c>
       <c r="C164" t="n">
         <v>0.617</v>
@@ -2350,7 +2350,7 @@
         <v>164</v>
       </c>
       <c r="B165" t="n">
-        <v>3.95244719354231</v>
+        <v>3.95244719354475</v>
       </c>
       <c r="C165" t="n">
         <v>0.233</v>
@@ -2361,7 +2361,7 @@
         <v>165</v>
       </c>
       <c r="B166" t="n">
-        <v>2.09322678377556</v>
+        <v>2.09322678370637</v>
       </c>
       <c r="C166" t="n">
         <v>0.709</v>
@@ -2372,7 +2372,7 @@
         <v>166</v>
       </c>
       <c r="B167" t="n">
-        <v>5.62020560129184</v>
+        <v>5.62020560144119</v>
       </c>
       <c r="C167" t="n">
         <v>0.114</v>
@@ -2394,7 +2394,7 @@
         <v>168</v>
       </c>
       <c r="B169" t="n">
-        <v>3.42414296114072</v>
+        <v>3.42414296113117</v>
       </c>
       <c r="C169" t="n">
         <v>0.677</v>
@@ -2405,7 +2405,7 @@
         <v>169</v>
       </c>
       <c r="B170" t="n">
-        <v>3.64149353710847</v>
+        <v>3.64149353708863</v>
       </c>
       <c r="C170" t="n">
         <v>0.365</v>
@@ -2416,7 +2416,7 @@
         <v>170</v>
       </c>
       <c r="B171" t="n">
-        <v>4.08690256776319</v>
+        <v>4.08690256776275</v>
       </c>
       <c r="C171" t="n">
         <v>0.193</v>
@@ -2427,7 +2427,7 @@
         <v>171</v>
       </c>
       <c r="B172" t="n">
-        <v>5.88513288360562</v>
+        <v>5.8851328830539</v>
       </c>
       <c r="C172" t="n">
         <v>0.108</v>
@@ -2438,7 +2438,7 @@
         <v>172</v>
       </c>
       <c r="B173" t="n">
-        <v>4.7002260890152</v>
+        <v>4.70022608909433</v>
       </c>
       <c r="C173" t="n">
         <v>0.326</v>
@@ -2449,7 +2449,7 @@
         <v>173</v>
       </c>
       <c r="B174" t="n">
-        <v>1.99963552241398</v>
+        <v>1.99963552241524</v>
       </c>
       <c r="C174" t="n">
         <v>0.927</v>
@@ -2460,7 +2460,7 @@
         <v>174</v>
       </c>
       <c r="B175" t="n">
-        <v>1.53497909950084</v>
+        <v>1.53497909962393</v>
       </c>
       <c r="C175" t="n">
         <v>0.835</v>
@@ -2482,7 +2482,7 @@
         <v>176</v>
       </c>
       <c r="B177" t="n">
-        <v>4.24128520617968</v>
+        <v>4.24128520616206</v>
       </c>
       <c r="C177" t="n">
         <v>0.254</v>
@@ -2504,7 +2504,7 @@
         <v>178</v>
       </c>
       <c r="B179" t="n">
-        <v>1.6040679174449</v>
+        <v>1.60406791732437</v>
       </c>
       <c r="C179" t="n">
         <v>0.948</v>
@@ -2526,7 +2526,7 @@
         <v>180</v>
       </c>
       <c r="B181" t="n">
-        <v>1.9535407826873</v>
+        <v>1.95354078268325</v>
       </c>
       <c r="C181" t="n">
         <v>0.818</v>
@@ -2537,7 +2537,7 @@
         <v>181</v>
       </c>
       <c r="B182" t="n">
-        <v>2.5530320709217</v>
+        <v>2.55303207090076</v>
       </c>
       <c r="C182" t="n">
         <v>0.622</v>
@@ -2548,7 +2548,7 @@
         <v>182</v>
       </c>
       <c r="B183" t="n">
-        <v>3.73244348683429</v>
+        <v>3.73244348682</v>
       </c>
       <c r="C183" t="n">
         <v>0.278</v>
@@ -2559,7 +2559,7 @@
         <v>183</v>
       </c>
       <c r="B184" t="n">
-        <v>4.63106799114976</v>
+        <v>4.63106799110904</v>
       </c>
       <c r="C184" t="n">
         <v>0.167</v>
@@ -2570,7 +2570,7 @@
         <v>184</v>
       </c>
       <c r="B185" t="n">
-        <v>3.44495756955744</v>
+        <v>3.44495756959347</v>
       </c>
       <c r="C185" t="n">
         <v>0.327</v>
@@ -2581,7 +2581,7 @@
         <v>185</v>
       </c>
       <c r="B186" t="n">
-        <v>3.9300561974211</v>
+        <v>3.93005619751611</v>
       </c>
       <c r="C186" t="n">
         <v>0.251</v>
@@ -2592,7 +2592,7 @@
         <v>186</v>
       </c>
       <c r="B187" t="n">
-        <v>2.65615282171456</v>
+        <v>2.65615282162889</v>
       </c>
       <c r="C187" t="n">
         <v>0.572</v>
@@ -2603,7 +2603,7 @@
         <v>187</v>
       </c>
       <c r="B188" t="n">
-        <v>1.81817980709704</v>
+        <v>1.81817982809767</v>
       </c>
       <c r="C188" t="n">
         <v>0.984</v>
@@ -2614,7 +2614,7 @@
         <v>188</v>
       </c>
       <c r="B189" t="n">
-        <v>2.54142305123865</v>
+        <v>2.54142305116688</v>
       </c>
       <c r="C189" t="n">
         <v>0.521</v>
@@ -2625,7 +2625,7 @@
         <v>189</v>
       </c>
       <c r="B190" t="n">
-        <v>2.70226658154645</v>
+        <v>2.70226658157825</v>
       </c>
       <c r="C190" t="n">
         <v>0.573</v>
@@ -2636,7 +2636,7 @@
         <v>190</v>
       </c>
       <c r="B191" t="n">
-        <v>1.14661311628372</v>
+        <v>1.14661311171191</v>
       </c>
       <c r="C191" t="n">
         <v>0.96</v>
@@ -2647,7 +2647,7 @@
         <v>191</v>
       </c>
       <c r="B192" t="n">
-        <v>1.99594574709006</v>
+        <v>1.99594574709041</v>
       </c>
       <c r="C192" t="n">
         <v>0.965</v>
@@ -2658,7 +2658,7 @@
         <v>192</v>
       </c>
       <c r="B193" t="n">
-        <v>1.0499835229322</v>
+        <v>1.04998352295855</v>
       </c>
       <c r="C193" t="n">
         <v>0.984</v>
@@ -2669,7 +2669,7 @@
         <v>193</v>
       </c>
       <c r="B194" t="n">
-        <v>5.28606856748702</v>
+        <v>5.28606856753219</v>
       </c>
       <c r="C194" t="n">
         <v>0.11</v>
@@ -2680,7 +2680,7 @@
         <v>194</v>
       </c>
       <c r="B195" t="n">
-        <v>2.74007509633071</v>
+        <v>2.74007509635323</v>
       </c>
       <c r="C195" t="n">
         <v>0.489</v>
@@ -2691,7 +2691,7 @@
         <v>195</v>
       </c>
       <c r="B196" t="n">
-        <v>5.24799713042125</v>
+        <v>5.24799713043477</v>
       </c>
       <c r="C196" t="n">
         <v>0.121</v>
@@ -2702,7 +2702,7 @@
         <v>196</v>
       </c>
       <c r="B197" t="n">
-        <v>4.59614836704689</v>
+        <v>4.59614836714</v>
       </c>
       <c r="C197" t="n">
         <v>0.162</v>
@@ -2713,7 +2713,7 @@
         <v>197</v>
       </c>
       <c r="B198" t="n">
-        <v>1.99989590033073</v>
+        <v>1.99989590033071</v>
       </c>
       <c r="C198" t="n">
         <v>0.906</v>
@@ -2724,7 +2724,7 @@
         <v>198</v>
       </c>
       <c r="B199" t="n">
-        <v>2.6830120916357</v>
+        <v>2.68301209161039</v>
       </c>
       <c r="C199" t="n">
         <v>0.563</v>
@@ -2735,7 +2735,7 @@
         <v>199</v>
       </c>
       <c r="B200" t="n">
-        <v>2.68989904413744</v>
+        <v>2.6898990439587</v>
       </c>
       <c r="C200" t="n">
         <v>0.545</v>
@@ -2746,7 +2746,7 @@
         <v>200</v>
       </c>
       <c r="B201" t="n">
-        <v>1.78373371376967</v>
+        <v>1.78373371376207</v>
       </c>
       <c r="C201" t="n">
         <v>0.755</v>
@@ -2757,7 +2757,7 @@
         <v>201</v>
       </c>
       <c r="B202" t="n">
-        <v>2.4958625528456</v>
+        <v>2.49586255269838</v>
       </c>
       <c r="C202" t="n">
         <v>0.619</v>
@@ -2768,7 +2768,7 @@
         <v>202</v>
       </c>
       <c r="B203" t="n">
-        <v>1.78833934850264</v>
+        <v>1.7883393485243</v>
       </c>
       <c r="C203" t="n">
         <v>0.816</v>
@@ -2779,7 +2779,7 @@
         <v>203</v>
       </c>
       <c r="B204" t="n">
-        <v>3.7360208732355</v>
+        <v>3.73602087322963</v>
       </c>
       <c r="C204" t="n">
         <v>0.334</v>
@@ -2790,7 +2790,7 @@
         <v>204</v>
       </c>
       <c r="B205" t="n">
-        <v>2.2519092906553</v>
+        <v>2.25190929065475</v>
       </c>
       <c r="C205" t="n">
         <v>0.632</v>
@@ -2801,7 +2801,7 @@
         <v>205</v>
       </c>
       <c r="B206" t="n">
-        <v>2.8215939903143</v>
+        <v>2.82159399021577</v>
       </c>
       <c r="C206" t="n">
         <v>0.678</v>
@@ -2812,7 +2812,7 @@
         <v>206</v>
       </c>
       <c r="B207" t="n">
-        <v>2.95041639061621</v>
+        <v>2.95041639150825</v>
       </c>
       <c r="C207" t="n">
         <v>0.574</v>
@@ -2823,7 +2823,7 @@
         <v>207</v>
       </c>
       <c r="B208" t="n">
-        <v>1.99997344972943</v>
+        <v>1.99997344972944</v>
       </c>
       <c r="C208" t="n">
         <v>0.842</v>
@@ -2834,7 +2834,7 @@
         <v>208</v>
       </c>
       <c r="B209" t="n">
-        <v>4.83190991315614</v>
+        <v>4.83190991298746</v>
       </c>
       <c r="C209" t="n">
         <v>0.151</v>
@@ -2845,7 +2845,7 @@
         <v>209</v>
       </c>
       <c r="B210" t="n">
-        <v>3.07008714717039</v>
+        <v>3.07008714718323</v>
       </c>
       <c r="C210" t="n">
         <v>0.506</v>
@@ -2856,7 +2856,7 @@
         <v>210</v>
       </c>
       <c r="B211" t="n">
-        <v>2.0002240571935</v>
+        <v>2.00022405712527</v>
       </c>
       <c r="C211" t="n">
         <v>0.678</v>
@@ -2867,7 +2867,7 @@
         <v>211</v>
       </c>
       <c r="B212" t="n">
-        <v>1.91795328221276</v>
+        <v>1.91795328223278</v>
       </c>
       <c r="C212" t="n">
         <v>0.776</v>
@@ -2878,7 +2878,7 @@
         <v>212</v>
       </c>
       <c r="B213" t="n">
-        <v>1.29831287645205</v>
+        <v>1.29831287651741</v>
       </c>
       <c r="C213" t="n">
         <v>0.944</v>
@@ -2889,7 +2889,7 @@
         <v>213</v>
       </c>
       <c r="B214" t="n">
-        <v>2.91262073624231</v>
+        <v>2.91262073623444</v>
       </c>
       <c r="C214" t="n">
         <v>0.438</v>
@@ -2900,7 +2900,7 @@
         <v>214</v>
       </c>
       <c r="B215" t="n">
-        <v>3.19016129264189</v>
+        <v>3.19016129255698</v>
       </c>
       <c r="C215" t="n">
         <v>0.547</v>
@@ -2911,7 +2911,7 @@
         <v>215</v>
       </c>
       <c r="B216" t="n">
-        <v>0.999978975850555</v>
+        <v>0.999978975850556</v>
       </c>
       <c r="C216" t="n">
         <v>0.99</v>
@@ -2922,7 +2922,7 @@
         <v>216</v>
       </c>
       <c r="B217" t="n">
-        <v>2.23302581905569</v>
+        <v>2.23302581903953</v>
       </c>
       <c r="C217" t="n">
         <v>0.724</v>
@@ -2933,7 +2933,7 @@
         <v>217</v>
       </c>
       <c r="B218" t="n">
-        <v>2.57278119677166</v>
+        <v>2.57278119677094</v>
       </c>
       <c r="C218" t="n">
         <v>0.719</v>
@@ -2944,7 +2944,7 @@
         <v>218</v>
       </c>
       <c r="B219" t="n">
-        <v>1.55394678898252</v>
+        <v>1.55394678898235</v>
       </c>
       <c r="C219" t="n">
         <v>0.866</v>
@@ -2955,7 +2955,7 @@
         <v>219</v>
       </c>
       <c r="B220" t="n">
-        <v>3.87573741660056</v>
+        <v>3.87573741826144</v>
       </c>
       <c r="C220" t="n">
         <v>0.368</v>
@@ -2966,7 +2966,7 @@
         <v>220</v>
       </c>
       <c r="B221" t="n">
-        <v>2.93659281290398</v>
+        <v>2.93659281280578</v>
       </c>
       <c r="C221" t="n">
         <v>0.437</v>
@@ -2977,7 +2977,7 @@
         <v>221</v>
       </c>
       <c r="B222" t="n">
-        <v>4.57943498730497</v>
+        <v>4.57943498743921</v>
       </c>
       <c r="C222" t="n">
         <v>0.191</v>
@@ -2988,7 +2988,7 @@
         <v>222</v>
       </c>
       <c r="B223" t="n">
-        <v>6.36161379072171</v>
+        <v>6.36161379072823</v>
       </c>
       <c r="C223" t="n">
         <v>0.065</v>
@@ -2999,7 +2999,7 @@
         <v>223</v>
       </c>
       <c r="B224" t="n">
-        <v>2.28952895868336</v>
+        <v>2.28952895865493</v>
       </c>
       <c r="C224" t="n">
         <v>0.709</v>
@@ -3010,7 +3010,7 @@
         <v>224</v>
       </c>
       <c r="B225" t="n">
-        <v>1.65720145006038</v>
+        <v>1.65720145003599</v>
       </c>
       <c r="C225" t="n">
         <v>0.815</v>
@@ -3021,7 +3021,7 @@
         <v>225</v>
       </c>
       <c r="B226" t="n">
-        <v>2.81940050812263</v>
+        <v>2.81940051627637</v>
       </c>
       <c r="C226" t="n">
         <v>0.498</v>
@@ -3032,7 +3032,7 @@
         <v>226</v>
       </c>
       <c r="B227" t="n">
-        <v>2.84660971749618</v>
+        <v>2.84660971767848</v>
       </c>
       <c r="C227" t="n">
         <v>0.388</v>
@@ -3043,7 +3043,7 @@
         <v>227</v>
       </c>
       <c r="B228" t="n">
-        <v>5.975144156217</v>
+        <v>5.97514415629023</v>
       </c>
       <c r="C228" t="n">
         <v>0.084</v>
@@ -3054,7 +3054,7 @@
         <v>228</v>
       </c>
       <c r="B229" t="n">
-        <v>3.14948783795326</v>
+        <v>3.14948783850745</v>
       </c>
       <c r="C229" t="n">
         <v>0.486</v>
@@ -3065,7 +3065,7 @@
         <v>229</v>
       </c>
       <c r="B230" t="n">
-        <v>0.999961834002155</v>
+        <v>0.999961834002156</v>
       </c>
       <c r="C230" t="n">
         <v>0.996</v>
@@ -3076,7 +3076,7 @@
         <v>230</v>
       </c>
       <c r="B231" t="n">
-        <v>3.37719278196416</v>
+        <v>3.37719278190539</v>
       </c>
       <c r="C231" t="n">
         <v>0.373</v>
@@ -3087,7 +3087,7 @@
         <v>231</v>
       </c>
       <c r="B232" t="n">
-        <v>1.95203651564679</v>
+        <v>1.95203651596073</v>
       </c>
       <c r="C232" t="n">
         <v>0.773</v>
@@ -3098,7 +3098,7 @@
         <v>232</v>
       </c>
       <c r="B233" t="n">
-        <v>3.37100414059061</v>
+        <v>3.3710041407234</v>
       </c>
       <c r="C233" t="n">
         <v>0.446</v>
@@ -3109,7 +3109,7 @@
         <v>233</v>
       </c>
       <c r="B234" t="n">
-        <v>2.32725107081657</v>
+        <v>2.32725107077933</v>
       </c>
       <c r="C234" t="n">
         <v>0.718</v>
@@ -3120,7 +3120,7 @@
         <v>234</v>
       </c>
       <c r="B235" t="n">
-        <v>3.99793846468567</v>
+        <v>3.99793846459102</v>
       </c>
       <c r="C235" t="n">
         <v>0.205</v>
@@ -3131,7 +3131,7 @@
         <v>235</v>
       </c>
       <c r="B236" t="n">
-        <v>1.46182930462626</v>
+        <v>1.46182930465675</v>
       </c>
       <c r="C236" t="n">
         <v>0.923</v>
@@ -3142,7 +3142,7 @@
         <v>236</v>
       </c>
       <c r="B237" t="n">
-        <v>1.6410600480714</v>
+        <v>1.64106004801826</v>
       </c>
       <c r="C237" t="n">
         <v>0.855</v>
@@ -3153,7 +3153,7 @@
         <v>237</v>
       </c>
       <c r="B238" t="n">
-        <v>2.29607012429546</v>
+        <v>2.29607012425649</v>
       </c>
       <c r="C238" t="n">
         <v>0.702</v>
@@ -3164,7 +3164,7 @@
         <v>238</v>
       </c>
       <c r="B239" t="n">
-        <v>1.96417342362722</v>
+        <v>1.9641734235064</v>
       </c>
       <c r="C239" t="n">
         <v>0.723</v>
@@ -3175,7 +3175,7 @@
         <v>239</v>
       </c>
       <c r="B240" t="n">
-        <v>5.39433842704068</v>
+        <v>5.39433842703148</v>
       </c>
       <c r="C240" t="n">
         <v>0.067</v>
@@ -3186,7 +3186,7 @@
         <v>240</v>
       </c>
       <c r="B241" t="n">
-        <v>2.37051136209484</v>
+        <v>2.37051136212287</v>
       </c>
       <c r="C241" t="n">
         <v>0.8</v>
@@ -3197,7 +3197,7 @@
         <v>241</v>
       </c>
       <c r="B242" t="n">
-        <v>3.77141157869009</v>
+        <v>3.77141157868947</v>
       </c>
       <c r="C242" t="n">
         <v>0.246</v>
@@ -3219,7 +3219,7 @@
         <v>243</v>
       </c>
       <c r="B244" t="n">
-        <v>1.95022656138279</v>
+        <v>1.95022656211932</v>
       </c>
       <c r="C244" t="n">
         <v>0.797</v>
@@ -3230,7 +3230,7 @@
         <v>244</v>
       </c>
       <c r="B245" t="n">
-        <v>2.89626027768</v>
+        <v>2.89626027767864</v>
       </c>
       <c r="C245" t="n">
         <v>0.594</v>
@@ -3241,7 +3241,7 @@
         <v>245</v>
       </c>
       <c r="B246" t="n">
-        <v>2.86940797256276</v>
+        <v>2.86940797256231</v>
       </c>
       <c r="C246" t="n">
         <v>0.463</v>
@@ -3252,7 +3252,7 @@
         <v>246</v>
       </c>
       <c r="B247" t="n">
-        <v>2.82175150563351</v>
+        <v>2.82175150568697</v>
       </c>
       <c r="C247" t="n">
         <v>0.44</v>
@@ -3263,7 +3263,7 @@
         <v>247</v>
       </c>
       <c r="B248" t="n">
-        <v>3.43601619712863</v>
+        <v>3.43601619712111</v>
       </c>
       <c r="C248" t="n">
         <v>0.283</v>
@@ -3274,7 +3274,7 @@
         <v>248</v>
       </c>
       <c r="B249" t="n">
-        <v>4.89227002172851</v>
+        <v>4.89227002175117</v>
       </c>
       <c r="C249" t="n">
         <v>0.138</v>
@@ -3285,7 +3285,7 @@
         <v>249</v>
       </c>
       <c r="B250" t="n">
-        <v>2.0240310384647</v>
+        <v>2.02403103846383</v>
       </c>
       <c r="C250" t="n">
         <v>0.83</v>
@@ -3296,7 +3296,7 @@
         <v>250</v>
       </c>
       <c r="B251" t="n">
-        <v>2.31406471826411</v>
+        <v>2.31406471835651</v>
       </c>
       <c r="C251" t="n">
         <v>0.703</v>
@@ -3307,7 +3307,7 @@
         <v>251</v>
       </c>
       <c r="B252" t="n">
-        <v>4.55043467914545</v>
+        <v>4.55043467915468</v>
       </c>
       <c r="C252" t="n">
         <v>0.194</v>
@@ -3318,7 +3318,7 @@
         <v>252</v>
       </c>
       <c r="B253" t="n">
-        <v>1.99366567573934</v>
+        <v>1.99366567573942</v>
       </c>
       <c r="C253" t="n">
         <v>0.976</v>
@@ -3329,7 +3329,7 @@
         <v>253</v>
       </c>
       <c r="B254" t="n">
-        <v>1.1043905903598</v>
+        <v>1.10439059030195</v>
       </c>
       <c r="C254" t="n">
         <v>0.944</v>
@@ -3340,7 +3340,7 @@
         <v>254</v>
       </c>
       <c r="B255" t="n">
-        <v>3.28924989165984</v>
+        <v>3.28924989165442</v>
       </c>
       <c r="C255" t="n">
         <v>0.453</v>
@@ -3351,7 +3351,7 @@
         <v>255</v>
       </c>
       <c r="B256" t="n">
-        <v>2.43204934496252</v>
+        <v>2.43204934498954</v>
       </c>
       <c r="C256" t="n">
         <v>0.677</v>
@@ -3362,7 +3362,7 @@
         <v>256</v>
       </c>
       <c r="B257" t="n">
-        <v>3.47049437666646</v>
+        <v>3.470494376565</v>
       </c>
       <c r="C257" t="n">
         <v>0.421</v>
@@ -3373,7 +3373,7 @@
         <v>257</v>
       </c>
       <c r="B258" t="n">
-        <v>2.41820097814906</v>
+        <v>2.4182009781418</v>
       </c>
       <c r="C258" t="n">
         <v>0.653</v>
@@ -3384,7 +3384,7 @@
         <v>258</v>
       </c>
       <c r="B259" t="n">
-        <v>4.01399254062787</v>
+        <v>4.01399254064862</v>
       </c>
       <c r="C259" t="n">
         <v>0.223</v>
@@ -3406,7 +3406,7 @@
         <v>260</v>
       </c>
       <c r="B261" t="n">
-        <v>2.20880537501686</v>
+        <v>2.20880537501177</v>
       </c>
       <c r="C261" t="n">
         <v>0.689</v>
@@ -3417,7 +3417,7 @@
         <v>261</v>
       </c>
       <c r="B262" t="n">
-        <v>1.9989359238817</v>
+        <v>1.99893592388166</v>
       </c>
       <c r="C262" t="n">
         <v>0.979</v>
@@ -3439,7 +3439,7 @@
         <v>263</v>
       </c>
       <c r="B264" t="n">
-        <v>3.45575627923089</v>
+        <v>3.45575627916439</v>
       </c>
       <c r="C264" t="n">
         <v>0.31</v>
@@ -3450,7 +3450,7 @@
         <v>264</v>
       </c>
       <c r="B265" t="n">
-        <v>4.82097941707032</v>
+        <v>4.82097941717162</v>
       </c>
       <c r="C265" t="n">
         <v>0.168</v>
@@ -3461,7 +3461,7 @@
         <v>265</v>
       </c>
       <c r="B266" t="n">
-        <v>6.45123696755494</v>
+        <v>6.4512369675843</v>
       </c>
       <c r="C266" t="n">
         <v>0.033</v>
@@ -3472,7 +3472,7 @@
         <v>266</v>
       </c>
       <c r="B267" t="n">
-        <v>4.11226303374314</v>
+        <v>4.11226303373752</v>
       </c>
       <c r="C267" t="n">
         <v>0.248</v>
@@ -3494,7 +3494,7 @@
         <v>268</v>
       </c>
       <c r="B269" t="n">
-        <v>1.55697389498515</v>
+        <v>1.55697389498482</v>
       </c>
       <c r="C269" t="n">
         <v>0.881</v>
@@ -3505,7 +3505,7 @@
         <v>269</v>
       </c>
       <c r="B270" t="n">
-        <v>0.999969438634286</v>
+        <v>0.999969438634287</v>
       </c>
       <c r="C270" t="n">
         <v>0.989</v>
@@ -3516,7 +3516,7 @@
         <v>270</v>
       </c>
       <c r="B271" t="n">
-        <v>3.49496827631377</v>
+        <v>3.49496827632277</v>
       </c>
       <c r="C271" t="n">
         <v>0.364</v>
@@ -3527,7 +3527,7 @@
         <v>271</v>
       </c>
       <c r="B272" t="n">
-        <v>2.07193242779129</v>
+        <v>2.0719324276641</v>
       </c>
       <c r="C272" t="n">
         <v>0.753</v>
@@ -3538,7 +3538,7 @@
         <v>272</v>
       </c>
       <c r="B273" t="n">
-        <v>2.81614042143286</v>
+        <v>2.81614042143681</v>
       </c>
       <c r="C273" t="n">
         <v>0.591</v>
@@ -3549,7 +3549,7 @@
         <v>273</v>
       </c>
       <c r="B274" t="n">
-        <v>2.9755584784274</v>
+        <v>2.97555847842668</v>
       </c>
       <c r="C274" t="n">
         <v>0.491</v>
@@ -3560,7 +3560,7 @@
         <v>274</v>
       </c>
       <c r="B275" t="n">
-        <v>4.13893897484744</v>
+        <v>4.13893897469388</v>
       </c>
       <c r="C275" t="n">
         <v>0.26</v>
@@ -3571,7 +3571,7 @@
         <v>275</v>
       </c>
       <c r="B276" t="n">
-        <v>2.68856198531603</v>
+        <v>2.68856198531564</v>
       </c>
       <c r="C276" t="n">
         <v>0.603</v>
@@ -3582,7 +3582,7 @@
         <v>276</v>
       </c>
       <c r="B277" t="n">
-        <v>4.35844845475828</v>
+        <v>4.3584484547475</v>
       </c>
       <c r="C277" t="n">
         <v>0.185</v>
@@ -3593,7 +3593,7 @@
         <v>277</v>
       </c>
       <c r="B278" t="n">
-        <v>2.57663877158617</v>
+        <v>2.57663877161904</v>
       </c>
       <c r="C278" t="n">
         <v>0.58</v>
@@ -3604,7 +3604,7 @@
         <v>278</v>
       </c>
       <c r="B279" t="n">
-        <v>1.79976932163427</v>
+        <v>1.79976932162428</v>
       </c>
       <c r="C279" t="n">
         <v>0.834</v>
@@ -3615,7 +3615,7 @@
         <v>279</v>
       </c>
       <c r="B280" t="n">
-        <v>3.86671698359916</v>
+        <v>3.86671698372248</v>
       </c>
       <c r="C280" t="n">
         <v>0.28</v>
@@ -3626,7 +3626,7 @@
         <v>280</v>
       </c>
       <c r="B281" t="n">
-        <v>4.93279259825445</v>
+        <v>4.93279259824816</v>
       </c>
       <c r="C281" t="n">
         <v>0.205</v>
@@ -3637,7 +3637,7 @@
         <v>281</v>
       </c>
       <c r="B282" t="n">
-        <v>2.0675035000435</v>
+        <v>2.06750350004951</v>
       </c>
       <c r="C282" t="n">
         <v>0.76</v>
@@ -3648,7 +3648,7 @@
         <v>282</v>
       </c>
       <c r="B283" t="n">
-        <v>4.57582052907173</v>
+        <v>4.57582052911485</v>
       </c>
       <c r="C283" t="n">
         <v>0.153</v>
@@ -3659,7 +3659,7 @@
         <v>283</v>
       </c>
       <c r="B284" t="n">
-        <v>3.07181620465081</v>
+        <v>3.07181620464174</v>
       </c>
       <c r="C284" t="n">
         <v>0.637</v>
@@ -3670,7 +3670,7 @@
         <v>284</v>
       </c>
       <c r="B285" t="n">
-        <v>3.35853927596662</v>
+        <v>3.35853927605468</v>
       </c>
       <c r="C285" t="n">
         <v>0.435</v>
@@ -3681,7 +3681,7 @@
         <v>285</v>
       </c>
       <c r="B286" t="n">
-        <v>1.62585357413465</v>
+        <v>1.62585357415441</v>
       </c>
       <c r="C286" t="n">
         <v>0.748</v>
@@ -3692,7 +3692,7 @@
         <v>286</v>
       </c>
       <c r="B287" t="n">
-        <v>1.999586060215</v>
+        <v>1.99958606021501</v>
       </c>
       <c r="C287" t="n">
         <v>0.898</v>
@@ -3703,7 +3703,7 @@
         <v>287</v>
       </c>
       <c r="B288" t="n">
-        <v>2.25506676341048</v>
+        <v>2.25506676339449</v>
       </c>
       <c r="C288" t="n">
         <v>0.756</v>
@@ -3714,7 +3714,7 @@
         <v>288</v>
       </c>
       <c r="B289" t="n">
-        <v>2.64672493466361</v>
+        <v>2.64672493464748</v>
       </c>
       <c r="C289" t="n">
         <v>0.472</v>
@@ -3725,7 +3725,7 @@
         <v>289</v>
       </c>
       <c r="B290" t="n">
-        <v>3.99643931100845</v>
+        <v>3.99643931099922</v>
       </c>
       <c r="C290" t="n">
         <v>0.256</v>
@@ -3736,7 +3736,7 @@
         <v>290</v>
       </c>
       <c r="B291" t="n">
-        <v>2.7298829556778</v>
+        <v>2.72988294754167</v>
       </c>
       <c r="C291" t="n">
         <v>0.502</v>
@@ -3747,7 +3747,7 @@
         <v>291</v>
       </c>
       <c r="B292" t="n">
-        <v>1.5994202450113</v>
+        <v>1.59942024504694</v>
       </c>
       <c r="C292" t="n">
         <v>0.944</v>
@@ -3758,7 +3758,7 @@
         <v>292</v>
       </c>
       <c r="B293" t="n">
-        <v>2.67263978144198</v>
+        <v>2.67263978145551</v>
       </c>
       <c r="C293" t="n">
         <v>0.564</v>
@@ -3769,7 +3769,7 @@
         <v>293</v>
       </c>
       <c r="B294" t="n">
-        <v>2.91152447230656</v>
+        <v>2.91152447230227</v>
       </c>
       <c r="C294" t="n">
         <v>0.47</v>
@@ -3780,7 +3780,7 @@
         <v>294</v>
       </c>
       <c r="B295" t="n">
-        <v>1.61498424328318</v>
+        <v>1.61498424327386</v>
       </c>
       <c r="C295" t="n">
         <v>0.744</v>
@@ -3791,7 +3791,7 @@
         <v>295</v>
       </c>
       <c r="B296" t="n">
-        <v>2.38567460647452</v>
+        <v>2.38567460647305</v>
       </c>
       <c r="C296" t="n">
         <v>0.699</v>
@@ -3802,7 +3802,7 @@
         <v>296</v>
       </c>
       <c r="B297" t="n">
-        <v>2.9838184570183</v>
+        <v>2.98381845701793</v>
       </c>
       <c r="C297" t="n">
         <v>0.463</v>
@@ -3813,7 +3813,7 @@
         <v>297</v>
       </c>
       <c r="B298" t="n">
-        <v>2.37823459009486</v>
+        <v>2.37823459002274</v>
       </c>
       <c r="C298" t="n">
         <v>0.709</v>
@@ -3824,7 +3824,7 @@
         <v>298</v>
       </c>
       <c r="B299" t="n">
-        <v>6.45631722193075</v>
+        <v>6.45631722190756</v>
       </c>
       <c r="C299" t="n">
         <v>0.046</v>
@@ -3846,7 +3846,7 @@
         <v>300</v>
       </c>
       <c r="B301" t="n">
-        <v>5.39167531528364</v>
+        <v>5.39167531537678</v>
       </c>
       <c r="C301" t="n">
         <v>0.131</v>
@@ -3857,7 +3857,7 @@
         <v>301</v>
       </c>
       <c r="B302" t="n">
-        <v>4.9369588634078</v>
+        <v>4.93695886339923</v>
       </c>
       <c r="C302" t="n">
         <v>0.14</v>
@@ -3868,7 +3868,7 @@
         <v>302</v>
       </c>
       <c r="B303" t="n">
-        <v>3.90615594095199</v>
+        <v>3.90615594097639</v>
       </c>
       <c r="C303" t="n">
         <v>0.398</v>
@@ -3879,7 +3879,7 @@
         <v>303</v>
       </c>
       <c r="B304" t="n">
-        <v>2.35375896491458</v>
+        <v>2.35375896493174</v>
       </c>
       <c r="C304" t="n">
         <v>0.548</v>
@@ -3890,7 +3890,7 @@
         <v>304</v>
       </c>
       <c r="B305" t="n">
-        <v>3.64968364571491</v>
+        <v>3.64968364611032</v>
       </c>
       <c r="C305" t="n">
         <v>0.501</v>
@@ -3901,7 +3901,7 @@
         <v>305</v>
       </c>
       <c r="B306" t="n">
-        <v>3.98619076252353</v>
+        <v>3.98619076252546</v>
       </c>
       <c r="C306" t="n">
         <v>0.269</v>
@@ -3912,7 +3912,7 @@
         <v>306</v>
       </c>
       <c r="B307" t="n">
-        <v>2.42670604969399</v>
+        <v>2.42670604968622</v>
       </c>
       <c r="C307" t="n">
         <v>0.667</v>
@@ -3923,7 +3923,7 @@
         <v>307</v>
       </c>
       <c r="B308" t="n">
-        <v>1.39654013433302</v>
+        <v>1.39654013448945</v>
       </c>
       <c r="C308" t="n">
         <v>0.96</v>
@@ -3934,7 +3934,7 @@
         <v>308</v>
       </c>
       <c r="B309" t="n">
-        <v>3.78170912817644</v>
+        <v>3.78170912836354</v>
       </c>
       <c r="C309" t="n">
         <v>0.352</v>
@@ -3945,7 +3945,7 @@
         <v>309</v>
       </c>
       <c r="B310" t="n">
-        <v>4.5799991069279</v>
+        <v>4.57999910689874</v>
       </c>
       <c r="C310" t="n">
         <v>0.174</v>
@@ -3956,7 +3956,7 @@
         <v>310</v>
       </c>
       <c r="B311" t="n">
-        <v>3.28103793179218</v>
+        <v>3.28103793179017</v>
       </c>
       <c r="C311" t="n">
         <v>0.412</v>
@@ -3967,7 +3967,7 @@
         <v>311</v>
       </c>
       <c r="B312" t="n">
-        <v>1.48255522380205</v>
+        <v>1.48255522372583</v>
       </c>
       <c r="C312" t="n">
         <v>0.927</v>
@@ -3978,7 +3978,7 @@
         <v>312</v>
       </c>
       <c r="B313" t="n">
-        <v>2.89349274968064</v>
+        <v>2.89349274968316</v>
       </c>
       <c r="C313" t="n">
         <v>0.542</v>
@@ -3989,7 +3989,7 @@
         <v>313</v>
       </c>
       <c r="B314" t="n">
-        <v>1.39965789368516</v>
+        <v>1.39965789368634</v>
       </c>
       <c r="C314" t="n">
         <v>0.946</v>
@@ -4000,7 +4000,7 @@
         <v>314</v>
       </c>
       <c r="B315" t="n">
-        <v>3.52194534157307</v>
+        <v>3.52194534157613</v>
       </c>
       <c r="C315" t="n">
         <v>0.38</v>
@@ -4011,7 +4011,7 @@
         <v>315</v>
       </c>
       <c r="B316" t="n">
-        <v>4.23252644124226</v>
+        <v>4.23252644120676</v>
       </c>
       <c r="C316" t="n">
         <v>0.267</v>
@@ -4022,7 +4022,7 @@
         <v>316</v>
       </c>
       <c r="B317" t="n">
-        <v>2.3693762302778</v>
+        <v>2.3693762302331</v>
       </c>
       <c r="C317" t="n">
         <v>0.646</v>
@@ -4033,7 +4033,7 @@
         <v>317</v>
       </c>
       <c r="B318" t="n">
-        <v>5.43261704337478</v>
+        <v>5.4326170411086</v>
       </c>
       <c r="C318" t="n">
         <v>0.135</v>
@@ -4044,7 +4044,7 @@
         <v>318</v>
       </c>
       <c r="B319" t="n">
-        <v>3.45018508117542</v>
+        <v>3.45018508117571</v>
       </c>
       <c r="C319" t="n">
         <v>0.414</v>
@@ -4055,7 +4055,7 @@
         <v>319</v>
       </c>
       <c r="B320" t="n">
-        <v>4.71713205660122</v>
+        <v>4.71713205660566</v>
       </c>
       <c r="C320" t="n">
         <v>0.182</v>
@@ -4066,7 +4066,7 @@
         <v>320</v>
       </c>
       <c r="B321" t="n">
-        <v>2.68565884202618</v>
+        <v>2.68565884199928</v>
       </c>
       <c r="C321" t="n">
         <v>0.474</v>
@@ -4077,7 +4077,7 @@
         <v>321</v>
       </c>
       <c r="B322" t="n">
-        <v>2.70038156116371</v>
+        <v>2.70038156119268</v>
       </c>
       <c r="C322" t="n">
         <v>0.435</v>
@@ -4088,7 +4088,7 @@
         <v>322</v>
       </c>
       <c r="B323" t="n">
-        <v>2.13207226100104</v>
+        <v>2.1320722610389</v>
       </c>
       <c r="C323" t="n">
         <v>0.664</v>
@@ -4099,7 +4099,7 @@
         <v>323</v>
       </c>
       <c r="B324" t="n">
-        <v>1.15886577983115</v>
+        <v>1.15886577989835</v>
       </c>
       <c r="C324" t="n">
         <v>0.939</v>
@@ -4110,7 +4110,7 @@
         <v>324</v>
       </c>
       <c r="B325" t="n">
-        <v>3.82850153213842</v>
+        <v>3.82850153229111</v>
       </c>
       <c r="C325" t="n">
         <v>0.349</v>
@@ -4121,7 +4121,7 @@
         <v>325</v>
       </c>
       <c r="B326" t="n">
-        <v>3.03108099259598</v>
+        <v>3.03108099260957</v>
       </c>
       <c r="C326" t="n">
         <v>0.533</v>
@@ -4132,7 +4132,7 @@
         <v>326</v>
       </c>
       <c r="B327" t="n">
-        <v>3.87743480623969</v>
+        <v>3.87743480624008</v>
       </c>
       <c r="C327" t="n">
         <v>0.387</v>
@@ -4143,7 +4143,7 @@
         <v>327</v>
       </c>
       <c r="B328" t="n">
-        <v>1.87880449122073</v>
+        <v>1.87880449121404</v>
       </c>
       <c r="C328" t="n">
         <v>0.814</v>
@@ -4154,7 +4154,7 @@
         <v>328</v>
       </c>
       <c r="B329" t="n">
-        <v>2.76602663242104</v>
+        <v>2.76602663241947</v>
       </c>
       <c r="C329" t="n">
         <v>0.555</v>
@@ -4165,7 +4165,7 @@
         <v>329</v>
       </c>
       <c r="B330" t="n">
-        <v>5.30434003630678</v>
+        <v>5.3043400363088</v>
       </c>
       <c r="C330" t="n">
         <v>0.16</v>
@@ -4176,7 +4176,7 @@
         <v>330</v>
       </c>
       <c r="B331" t="n">
-        <v>5.00526384531429</v>
+        <v>5.0052638453251</v>
       </c>
       <c r="C331" t="n">
         <v>0.166</v>
@@ -4209,7 +4209,7 @@
         <v>333</v>
       </c>
       <c r="B334" t="n">
-        <v>2.20903576660693</v>
+        <v>2.20903576669196</v>
       </c>
       <c r="C334" t="n">
         <v>0.616</v>
@@ -4220,7 +4220,7 @@
         <v>334</v>
       </c>
       <c r="B335" t="n">
-        <v>1.93520290570094</v>
+        <v>1.93520290571191</v>
       </c>
       <c r="C335" t="n">
         <v>0.871</v>
@@ -4231,7 +4231,7 @@
         <v>335</v>
       </c>
       <c r="B336" t="n">
-        <v>2.59042420620244</v>
+        <v>2.59042420622374</v>
       </c>
       <c r="C336" t="n">
         <v>0.59</v>
@@ -4242,7 +4242,7 @@
         <v>336</v>
       </c>
       <c r="B337" t="n">
-        <v>1.64227168776197</v>
+        <v>1.64227168778135</v>
       </c>
       <c r="C337" t="n">
         <v>0.796</v>
@@ -4253,7 +4253,7 @@
         <v>337</v>
       </c>
       <c r="B338" t="n">
-        <v>3.83850141429971</v>
+        <v>3.838501414319</v>
       </c>
       <c r="C338" t="n">
         <v>0.29</v>
@@ -4264,7 +4264,7 @@
         <v>338</v>
       </c>
       <c r="B339" t="n">
-        <v>1.31169238853035</v>
+        <v>1.31169238841795</v>
       </c>
       <c r="C339" t="n">
         <v>0.955</v>
@@ -4275,7 +4275,7 @@
         <v>339</v>
       </c>
       <c r="B340" t="n">
-        <v>5.55266784526218</v>
+        <v>5.5526678452535</v>
       </c>
       <c r="C340" t="n">
         <v>0.119</v>
@@ -4286,7 +4286,7 @@
         <v>340</v>
       </c>
       <c r="B341" t="n">
-        <v>7.11894798788056</v>
+        <v>7.11894798788732</v>
       </c>
       <c r="C341" t="n">
         <v>0.053</v>
@@ -4297,7 +4297,7 @@
         <v>341</v>
       </c>
       <c r="B342" t="n">
-        <v>1.26135894249972</v>
+        <v>1.26135894250052</v>
       </c>
       <c r="C342" t="n">
         <v>0.969</v>
@@ -4308,7 +4308,7 @@
         <v>342</v>
       </c>
       <c r="B343" t="n">
-        <v>5.45742743547567</v>
+        <v>5.45742743563493</v>
       </c>
       <c r="C343" t="n">
         <v>0.103</v>
@@ -4319,7 +4319,7 @@
         <v>343</v>
       </c>
       <c r="B344" t="n">
-        <v>1.66014263542928</v>
+        <v>1.66014263542526</v>
       </c>
       <c r="C344" t="n">
         <v>0.853</v>
@@ -4330,7 +4330,7 @@
         <v>344</v>
       </c>
       <c r="B345" t="n">
-        <v>6.0374246223753</v>
+        <v>6.03742462222221</v>
       </c>
       <c r="C345" t="n">
         <v>0.183</v>
@@ -4341,7 +4341,7 @@
         <v>345</v>
       </c>
       <c r="B346" t="n">
-        <v>3.79429681042122</v>
+        <v>3.79429681022699</v>
       </c>
       <c r="C346" t="n">
         <v>0.391</v>
@@ -4352,7 +4352,7 @@
         <v>346</v>
       </c>
       <c r="B347" t="n">
-        <v>2.07770831003007</v>
+        <v>2.07770830991217</v>
       </c>
       <c r="C347" t="n">
         <v>0.854</v>
@@ -4363,7 +4363,7 @@
         <v>347</v>
       </c>
       <c r="B348" t="n">
-        <v>2.78540753028619</v>
+        <v>2.78540753020215</v>
       </c>
       <c r="C348" t="n">
         <v>0.734</v>
@@ -4374,7 +4374,7 @@
         <v>348</v>
       </c>
       <c r="B349" t="n">
-        <v>1.99902202014656</v>
+        <v>1.99902202014644</v>
       </c>
       <c r="C349" t="n">
         <v>0.947</v>
@@ -4385,7 +4385,7 @@
         <v>349</v>
       </c>
       <c r="B350" t="n">
-        <v>4.55608045033904</v>
+        <v>4.55608045313105</v>
       </c>
       <c r="C350" t="n">
         <v>0.249</v>
@@ -4396,7 +4396,7 @@
         <v>350</v>
       </c>
       <c r="B351" t="n">
-        <v>4.31212449324391</v>
+        <v>4.31212449353336</v>
       </c>
       <c r="C351" t="n">
         <v>0.18</v>
@@ -4407,7 +4407,7 @@
         <v>351</v>
       </c>
       <c r="B352" t="n">
-        <v>2.25926431928121</v>
+        <v>2.25926431905944</v>
       </c>
       <c r="C352" t="n">
         <v>0.729</v>
@@ -4418,7 +4418,7 @@
         <v>352</v>
       </c>
       <c r="B353" t="n">
-        <v>2.20123364258369</v>
+        <v>2.20123364256993</v>
       </c>
       <c r="C353" t="n">
         <v>0.694</v>
@@ -4440,7 +4440,7 @@
         <v>354</v>
       </c>
       <c r="B355" t="n">
-        <v>1.64683376377594</v>
+        <v>1.64683376388961</v>
       </c>
       <c r="C355" t="n">
         <v>0.746</v>
@@ -4451,7 +4451,7 @@
         <v>355</v>
       </c>
       <c r="B356" t="n">
-        <v>1.99982340358913</v>
+        <v>1.99982340358914</v>
       </c>
       <c r="C356" t="n">
         <v>0.93</v>
@@ -4462,7 +4462,7 @@
         <v>356</v>
       </c>
       <c r="B357" t="n">
-        <v>4.67162063227448</v>
+        <v>4.67162063207221</v>
       </c>
       <c r="C357" t="n">
         <v>0.302</v>
@@ -4473,7 +4473,7 @@
         <v>357</v>
       </c>
       <c r="B358" t="n">
-        <v>2.76732929906464</v>
+        <v>2.76732929898734</v>
       </c>
       <c r="C358" t="n">
         <v>0.508</v>
@@ -4484,7 +4484,7 @@
         <v>358</v>
       </c>
       <c r="B359" t="n">
-        <v>3.46529042878161</v>
+        <v>3.46529042869656</v>
       </c>
       <c r="C359" t="n">
         <v>0.387</v>
@@ -4495,7 +4495,7 @@
         <v>359</v>
       </c>
       <c r="B360" t="n">
-        <v>1.75081992075363</v>
+        <v>1.75081992085289</v>
       </c>
       <c r="C360" t="n">
         <v>0.899</v>
@@ -4506,7 +4506,7 @@
         <v>360</v>
       </c>
       <c r="B361" t="n">
-        <v>4.42324766563716</v>
+        <v>4.4232476656997</v>
       </c>
       <c r="C361" t="n">
         <v>0.332</v>
@@ -4517,7 +4517,7 @@
         <v>361</v>
       </c>
       <c r="B362" t="n">
-        <v>1.33139595489379</v>
+        <v>1.33139595539009</v>
       </c>
       <c r="C362" t="n">
         <v>0.86</v>
@@ -4528,7 +4528,7 @@
         <v>362</v>
       </c>
       <c r="B363" t="n">
-        <v>1.4403350067912</v>
+        <v>1.44033500624844</v>
       </c>
       <c r="C363" t="n">
         <v>0.854</v>
@@ -4539,7 +4539,7 @@
         <v>363</v>
       </c>
       <c r="B364" t="n">
-        <v>3.92161249157463</v>
+        <v>3.92161249160989</v>
       </c>
       <c r="C364" t="n">
         <v>0.309</v>
@@ -4550,7 +4550,7 @@
         <v>364</v>
       </c>
       <c r="B365" t="n">
-        <v>2.89578120745024</v>
+        <v>2.89578120742185</v>
       </c>
       <c r="C365" t="n">
         <v>0.441</v>
@@ -4561,7 +4561,7 @@
         <v>365</v>
       </c>
       <c r="B366" t="n">
-        <v>2.68804491621362</v>
+        <v>2.68804491622874</v>
       </c>
       <c r="C366" t="n">
         <v>0.513</v>
@@ -4572,7 +4572,7 @@
         <v>366</v>
       </c>
       <c r="B367" t="n">
-        <v>1.93709263205805</v>
+        <v>1.93709263201741</v>
       </c>
       <c r="C367" t="n">
         <v>0.8</v>
@@ -4583,7 +4583,7 @@
         <v>367</v>
       </c>
       <c r="B368" t="n">
-        <v>1.99853789264254</v>
+        <v>1.99853789264251</v>
       </c>
       <c r="C368" t="n">
         <v>0.97</v>
@@ -4594,7 +4594,7 @@
         <v>368</v>
       </c>
       <c r="B369" t="n">
-        <v>2.87031901828466</v>
+        <v>2.87031901828696</v>
       </c>
       <c r="C369" t="n">
         <v>0.535</v>
@@ -4605,7 +4605,7 @@
         <v>369</v>
       </c>
       <c r="B370" t="n">
-        <v>1.46946770351907</v>
+        <v>1.46946770352806</v>
       </c>
       <c r="C370" t="n">
         <v>0.877</v>
@@ -4616,7 +4616,7 @@
         <v>370</v>
       </c>
       <c r="B371" t="n">
-        <v>1.45263765619707</v>
+        <v>1.45263765612759</v>
       </c>
       <c r="C371" t="n">
         <v>0.858</v>
@@ -4627,7 +4627,7 @@
         <v>371</v>
       </c>
       <c r="B372" t="n">
-        <v>1.11024210966186</v>
+        <v>1.11024210969191</v>
       </c>
       <c r="C372" t="n">
         <v>0.953</v>
@@ -4638,7 +4638,7 @@
         <v>372</v>
       </c>
       <c r="B373" t="n">
-        <v>2.97029814070622</v>
+        <v>2.97029814124485</v>
       </c>
       <c r="C373" t="n">
         <v>0.504</v>
@@ -4649,7 +4649,7 @@
         <v>373</v>
       </c>
       <c r="B374" t="n">
-        <v>1.07803705379008</v>
+        <v>1.07803705371712</v>
       </c>
       <c r="C374" t="n">
         <v>0.943</v>
@@ -4660,7 +4660,7 @@
         <v>374</v>
       </c>
       <c r="B375" t="n">
-        <v>1.95836429687455</v>
+        <v>1.95836429685704</v>
       </c>
       <c r="C375" t="n">
         <v>0.82</v>
@@ -4671,7 +4671,7 @@
         <v>375</v>
       </c>
       <c r="B376" t="n">
-        <v>2.86422934627825</v>
+        <v>2.86422934633454</v>
       </c>
       <c r="C376" t="n">
         <v>0.355</v>
@@ -4682,7 +4682,7 @@
         <v>376</v>
       </c>
       <c r="B377" t="n">
-        <v>1.99129553752903</v>
+        <v>1.99129553752925</v>
       </c>
       <c r="C377" t="n">
         <v>0.981</v>
@@ -4693,7 +4693,7 @@
         <v>377</v>
       </c>
       <c r="B378" t="n">
-        <v>7.31435539463578</v>
+        <v>7.31435539469142</v>
       </c>
       <c r="C378" t="n">
         <v>0.033</v>
@@ -4704,7 +4704,7 @@
         <v>378</v>
       </c>
       <c r="B379" t="n">
-        <v>3.75421072628932</v>
+        <v>3.75421072642949</v>
       </c>
       <c r="C379" t="n">
         <v>0.326</v>
@@ -4715,7 +4715,7 @@
         <v>379</v>
       </c>
       <c r="B380" t="n">
-        <v>3.12052926848414</v>
+        <v>3.12052926856649</v>
       </c>
       <c r="C380" t="n">
         <v>0.6</v>
@@ -4726,7 +4726,7 @@
         <v>380</v>
       </c>
       <c r="B381" t="n">
-        <v>1.52605539360978</v>
+        <v>1.52605539368495</v>
       </c>
       <c r="C381" t="n">
         <v>0.76</v>
@@ -4737,7 +4737,7 @@
         <v>381</v>
       </c>
       <c r="B382" t="n">
-        <v>1.35095258497858</v>
+        <v>1.35095258490713</v>
       </c>
       <c r="C382" t="n">
         <v>0.878</v>
@@ -4748,7 +4748,7 @@
         <v>382</v>
       </c>
       <c r="B383" t="n">
-        <v>3.13788061426076</v>
+        <v>3.13788061425942</v>
       </c>
       <c r="C383" t="n">
         <v>0.544</v>
@@ -4759,7 +4759,7 @@
         <v>383</v>
       </c>
       <c r="B384" t="n">
-        <v>3.17729760907434</v>
+        <v>3.17729760906463</v>
       </c>
       <c r="C384" t="n">
         <v>0.429</v>
@@ -4770,7 +4770,7 @@
         <v>384</v>
       </c>
       <c r="B385" t="n">
-        <v>6.70047783140372</v>
+        <v>6.7004778308765</v>
       </c>
       <c r="C385" t="n">
         <v>0.053</v>
@@ -4781,7 +4781,7 @@
         <v>385</v>
       </c>
       <c r="B386" t="n">
-        <v>4.15353937959472</v>
+        <v>4.15353937975938</v>
       </c>
       <c r="C386" t="n">
         <v>0.277</v>
@@ -4792,7 +4792,7 @@
         <v>386</v>
       </c>
       <c r="B387" t="n">
-        <v>2.13054584508762</v>
+        <v>2.1305458450793</v>
       </c>
       <c r="C387" t="n">
         <v>0.697</v>
@@ -4803,7 +4803,7 @@
         <v>387</v>
       </c>
       <c r="B388" t="n">
-        <v>3.28721890503493</v>
+        <v>3.2872189050239</v>
       </c>
       <c r="C388" t="n">
         <v>0.602</v>
@@ -4814,7 +4814,7 @@
         <v>388</v>
       </c>
       <c r="B389" t="n">
-        <v>1.05062910710612</v>
+        <v>1.0506291070907</v>
       </c>
       <c r="C389" t="n">
         <v>0.96</v>
@@ -4825,7 +4825,7 @@
         <v>389</v>
       </c>
       <c r="B390" t="n">
-        <v>2.86449075509229</v>
+        <v>2.86449075745159</v>
       </c>
       <c r="C390" t="n">
         <v>0.456</v>
@@ -4836,7 +4836,7 @@
         <v>390</v>
       </c>
       <c r="B391" t="n">
-        <v>2.56787513913705</v>
+        <v>2.56787513901905</v>
       </c>
       <c r="C391" t="n">
         <v>0.671</v>
@@ -4869,7 +4869,7 @@
         <v>393</v>
       </c>
       <c r="B394" t="n">
-        <v>1.99058419117997</v>
+        <v>1.99058419120359</v>
       </c>
       <c r="C394" t="n">
         <v>0.977</v>
@@ -4880,7 +4880,7 @@
         <v>394</v>
       </c>
       <c r="B395" t="n">
-        <v>2.49631268262616</v>
+        <v>2.49631268248758</v>
       </c>
       <c r="C395" t="n">
         <v>0.689</v>
@@ -4891,7 +4891,7 @@
         <v>395</v>
       </c>
       <c r="B396" t="n">
-        <v>1.19241036989206</v>
+        <v>1.19241036981589</v>
       </c>
       <c r="C396" t="n">
         <v>0.923</v>
@@ -4902,7 +4902,7 @@
         <v>396</v>
       </c>
       <c r="B397" t="n">
-        <v>2.11893461843808</v>
+        <v>2.11893461888857</v>
       </c>
       <c r="C397" t="n">
         <v>0.755</v>
@@ -4913,7 +4913,7 @@
         <v>397</v>
       </c>
       <c r="B398" t="n">
-        <v>5.09516593601297</v>
+        <v>5.09516593601016</v>
       </c>
       <c r="C398" t="n">
         <v>0.1</v>
@@ -4924,7 +4924,7 @@
         <v>398</v>
       </c>
       <c r="B399" t="n">
-        <v>3.412503391366</v>
+        <v>3.41250339136063</v>
       </c>
       <c r="C399" t="n">
         <v>0.418</v>
@@ -4946,7 +4946,7 @@
         <v>400</v>
       </c>
       <c r="B401" t="n">
-        <v>6.07318250631478</v>
+        <v>6.07318250631779</v>
       </c>
       <c r="C401" t="n">
         <v>0.043</v>
@@ -4957,7 +4957,7 @@
         <v>401</v>
       </c>
       <c r="B402" t="n">
-        <v>3.04944660131557</v>
+        <v>3.0494466012549</v>
       </c>
       <c r="C402" t="n">
         <v>0.375</v>
@@ -4968,7 +4968,7 @@
         <v>402</v>
       </c>
       <c r="B403" t="n">
-        <v>2.74050217342667</v>
+        <v>2.74050217342883</v>
       </c>
       <c r="C403" t="n">
         <v>0.616</v>
@@ -4979,7 +4979,7 @@
         <v>403</v>
       </c>
       <c r="B404" t="n">
-        <v>5.08333350105267</v>
+        <v>5.08333350105501</v>
       </c>
       <c r="C404" t="n">
         <v>0.157</v>
@@ -4990,7 +4990,7 @@
         <v>404</v>
       </c>
       <c r="B405" t="n">
-        <v>4.08752379658576</v>
+        <v>4.08752379658624</v>
       </c>
       <c r="C405" t="n">
         <v>0.232</v>
@@ -5001,7 +5001,7 @@
         <v>405</v>
       </c>
       <c r="B406" t="n">
-        <v>2.63229821336434</v>
+        <v>2.63229821332738</v>
       </c>
       <c r="C406" t="n">
         <v>0.613</v>
@@ -5012,7 +5012,7 @@
         <v>406</v>
       </c>
       <c r="B407" t="n">
-        <v>3.37219207402164</v>
+        <v>3.3721920741405</v>
       </c>
       <c r="C407" t="n">
         <v>0.401</v>
@@ -5023,7 +5023,7 @@
         <v>407</v>
       </c>
       <c r="B408" t="n">
-        <v>4.81597050969251</v>
+        <v>4.81597050964116</v>
       </c>
       <c r="C408" t="n">
         <v>0.145</v>
@@ -5034,7 +5034,7 @@
         <v>408</v>
       </c>
       <c r="B409" t="n">
-        <v>2.44706313514457</v>
+        <v>2.44706313514864</v>
       </c>
       <c r="C409" t="n">
         <v>0.712</v>
@@ -5045,7 +5045,7 @@
         <v>409</v>
       </c>
       <c r="B410" t="n">
-        <v>4.53648015855972</v>
+        <v>4.53648015855374</v>
       </c>
       <c r="C410" t="n">
         <v>0.155</v>
@@ -5056,7 +5056,7 @@
         <v>410</v>
       </c>
       <c r="B411" t="n">
-        <v>2.03840344454043</v>
+        <v>2.03840344383736</v>
       </c>
       <c r="C411" t="n">
         <v>0.609</v>
@@ -5067,7 +5067,7 @@
         <v>411</v>
       </c>
       <c r="B412" t="n">
-        <v>2.09357277604159</v>
+        <v>2.09357277604248</v>
       </c>
       <c r="C412" t="n">
         <v>0.728</v>
@@ -5078,7 +5078,7 @@
         <v>412</v>
       </c>
       <c r="B413" t="n">
-        <v>4.34578757109217</v>
+        <v>4.34578757115066</v>
       </c>
       <c r="C413" t="n">
         <v>0.252</v>
@@ -5089,7 +5089,7 @@
         <v>413</v>
       </c>
       <c r="B414" t="n">
-        <v>2.25061371184614</v>
+        <v>2.25061371188634</v>
       </c>
       <c r="C414" t="n">
         <v>0.838</v>
@@ -5100,7 +5100,7 @@
         <v>414</v>
       </c>
       <c r="B415" t="n">
-        <v>1.97862355430086</v>
+        <v>1.97862355430394</v>
       </c>
       <c r="C415" t="n">
         <v>0.697</v>
@@ -5111,7 +5111,7 @@
         <v>415</v>
       </c>
       <c r="B416" t="n">
-        <v>2.75040880089042</v>
+        <v>2.75040880089164</v>
       </c>
       <c r="C416" t="n">
         <v>0.516</v>
@@ -5122,7 +5122,7 @@
         <v>416</v>
       </c>
       <c r="B417" t="n">
-        <v>1.49462818004811</v>
+        <v>1.49462818008314</v>
       </c>
       <c r="C417" t="n">
         <v>0.765</v>
@@ -5133,7 +5133,7 @@
         <v>417</v>
       </c>
       <c r="B418" t="n">
-        <v>3.49193687041579</v>
+        <v>3.49193687043897</v>
       </c>
       <c r="C418" t="n">
         <v>0.403</v>
@@ -5144,7 +5144,7 @@
         <v>418</v>
       </c>
       <c r="B419" t="n">
-        <v>1.99985758793988</v>
+        <v>1.99985758793989</v>
       </c>
       <c r="C419" t="n">
         <v>0.909</v>
@@ -5155,7 +5155,7 @@
         <v>419</v>
       </c>
       <c r="B420" t="n">
-        <v>3.17674000854534</v>
+        <v>3.17674000853646</v>
       </c>
       <c r="C420" t="n">
         <v>0.522</v>
@@ -5166,7 +5166,7 @@
         <v>420</v>
       </c>
       <c r="B421" t="n">
-        <v>3.33328677490114</v>
+        <v>3.33328677485716</v>
       </c>
       <c r="C421" t="n">
         <v>0.421</v>
@@ -5177,7 +5177,7 @@
         <v>421</v>
       </c>
       <c r="B422" t="n">
-        <v>3.0990495408889</v>
+        <v>3.09904954089028</v>
       </c>
       <c r="C422" t="n">
         <v>0.495</v>
@@ -5188,7 +5188,7 @@
         <v>422</v>
       </c>
       <c r="B423" t="n">
-        <v>1.75431956111902</v>
+        <v>1.75431956111832</v>
       </c>
       <c r="C423" t="n">
         <v>0.747</v>
@@ -5199,7 +5199,7 @@
         <v>423</v>
       </c>
       <c r="B424" t="n">
-        <v>3.92663018941765</v>
+        <v>3.92663018941677</v>
       </c>
       <c r="C424" t="n">
         <v>0.262</v>
@@ -5210,7 +5210,7 @@
         <v>424</v>
       </c>
       <c r="B425" t="n">
-        <v>1.99139219568941</v>
+        <v>1.99139219568963</v>
       </c>
       <c r="C425" t="n">
         <v>0.974</v>
@@ -5221,7 +5221,7 @@
         <v>425</v>
       </c>
       <c r="B426" t="n">
-        <v>1.36967836207989</v>
+        <v>1.36967836212862</v>
       </c>
       <c r="C426" t="n">
         <v>0.865</v>
@@ -5232,7 +5232,7 @@
         <v>426</v>
       </c>
       <c r="B427" t="n">
-        <v>5.09563637040885</v>
+        <v>5.09563637026188</v>
       </c>
       <c r="C427" t="n">
         <v>0.138</v>
@@ -5243,7 +5243,7 @@
         <v>427</v>
       </c>
       <c r="B428" t="n">
-        <v>2.41241220840748</v>
+        <v>2.412412208558</v>
       </c>
       <c r="C428" t="n">
         <v>0.705</v>
@@ -5254,7 +5254,7 @@
         <v>428</v>
       </c>
       <c r="B429" t="n">
-        <v>2.96118504102784</v>
+        <v>2.96118504102933</v>
       </c>
       <c r="C429" t="n">
         <v>0.563</v>
@@ -5276,7 +5276,7 @@
         <v>430</v>
       </c>
       <c r="B431" t="n">
-        <v>4.77980146786353</v>
+        <v>4.77980146808875</v>
       </c>
       <c r="C431" t="n">
         <v>0.167</v>
@@ -5287,7 +5287,7 @@
         <v>431</v>
       </c>
       <c r="B432" t="n">
-        <v>2.50782685078242</v>
+        <v>2.50782685081296</v>
       </c>
       <c r="C432" t="n">
         <v>0.562</v>
@@ -5298,7 +5298,7 @@
         <v>432</v>
       </c>
       <c r="B433" t="n">
-        <v>1.27362648243756</v>
+        <v>1.27362648240383</v>
       </c>
       <c r="C433" t="n">
         <v>0.933</v>
@@ -5309,7 +5309,7 @@
         <v>433</v>
       </c>
       <c r="B434" t="n">
-        <v>4.82177000595202</v>
+        <v>4.82177000595404</v>
       </c>
       <c r="C434" t="n">
         <v>0.2</v>
@@ -5320,7 +5320,7 @@
         <v>434</v>
       </c>
       <c r="B435" t="n">
-        <v>2.78646471363621</v>
+        <v>2.78646471362172</v>
       </c>
       <c r="C435" t="n">
         <v>0.578</v>
@@ -5331,7 +5331,7 @@
         <v>435</v>
       </c>
       <c r="B436" t="n">
-        <v>1.59195923318462</v>
+        <v>1.59195923323647</v>
       </c>
       <c r="C436" t="n">
         <v>0.833</v>
@@ -5342,7 +5342,7 @@
         <v>436</v>
       </c>
       <c r="B437" t="n">
-        <v>3.53128311036097</v>
+        <v>3.53128311024692</v>
       </c>
       <c r="C437" t="n">
         <v>0.424</v>
@@ -5353,7 +5353,7 @@
         <v>437</v>
       </c>
       <c r="B438" t="n">
-        <v>3.37580977924783</v>
+        <v>3.37580977932275</v>
       </c>
       <c r="C438" t="n">
         <v>0.338</v>
@@ -5364,7 +5364,7 @@
         <v>438</v>
       </c>
       <c r="B439" t="n">
-        <v>1.99898374972858</v>
+        <v>1.99898374972863</v>
       </c>
       <c r="C439" t="n">
         <v>0.962</v>
@@ -5375,7 +5375,7 @@
         <v>439</v>
       </c>
       <c r="B440" t="n">
-        <v>1.54378830781081</v>
+        <v>1.54378830781338</v>
       </c>
       <c r="C440" t="n">
         <v>0.89</v>
@@ -5386,7 +5386,7 @@
         <v>440</v>
       </c>
       <c r="B441" t="n">
-        <v>3.36749307041966</v>
+        <v>3.36749307044154</v>
       </c>
       <c r="C441" t="n">
         <v>0.368</v>
@@ -5397,7 +5397,7 @@
         <v>441</v>
       </c>
       <c r="B442" t="n">
-        <v>3.34121841758331</v>
+        <v>3.34121841789637</v>
       </c>
       <c r="C442" t="n">
         <v>0.477</v>
@@ -5408,7 +5408,7 @@
         <v>442</v>
       </c>
       <c r="B443" t="n">
-        <v>6.66937910251817</v>
+        <v>6.66937910251702</v>
       </c>
       <c r="C443" t="n">
         <v>0.065</v>
@@ -5419,7 +5419,7 @@
         <v>443</v>
       </c>
       <c r="B444" t="n">
-        <v>2.43392522375452</v>
+        <v>2.4339252230653</v>
       </c>
       <c r="C444" t="n">
         <v>0.66</v>
@@ -5430,7 +5430,7 @@
         <v>444</v>
       </c>
       <c r="B445" t="n">
-        <v>4.06870722086353</v>
+        <v>4.06870722088133</v>
       </c>
       <c r="C445" t="n">
         <v>0.335</v>
@@ -5441,7 +5441,7 @@
         <v>445</v>
       </c>
       <c r="B446" t="n">
-        <v>2.5664213716301</v>
+        <v>2.56642137165545</v>
       </c>
       <c r="C446" t="n">
         <v>0.644</v>
@@ -5452,7 +5452,7 @@
         <v>446</v>
       </c>
       <c r="B447" t="n">
-        <v>1.0834144900657</v>
+        <v>1.08341448995955</v>
       </c>
       <c r="C447" t="n">
         <v>0.949</v>
@@ -5463,7 +5463,7 @@
         <v>447</v>
       </c>
       <c r="B448" t="n">
-        <v>1.86393611946644</v>
+        <v>1.86393611943106</v>
       </c>
       <c r="C448" t="n">
         <v>0.777</v>
@@ -5474,7 +5474,7 @@
         <v>448</v>
       </c>
       <c r="B449" t="n">
-        <v>3.84936461100221</v>
+        <v>3.84936461100407</v>
       </c>
       <c r="C449" t="n">
         <v>0.476</v>
@@ -5485,7 +5485,7 @@
         <v>449</v>
       </c>
       <c r="B450" t="n">
-        <v>1.98888622994238</v>
+        <v>1.98888622994146</v>
       </c>
       <c r="C450" t="n">
         <v>0.981</v>
@@ -5496,7 +5496,7 @@
         <v>450</v>
       </c>
       <c r="B451" t="n">
-        <v>6.62131253628902</v>
+        <v>6.62131253637407</v>
       </c>
       <c r="C451" t="n">
         <v>0.1</v>
@@ -5507,7 +5507,7 @@
         <v>451</v>
       </c>
       <c r="B452" t="n">
-        <v>1.91592779544593</v>
+        <v>1.91592779544653</v>
       </c>
       <c r="C452" t="n">
         <v>0.817</v>
@@ -5518,7 +5518,7 @@
         <v>452</v>
       </c>
       <c r="B453" t="n">
-        <v>5.79681202790543</v>
+        <v>5.79681202790635</v>
       </c>
       <c r="C453" t="n">
         <v>0.087</v>
@@ -5529,7 +5529,7 @@
         <v>453</v>
       </c>
       <c r="B454" t="n">
-        <v>2.97512286562355</v>
+        <v>2.97512286562793</v>
       </c>
       <c r="C454" t="n">
         <v>0.503</v>
@@ -5540,7 +5540,7 @@
         <v>454</v>
       </c>
       <c r="B455" t="n">
-        <v>6.02796104759616</v>
+        <v>6.02796104751638</v>
       </c>
       <c r="C455" t="n">
         <v>0.059</v>
@@ -5551,7 +5551,7 @@
         <v>455</v>
       </c>
       <c r="B456" t="n">
-        <v>2.76310207517639</v>
+        <v>2.76310207509126</v>
       </c>
       <c r="C456" t="n">
         <v>0.657</v>
@@ -5562,7 +5562,7 @@
         <v>456</v>
       </c>
       <c r="B457" t="n">
-        <v>4.38058116167241</v>
+        <v>4.38058116171625</v>
       </c>
       <c r="C457" t="n">
         <v>0.207</v>
@@ -5573,7 +5573,7 @@
         <v>457</v>
       </c>
       <c r="B458" t="n">
-        <v>2.74910908028012</v>
+        <v>2.74910908030887</v>
       </c>
       <c r="C458" t="n">
         <v>0.528</v>
@@ -5584,7 +5584,7 @@
         <v>458</v>
       </c>
       <c r="B459" t="n">
-        <v>3.92022673694507</v>
+        <v>3.92022673697588</v>
       </c>
       <c r="C459" t="n">
         <v>0.281</v>
@@ -5595,7 +5595,7 @@
         <v>459</v>
       </c>
       <c r="B460" t="n">
-        <v>2.55474329782101</v>
+        <v>2.55474329803199</v>
       </c>
       <c r="C460" t="n">
         <v>0.486</v>
@@ -5617,7 +5617,7 @@
         <v>461</v>
       </c>
       <c r="B462" t="n">
-        <v>1.5575334686205</v>
+        <v>1.55753346862702</v>
       </c>
       <c r="C462" t="n">
         <v>0.872</v>
@@ -5661,7 +5661,7 @@
         <v>465</v>
       </c>
       <c r="B466" t="n">
-        <v>2.13947969333686</v>
+        <v>2.13947969322678</v>
       </c>
       <c r="C466" t="n">
         <v>0.726</v>
@@ -5672,7 +5672,7 @@
         <v>466</v>
       </c>
       <c r="B467" t="n">
-        <v>1.82899037393224</v>
+        <v>1.82899037398282</v>
       </c>
       <c r="C467" t="n">
         <v>0.804</v>
@@ -5683,7 +5683,7 @@
         <v>467</v>
       </c>
       <c r="B468" t="n">
-        <v>5.03274221179748</v>
+        <v>5.03274221178095</v>
       </c>
       <c r="C468" t="n">
         <v>0.288</v>
@@ -5694,7 +5694,7 @@
         <v>468</v>
       </c>
       <c r="B469" t="n">
-        <v>2.60420127883402</v>
+        <v>2.6042012787376</v>
       </c>
       <c r="C469" t="n">
         <v>0.659</v>
@@ -5705,7 +5705,7 @@
         <v>469</v>
       </c>
       <c r="B470" t="n">
-        <v>1.99997040120445</v>
+        <v>1.99997040120443</v>
       </c>
       <c r="C470" t="n">
         <v>0.938</v>
@@ -5716,7 +5716,7 @@
         <v>470</v>
       </c>
       <c r="B471" t="n">
-        <v>3.18869319399741</v>
+        <v>3.18869319400252</v>
       </c>
       <c r="C471" t="n">
         <v>0.52</v>
@@ -5727,7 +5727,7 @@
         <v>471</v>
       </c>
       <c r="B472" t="n">
-        <v>5.12076055368847</v>
+        <v>5.12076055361053</v>
       </c>
       <c r="C472" t="n">
         <v>0.171</v>
@@ -5738,7 +5738,7 @@
         <v>472</v>
       </c>
       <c r="B473" t="n">
-        <v>7.16382144671818</v>
+        <v>7.16382144551206</v>
       </c>
       <c r="C473" t="n">
         <v>0.036</v>
@@ -5749,7 +5749,7 @@
         <v>473</v>
       </c>
       <c r="B474" t="n">
-        <v>3.01856777253105</v>
+        <v>3.01856777251935</v>
       </c>
       <c r="C474" t="n">
         <v>0.468</v>
@@ -5760,7 +5760,7 @@
         <v>474</v>
       </c>
       <c r="B475" t="n">
-        <v>4.8147769435452</v>
+        <v>4.81477694302321</v>
       </c>
       <c r="C475" t="n">
         <v>0.162</v>
@@ -5771,7 +5771,7 @@
         <v>475</v>
       </c>
       <c r="B476" t="n">
-        <v>2.24212162822936</v>
+        <v>2.24212162821055</v>
       </c>
       <c r="C476" t="n">
         <v>0.572</v>
@@ -5782,7 +5782,7 @@
         <v>476</v>
       </c>
       <c r="B477" t="n">
-        <v>1.6243725113333</v>
+        <v>1.62437251133169</v>
       </c>
       <c r="C477" t="n">
         <v>0.887</v>
@@ -5793,7 +5793,7 @@
         <v>477</v>
       </c>
       <c r="B478" t="n">
-        <v>1.16168394762512</v>
+        <v>1.16168394767478</v>
       </c>
       <c r="C478" t="n">
         <v>0.889</v>
@@ -5804,7 +5804,7 @@
         <v>478</v>
       </c>
       <c r="B479" t="n">
-        <v>1.99134176508337</v>
+        <v>1.99134176511927</v>
       </c>
       <c r="C479" t="n">
         <v>0.854</v>
@@ -5815,7 +5815,7 @@
         <v>479</v>
       </c>
       <c r="B480" t="n">
-        <v>3.36955764805592</v>
+        <v>3.36955764805759</v>
       </c>
       <c r="C480" t="n">
         <v>0.442</v>
@@ -5826,7 +5826,7 @@
         <v>480</v>
       </c>
       <c r="B481" t="n">
-        <v>5.52443589296017</v>
+        <v>5.52443589298364</v>
       </c>
       <c r="C481" t="n">
         <v>0.097</v>
@@ -5837,7 +5837,7 @@
         <v>481</v>
       </c>
       <c r="B482" t="n">
-        <v>1.04438243817274</v>
+        <v>1.04438243817933</v>
       </c>
       <c r="C482" t="n">
         <v>0.969</v>
@@ -5848,7 +5848,7 @@
         <v>482</v>
       </c>
       <c r="B483" t="n">
-        <v>0.999927514384142</v>
+        <v>0.999927514384713</v>
       </c>
       <c r="C483" t="n">
         <v>0.995</v>
@@ -5859,7 +5859,7 @@
         <v>483</v>
       </c>
       <c r="B484" t="n">
-        <v>1.3555503409553</v>
+        <v>1.3555503410316</v>
       </c>
       <c r="C484" t="n">
         <v>0.927</v>
@@ -5870,7 +5870,7 @@
         <v>484</v>
       </c>
       <c r="B485" t="n">
-        <v>3.89982753853745</v>
+        <v>3.89982753838309</v>
       </c>
       <c r="C485" t="n">
         <v>0.233</v>
@@ -5881,7 +5881,7 @@
         <v>485</v>
       </c>
       <c r="B486" t="n">
-        <v>3.82497130063861</v>
+        <v>3.82497130067691</v>
       </c>
       <c r="C486" t="n">
         <v>0.291</v>
@@ -5892,7 +5892,7 @@
         <v>486</v>
       </c>
       <c r="B487" t="n">
-        <v>6.87444914501562</v>
+        <v>6.87444914523159</v>
       </c>
       <c r="C487" t="n">
         <v>0.058</v>
@@ -5903,7 +5903,7 @@
         <v>487</v>
       </c>
       <c r="B488" t="n">
-        <v>3.70060875959775</v>
+        <v>3.7006087506788</v>
       </c>
       <c r="C488" t="n">
         <v>0.476</v>
@@ -5914,7 +5914,7 @@
         <v>488</v>
       </c>
       <c r="B489" t="n">
-        <v>2.8400296676476</v>
+        <v>2.84002966765603</v>
       </c>
       <c r="C489" t="n">
         <v>0.514</v>
@@ -5925,7 +5925,7 @@
         <v>489</v>
       </c>
       <c r="B490" t="n">
-        <v>2.03292828425157</v>
+        <v>2.03292828174759</v>
       </c>
       <c r="C490" t="n">
         <v>0.825</v>
@@ -5936,7 +5936,7 @@
         <v>490</v>
       </c>
       <c r="B491" t="n">
-        <v>1.99946476776047</v>
+        <v>1.99946476776043</v>
       </c>
       <c r="C491" t="n">
         <v>0.941</v>
@@ -5958,7 +5958,7 @@
         <v>492</v>
       </c>
       <c r="B493" t="n">
-        <v>2.46030860795989</v>
+        <v>2.46030860791997</v>
       </c>
       <c r="C493" t="n">
         <v>0.769</v>
@@ -5969,7 +5969,7 @@
         <v>493</v>
       </c>
       <c r="B494" t="n">
-        <v>4.60347345712497</v>
+        <v>4.60347345712311</v>
       </c>
       <c r="C494" t="n">
         <v>0.145</v>
@@ -5980,7 +5980,7 @@
         <v>494</v>
       </c>
       <c r="B495" t="n">
-        <v>5.0174135858816</v>
+        <v>5.0174135836107</v>
       </c>
       <c r="C495" t="n">
         <v>0.166</v>
@@ -5991,7 +5991,7 @@
         <v>495</v>
       </c>
       <c r="B496" t="n">
-        <v>1.99981174700078</v>
+        <v>1.99981174700081</v>
       </c>
       <c r="C496" t="n">
         <v>0.914</v>
@@ -6002,7 +6002,7 @@
         <v>496</v>
       </c>
       <c r="B497" t="n">
-        <v>1.08055274620344</v>
+        <v>1.08055274621251</v>
       </c>
       <c r="C497" t="n">
         <v>0.952</v>
@@ -6013,7 +6013,7 @@
         <v>497</v>
       </c>
       <c r="B498" t="n">
-        <v>1.79315013382625</v>
+        <v>1.79315013369088</v>
       </c>
       <c r="C498" t="n">
         <v>0.872</v>
@@ -6024,7 +6024,7 @@
         <v>498</v>
       </c>
       <c r="B499" t="n">
-        <v>2.62771788526579</v>
+        <v>2.6277178850461</v>
       </c>
       <c r="C499" t="n">
         <v>0.614</v>
@@ -6035,7 +6035,7 @@
         <v>499</v>
       </c>
       <c r="B500" t="n">
-        <v>2.49004275233111</v>
+        <v>2.49004275213341</v>
       </c>
       <c r="C500" t="n">
         <v>0.697</v>
@@ -6046,7 +6046,7 @@
         <v>500</v>
       </c>
       <c r="B501" t="n">
-        <v>2.44594180596677</v>
+        <v>2.44594180594737</v>
       </c>
       <c r="C501" t="n">
         <v>0.666</v>
@@ -6057,7 +6057,7 @@
         <v>501</v>
       </c>
       <c r="B502" t="n">
-        <v>1.59778371983185</v>
+        <v>1.59778371942719</v>
       </c>
       <c r="C502" t="n">
         <v>0.73</v>
@@ -6068,7 +6068,7 @@
         <v>502</v>
       </c>
       <c r="B503" t="n">
-        <v>2.76707532141284</v>
+        <v>2.76707532142636</v>
       </c>
       <c r="C503" t="n">
         <v>0.552</v>
@@ -6079,7 +6079,7 @@
         <v>503</v>
       </c>
       <c r="B504" t="n">
-        <v>2.69665488066199</v>
+        <v>2.69665488057536</v>
       </c>
       <c r="C504" t="n">
         <v>0.345</v>
@@ -6090,7 +6090,7 @@
         <v>504</v>
       </c>
       <c r="B505" t="n">
-        <v>1.73282071284963</v>
+        <v>1.73282071285042</v>
       </c>
       <c r="C505" t="n">
         <v>0.871</v>
@@ -6101,7 +6101,7 @@
         <v>505</v>
       </c>
       <c r="B506" t="n">
-        <v>1.51130869791639</v>
+        <v>1.51130869786401</v>
       </c>
       <c r="C506" t="n">
         <v>0.909</v>
@@ -6112,7 +6112,7 @@
         <v>506</v>
       </c>
       <c r="B507" t="n">
-        <v>3.51271965373666</v>
+        <v>3.51271965371135</v>
       </c>
       <c r="C507" t="n">
         <v>0.483</v>
@@ -6123,7 +6123,7 @@
         <v>507</v>
       </c>
       <c r="B508" t="n">
-        <v>9.31364380119964</v>
+        <v>9.31364380125229</v>
       </c>
       <c r="C508" t="n">
         <v>0.013</v>
@@ -6134,7 +6134,7 @@
         <v>508</v>
       </c>
       <c r="B509" t="n">
-        <v>3.85822410392292</v>
+        <v>3.85822410441724</v>
       </c>
       <c r="C509" t="n">
         <v>0.34</v>
@@ -6145,7 +6145,7 @@
         <v>509</v>
       </c>
       <c r="B510" t="n">
-        <v>3.84302648239237</v>
+        <v>3.84302648232043</v>
       </c>
       <c r="C510" t="n">
         <v>0.293</v>
@@ -6156,7 +6156,7 @@
         <v>510</v>
       </c>
       <c r="B511" t="n">
-        <v>4.29174739964052</v>
+        <v>4.29174739964095</v>
       </c>
       <c r="C511" t="n">
         <v>0.234</v>
@@ -6167,7 +6167,7 @@
         <v>511</v>
       </c>
       <c r="B512" t="n">
-        <v>5.40350358644614</v>
+        <v>5.40350358643583</v>
       </c>
       <c r="C512" t="n">
         <v>0.108</v>
@@ -6178,7 +6178,7 @@
         <v>512</v>
       </c>
       <c r="B513" t="n">
-        <v>1.91288932994344</v>
+        <v>1.91288932995403</v>
       </c>
       <c r="C513" t="n">
         <v>0.787</v>
@@ -6189,7 +6189,7 @@
         <v>513</v>
       </c>
       <c r="B514" t="n">
-        <v>2.31276674785886</v>
+        <v>2.31276674787236</v>
       </c>
       <c r="C514" t="n">
         <v>0.666</v>
@@ -6200,7 +6200,7 @@
         <v>514</v>
       </c>
       <c r="B515" t="n">
-        <v>3.95181800109143</v>
+        <v>3.95181800113663</v>
       </c>
       <c r="C515" t="n">
         <v>0.323</v>
@@ -6211,7 +6211,7 @@
         <v>515</v>
       </c>
       <c r="B516" t="n">
-        <v>3.90715180406054</v>
+        <v>3.90715180406185</v>
       </c>
       <c r="C516" t="n">
         <v>0.283</v>
@@ -6222,7 +6222,7 @@
         <v>516</v>
       </c>
       <c r="B517" t="n">
-        <v>3.46788833588116</v>
+        <v>3.46788833591219</v>
       </c>
       <c r="C517" t="n">
         <v>0.364</v>
@@ -6233,7 +6233,7 @@
         <v>517</v>
       </c>
       <c r="B518" t="n">
-        <v>4.06810794906411</v>
+        <v>4.06810794912231</v>
       </c>
       <c r="C518" t="n">
         <v>0.269</v>
@@ -6244,7 +6244,7 @@
         <v>518</v>
       </c>
       <c r="B519" t="n">
-        <v>2.22626240785047</v>
+        <v>2.22626241333518</v>
       </c>
       <c r="C519" t="n">
         <v>0.651</v>
@@ -6255,7 +6255,7 @@
         <v>519</v>
       </c>
       <c r="B520" t="n">
-        <v>2.57652210567259</v>
+        <v>2.57652210566898</v>
       </c>
       <c r="C520" t="n">
         <v>0.656</v>
@@ -6266,7 +6266,7 @@
         <v>520</v>
       </c>
       <c r="B521" t="n">
-        <v>3.38174010629362</v>
+        <v>3.38174010629799</v>
       </c>
       <c r="C521" t="n">
         <v>0.431</v>
@@ -6277,7 +6277,7 @@
         <v>521</v>
       </c>
       <c r="B522" t="n">
-        <v>1.85175477150138</v>
+        <v>1.85175477149464</v>
       </c>
       <c r="C522" t="n">
         <v>0.8</v>
@@ -6288,7 +6288,7 @@
         <v>522</v>
       </c>
       <c r="B523" t="n">
-        <v>2.01626444782597</v>
+        <v>2.01626444781933</v>
       </c>
       <c r="C523" t="n">
         <v>0.82</v>
@@ -6299,7 +6299,7 @@
         <v>523</v>
       </c>
       <c r="B524" t="n">
-        <v>2.82980468808507</v>
+        <v>2.82980468809638</v>
       </c>
       <c r="C524" t="n">
         <v>0.5</v>
@@ -6310,7 +6310,7 @@
         <v>524</v>
       </c>
       <c r="B525" t="n">
-        <v>2.11071904385002</v>
+        <v>2.11071904384904</v>
       </c>
       <c r="C525" t="n">
         <v>0.856</v>
@@ -6321,7 +6321,7 @@
         <v>525</v>
       </c>
       <c r="B526" t="n">
-        <v>9.53044968450489</v>
+        <v>9.53044968496803</v>
       </c>
       <c r="C526" t="n">
         <v>0.01</v>
@@ -6332,7 +6332,7 @@
         <v>526</v>
       </c>
       <c r="B527" t="n">
-        <v>3.00689781734763</v>
+        <v>3.00689781734659</v>
       </c>
       <c r="C527" t="n">
         <v>0.442</v>
@@ -6343,7 +6343,7 @@
         <v>527</v>
       </c>
       <c r="B528" t="n">
-        <v>2.72741092965611</v>
+        <v>2.72741092966567</v>
       </c>
       <c r="C528" t="n">
         <v>0.546</v>
@@ -6354,7 +6354,7 @@
         <v>528</v>
       </c>
       <c r="B529" t="n">
-        <v>2.85463897727672</v>
+        <v>2.85463897698433</v>
       </c>
       <c r="C529" t="n">
         <v>0.428</v>
@@ -6365,7 +6365,7 @@
         <v>529</v>
       </c>
       <c r="B530" t="n">
-        <v>2.53576451816938</v>
+        <v>2.53576451821708</v>
       </c>
       <c r="C530" t="n">
         <v>0.518</v>
@@ -6376,7 +6376,7 @@
         <v>530</v>
       </c>
       <c r="B531" t="n">
-        <v>2.91639545247047</v>
+        <v>2.9163954523464</v>
       </c>
       <c r="C531" t="n">
         <v>0.476</v>
@@ -6387,7 +6387,7 @@
         <v>531</v>
       </c>
       <c r="B532" t="n">
-        <v>6.30194765026803</v>
+        <v>6.30194765019637</v>
       </c>
       <c r="C532" t="n">
         <v>0.079</v>
@@ -6398,7 +6398,7 @@
         <v>532</v>
       </c>
       <c r="B533" t="n">
-        <v>1.49494522316452</v>
+        <v>1.49494522311966</v>
       </c>
       <c r="C533" t="n">
         <v>0.879</v>
@@ -6409,7 +6409,7 @@
         <v>533</v>
       </c>
       <c r="B534" t="n">
-        <v>2.94130022412282</v>
+        <v>2.94130022412783</v>
       </c>
       <c r="C534" t="n">
         <v>0.488</v>
@@ -6420,7 +6420,7 @@
         <v>534</v>
       </c>
       <c r="B535" t="n">
-        <v>2.32212021414932</v>
+        <v>2.32212021384231</v>
       </c>
       <c r="C535" t="n">
         <v>0.652</v>
@@ -6431,7 +6431,7 @@
         <v>535</v>
       </c>
       <c r="B536" t="n">
-        <v>3.38445555076499</v>
+        <v>3.38445555067101</v>
       </c>
       <c r="C536" t="n">
         <v>0.441</v>
@@ -6442,7 +6442,7 @@
         <v>536</v>
       </c>
       <c r="B537" t="n">
-        <v>2.36022908951091</v>
+        <v>2.36022908961616</v>
       </c>
       <c r="C537" t="n">
         <v>0.682</v>
@@ -6453,7 +6453,7 @@
         <v>537</v>
       </c>
       <c r="B538" t="n">
-        <v>2.28198313367725</v>
+        <v>2.28198313368765</v>
       </c>
       <c r="C538" t="n">
         <v>0.679</v>
@@ -6464,7 +6464,7 @@
         <v>538</v>
       </c>
       <c r="B539" t="n">
-        <v>3.92375061397113</v>
+        <v>3.92375061401999</v>
       </c>
       <c r="C539" t="n">
         <v>0.295</v>
@@ -6475,7 +6475,7 @@
         <v>539</v>
       </c>
       <c r="B540" t="n">
-        <v>2.67576425574745</v>
+        <v>2.67576425569472</v>
       </c>
       <c r="C540" t="n">
         <v>0.562</v>
@@ -6486,7 +6486,7 @@
         <v>540</v>
       </c>
       <c r="B541" t="n">
-        <v>2.53250717841657</v>
+        <v>2.53250717749117</v>
       </c>
       <c r="C541" t="n">
         <v>0.519</v>
@@ -6497,7 +6497,7 @@
         <v>541</v>
       </c>
       <c r="B542" t="n">
-        <v>2.47549769809744</v>
+        <v>2.47549769808849</v>
       </c>
       <c r="C542" t="n">
         <v>0.709</v>
@@ -6519,7 +6519,7 @@
         <v>543</v>
       </c>
       <c r="B544" t="n">
-        <v>3.635040578656</v>
+        <v>3.63504057876002</v>
       </c>
       <c r="C544" t="n">
         <v>0.376</v>
@@ -6530,7 +6530,7 @@
         <v>544</v>
       </c>
       <c r="B545" t="n">
-        <v>2.95415526410796</v>
+        <v>2.9541552641077</v>
       </c>
       <c r="C545" t="n">
         <v>0.512</v>
@@ -6541,7 +6541,7 @@
         <v>545</v>
       </c>
       <c r="B546" t="n">
-        <v>4.47508667866193</v>
+        <v>4.47508667845834</v>
       </c>
       <c r="C546" t="n">
         <v>0.206</v>
@@ -6563,7 +6563,7 @@
         <v>547</v>
       </c>
       <c r="B548" t="n">
-        <v>2.35289490812072</v>
+        <v>2.35289490818957</v>
       </c>
       <c r="C548" t="n">
         <v>0.589</v>
@@ -6585,7 +6585,7 @@
         <v>549</v>
       </c>
       <c r="B550" t="n">
-        <v>5.59186939136861</v>
+        <v>5.59186939136629</v>
       </c>
       <c r="C550" t="n">
         <v>0.102</v>
@@ -6607,7 +6607,7 @@
         <v>551</v>
       </c>
       <c r="B552" t="n">
-        <v>1.36919256852374</v>
+        <v>1.36919256860584</v>
       </c>
       <c r="C552" t="n">
         <v>0.95</v>
@@ -6618,7 +6618,7 @@
         <v>552</v>
       </c>
       <c r="B553" t="n">
-        <v>4.50637475794921</v>
+        <v>4.506374757951</v>
       </c>
       <c r="C553" t="n">
         <v>0.235</v>
@@ -6629,7 +6629,7 @@
         <v>553</v>
       </c>
       <c r="B554" t="n">
-        <v>1.99916734193317</v>
+        <v>1.99916734193318</v>
       </c>
       <c r="C554" t="n">
         <v>0.949</v>
@@ -6640,7 +6640,7 @@
         <v>554</v>
       </c>
       <c r="B555" t="n">
-        <v>3.75837827724124</v>
+        <v>3.75837827725565</v>
       </c>
       <c r="C555" t="n">
         <v>0.341</v>
@@ -6651,7 +6651,7 @@
         <v>555</v>
       </c>
       <c r="B556" t="n">
-        <v>3.18641310351018</v>
+        <v>3.1864131035096</v>
       </c>
       <c r="C556" t="n">
         <v>0.528</v>
@@ -6662,7 +6662,7 @@
         <v>556</v>
       </c>
       <c r="B557" t="n">
-        <v>2.42246162306148</v>
+        <v>2.4224616231275</v>
       </c>
       <c r="C557" t="n">
         <v>0.551</v>
@@ -6673,7 +6673,7 @@
         <v>557</v>
       </c>
       <c r="B558" t="n">
-        <v>1.75964551664667</v>
+        <v>1.75964551645869</v>
       </c>
       <c r="C558" t="n">
         <v>0.901</v>
@@ -6684,7 +6684,7 @@
         <v>558</v>
       </c>
       <c r="B559" t="n">
-        <v>2.97983870968254</v>
+        <v>2.97983870968253</v>
       </c>
       <c r="C559" t="n">
         <v>0.379</v>
@@ -6695,7 +6695,7 @@
         <v>559</v>
       </c>
       <c r="B560" t="n">
-        <v>3.15172264174507</v>
+        <v>3.15172264188805</v>
       </c>
       <c r="C560" t="n">
         <v>0.425</v>
@@ -6706,7 +6706,7 @@
         <v>560</v>
       </c>
       <c r="B561" t="n">
-        <v>3.8738832832167</v>
+        <v>3.87388328316982</v>
       </c>
       <c r="C561" t="n">
         <v>0.351</v>
@@ -6717,7 +6717,7 @@
         <v>561</v>
       </c>
       <c r="B562" t="n">
-        <v>4.48172295788519</v>
+        <v>4.48172295788139</v>
       </c>
       <c r="C562" t="n">
         <v>0.267</v>
@@ -6728,7 +6728,7 @@
         <v>562</v>
       </c>
       <c r="B563" t="n">
-        <v>3.13018891592651</v>
+        <v>3.13018891606848</v>
       </c>
       <c r="C563" t="n">
         <v>0.479</v>
@@ -6761,7 +6761,7 @@
         <v>565</v>
       </c>
       <c r="B566" t="n">
-        <v>1.75904786302011</v>
+        <v>1.75904786302392</v>
       </c>
       <c r="C566" t="n">
         <v>0.726</v>
@@ -6772,7 +6772,7 @@
         <v>566</v>
       </c>
       <c r="B567" t="n">
-        <v>3.29220385096221</v>
+        <v>3.29220385095746</v>
       </c>
       <c r="C567" t="n">
         <v>0.406</v>
@@ -6783,7 +6783,7 @@
         <v>567</v>
       </c>
       <c r="B568" t="n">
-        <v>2.90116688555533</v>
+        <v>2.9011668855692</v>
       </c>
       <c r="C568" t="n">
         <v>0.567</v>
@@ -6794,7 +6794,7 @@
         <v>568</v>
       </c>
       <c r="B569" t="n">
-        <v>6.71603430259234</v>
+        <v>6.71603430255276</v>
       </c>
       <c r="C569" t="n">
         <v>0.038</v>
@@ -6805,7 +6805,7 @@
         <v>569</v>
       </c>
       <c r="B570" t="n">
-        <v>3.37866981578103</v>
+        <v>3.37866981578434</v>
       </c>
       <c r="C570" t="n">
         <v>0.29</v>
@@ -6816,7 +6816,7 @@
         <v>570</v>
       </c>
       <c r="B571" t="n">
-        <v>4.54887779239784</v>
+        <v>4.54887779278693</v>
       </c>
       <c r="C571" t="n">
         <v>0.174</v>
@@ -6827,7 +6827,7 @@
         <v>571</v>
       </c>
       <c r="B572" t="n">
-        <v>2.20692732121395</v>
+        <v>2.20692732109881</v>
       </c>
       <c r="C572" t="n">
         <v>0.774</v>
@@ -6838,7 +6838,7 @@
         <v>572</v>
       </c>
       <c r="B573" t="n">
-        <v>6.06169765277142</v>
+        <v>6.0616976522677</v>
       </c>
       <c r="C573" t="n">
         <v>0.065</v>
@@ -6849,7 +6849,7 @@
         <v>573</v>
       </c>
       <c r="B574" t="n">
-        <v>2.45681940386358</v>
+        <v>2.4568194038662</v>
       </c>
       <c r="C574" t="n">
         <v>0.736</v>
@@ -6860,7 +6860,7 @@
         <v>574</v>
       </c>
       <c r="B575" t="n">
-        <v>2.64143969738527</v>
+        <v>2.6414396973666</v>
       </c>
       <c r="C575" t="n">
         <v>0.537</v>
@@ -6871,7 +6871,7 @@
         <v>575</v>
       </c>
       <c r="B576" t="n">
-        <v>4.05833768564504</v>
+        <v>4.05833768564927</v>
       </c>
       <c r="C576" t="n">
         <v>0.282</v>
@@ -6882,7 +6882,7 @@
         <v>576</v>
       </c>
       <c r="B577" t="n">
-        <v>1.44204669939018</v>
+        <v>1.44204669935375</v>
       </c>
       <c r="C577" t="n">
         <v>0.946</v>
@@ -6893,7 +6893,7 @@
         <v>577</v>
       </c>
       <c r="B578" t="n">
-        <v>2.85933770529671</v>
+        <v>2.85933770526907</v>
       </c>
       <c r="C578" t="n">
         <v>0.482</v>
@@ -6904,7 +6904,7 @@
         <v>578</v>
       </c>
       <c r="B579" t="n">
-        <v>1.57304006678468</v>
+        <v>1.57304006671976</v>
       </c>
       <c r="C579" t="n">
         <v>0.907</v>
@@ -6915,7 +6915,7 @@
         <v>579</v>
       </c>
       <c r="B580" t="n">
-        <v>1.01514362300717</v>
+        <v>1.01514362313625</v>
       </c>
       <c r="C580" t="n">
         <v>0.982</v>
@@ -6926,7 +6926,7 @@
         <v>580</v>
       </c>
       <c r="B581" t="n">
-        <v>2.72762842341963</v>
+        <v>2.72762842341523</v>
       </c>
       <c r="C581" t="n">
         <v>0.589</v>
@@ -6937,7 +6937,7 @@
         <v>581</v>
       </c>
       <c r="B582" t="n">
-        <v>2.72560841078732</v>
+        <v>2.7256084107883</v>
       </c>
       <c r="C582" t="n">
         <v>0.611</v>
@@ -6948,7 +6948,7 @@
         <v>582</v>
       </c>
       <c r="B583" t="n">
-        <v>2.78773422572733</v>
+        <v>2.78773422571442</v>
       </c>
       <c r="C583" t="n">
         <v>0.516</v>
@@ -6970,7 +6970,7 @@
         <v>584</v>
       </c>
       <c r="B585" t="n">
-        <v>3.66917446813457</v>
+        <v>3.66917446836885</v>
       </c>
       <c r="C585" t="n">
         <v>0.391</v>
@@ -6981,7 +6981,7 @@
         <v>585</v>
       </c>
       <c r="B586" t="n">
-        <v>2.03110691956671</v>
+        <v>2.0311069201091</v>
       </c>
       <c r="C586" t="n">
         <v>0.826</v>
@@ -6992,7 +6992,7 @@
         <v>586</v>
       </c>
       <c r="B587" t="n">
-        <v>2.44919319442509</v>
+        <v>2.44919319427207</v>
       </c>
       <c r="C587" t="n">
         <v>0.55</v>
@@ -7003,7 +7003,7 @@
         <v>587</v>
       </c>
       <c r="B588" t="n">
-        <v>1.75964503993666</v>
+        <v>1.75964503994657</v>
       </c>
       <c r="C588" t="n">
         <v>0.862</v>
@@ -7014,7 +7014,7 @@
         <v>588</v>
       </c>
       <c r="B589" t="n">
-        <v>2.49160176938671</v>
+        <v>2.49160176935575</v>
       </c>
       <c r="C589" t="n">
         <v>0.686</v>
@@ -7036,7 +7036,7 @@
         <v>590</v>
       </c>
       <c r="B591" t="n">
-        <v>2.99364088304539</v>
+        <v>2.99364088304583</v>
       </c>
       <c r="C591" t="n">
         <v>0.422</v>
@@ -7047,7 +7047,7 @@
         <v>591</v>
       </c>
       <c r="B592" t="n">
-        <v>4.51253907986974</v>
+        <v>4.51253908004478</v>
       </c>
       <c r="C592" t="n">
         <v>0.233</v>
@@ -7058,7 +7058,7 @@
         <v>592</v>
       </c>
       <c r="B593" t="n">
-        <v>1.08102425463271</v>
+        <v>1.08102425463415</v>
       </c>
       <c r="C593" t="n">
         <v>0.937</v>
@@ -7069,7 +7069,7 @@
         <v>593</v>
       </c>
       <c r="B594" t="n">
-        <v>1.97530990380046</v>
+        <v>1.97530990388747</v>
       </c>
       <c r="C594" t="n">
         <v>0.79</v>
@@ -7080,7 +7080,7 @@
         <v>594</v>
       </c>
       <c r="B595" t="n">
-        <v>1.74418724723142</v>
+        <v>1.74418724732741</v>
       </c>
       <c r="C595" t="n">
         <v>0.863</v>
@@ -7091,7 +7091,7 @@
         <v>595</v>
       </c>
       <c r="B596" t="n">
-        <v>2.00296762152406</v>
+        <v>2.00296762161138</v>
       </c>
       <c r="C596" t="n">
         <v>0.85</v>
@@ -7102,7 +7102,7 @@
         <v>596</v>
       </c>
       <c r="B597" t="n">
-        <v>2.5876840108021</v>
+        <v>2.58768401114254</v>
       </c>
       <c r="C597" t="n">
         <v>0.533</v>
@@ -7113,7 +7113,7 @@
         <v>597</v>
       </c>
       <c r="B598" t="n">
-        <v>2.92911213326794</v>
+        <v>2.92911213326899</v>
       </c>
       <c r="C598" t="n">
         <v>0.57</v>
@@ -7124,7 +7124,7 @@
         <v>598</v>
       </c>
       <c r="B599" t="n">
-        <v>5.1520745221357</v>
+        <v>5.15207452199039</v>
       </c>
       <c r="C599" t="n">
         <v>0.173</v>
@@ -7135,7 +7135,7 @@
         <v>599</v>
       </c>
       <c r="B600" t="n">
-        <v>3.28668882962504</v>
+        <v>3.28668882966886</v>
       </c>
       <c r="C600" t="n">
         <v>0.235</v>
@@ -7146,7 +7146,7 @@
         <v>600</v>
       </c>
       <c r="B601" t="n">
-        <v>1.4651349523752</v>
+        <v>1.46513495237587</v>
       </c>
       <c r="C601" t="n">
         <v>0.894</v>
@@ -7157,7 +7157,7 @@
         <v>601</v>
       </c>
       <c r="B602" t="n">
-        <v>6.12181535761138</v>
+        <v>6.12181535799894</v>
       </c>
       <c r="C602" t="n">
         <v>0.103</v>
@@ -7168,7 +7168,7 @@
         <v>602</v>
       </c>
       <c r="B603" t="n">
-        <v>2.82648142123851</v>
+        <v>2.82648142123378</v>
       </c>
       <c r="C603" t="n">
         <v>0.62</v>
@@ -7179,7 +7179,7 @@
         <v>603</v>
       </c>
       <c r="B604" t="n">
-        <v>1.40930238818118</v>
+        <v>1.40930238858772</v>
       </c>
       <c r="C604" t="n">
         <v>0.893</v>
@@ -7190,7 +7190,7 @@
         <v>604</v>
       </c>
       <c r="B605" t="n">
-        <v>1.39971870415329</v>
+        <v>1.39971870361198</v>
       </c>
       <c r="C605" t="n">
         <v>0.916</v>
@@ -7201,7 +7201,7 @@
         <v>605</v>
       </c>
       <c r="B606" t="n">
-        <v>2.28633928041064</v>
+        <v>2.28633928048765</v>
       </c>
       <c r="C606" t="n">
         <v>0.689</v>
@@ -7212,7 +7212,7 @@
         <v>606</v>
       </c>
       <c r="B607" t="n">
-        <v>1.99993200935697</v>
+        <v>1.99993200935698</v>
       </c>
       <c r="C607" t="n">
         <v>0.894</v>
@@ -7223,7 +7223,7 @@
         <v>607</v>
       </c>
       <c r="B608" t="n">
-        <v>1.45658454265144</v>
+        <v>1.45658454265512</v>
       </c>
       <c r="C608" t="n">
         <v>0.908</v>
@@ -7234,7 +7234,7 @@
         <v>608</v>
       </c>
       <c r="B609" t="n">
-        <v>4.10120217120801</v>
+        <v>4.10120217122254</v>
       </c>
       <c r="C609" t="n">
         <v>0.298</v>
@@ -7245,7 +7245,7 @@
         <v>609</v>
       </c>
       <c r="B610" t="n">
-        <v>2.36396208571362</v>
+        <v>2.36396208575114</v>
       </c>
       <c r="C610" t="n">
         <v>0.46</v>
@@ -7256,7 +7256,7 @@
         <v>610</v>
       </c>
       <c r="B611" t="n">
-        <v>1.51145907145347</v>
+        <v>1.51145907147923</v>
       </c>
       <c r="C611" t="n">
         <v>0.892</v>
@@ -7267,7 +7267,7 @@
         <v>611</v>
       </c>
       <c r="B612" t="n">
-        <v>4.88605064734175</v>
+        <v>4.88605064664525</v>
       </c>
       <c r="C612" t="n">
         <v>0.185</v>
@@ -7278,7 +7278,7 @@
         <v>612</v>
       </c>
       <c r="B613" t="n">
-        <v>1.01352232323555</v>
+        <v>1.01352232306327</v>
       </c>
       <c r="C613" t="n">
         <v>0.965</v>
@@ -7289,7 +7289,7 @@
         <v>613</v>
       </c>
       <c r="B614" t="n">
-        <v>1.999878769953</v>
+        <v>1.99987876995302</v>
       </c>
       <c r="C614" t="n">
         <v>0.923</v>
@@ -7300,7 +7300,7 @@
         <v>614</v>
       </c>
       <c r="B615" t="n">
-        <v>3.26108637725944</v>
+        <v>3.26108637725953</v>
       </c>
       <c r="C615" t="n">
         <v>0.441</v>
@@ -7311,7 +7311,7 @@
         <v>615</v>
       </c>
       <c r="B616" t="n">
-        <v>2.74163918397854</v>
+        <v>2.7416391840143</v>
       </c>
       <c r="C616" t="n">
         <v>0.482</v>
@@ -7322,7 +7322,7 @@
         <v>616</v>
       </c>
       <c r="B617" t="n">
-        <v>2.99690112678261</v>
+        <v>2.99690112678881</v>
       </c>
       <c r="C617" t="n">
         <v>0.748</v>
@@ -7333,7 +7333,7 @@
         <v>617</v>
       </c>
       <c r="B618" t="n">
-        <v>1.18918801909592</v>
+        <v>1.18918801907253</v>
       </c>
       <c r="C618" t="n">
         <v>0.871</v>
@@ -7344,7 +7344,7 @@
         <v>618</v>
       </c>
       <c r="B619" t="n">
-        <v>2.94969611056654</v>
+        <v>2.94969611056567</v>
       </c>
       <c r="C619" t="n">
         <v>0.38</v>
@@ -7355,7 +7355,7 @@
         <v>619</v>
       </c>
       <c r="B620" t="n">
-        <v>2.96532948460948</v>
+        <v>2.96532942820971</v>
       </c>
       <c r="C620" t="n">
         <v>0.515</v>
@@ -7366,7 +7366,7 @@
         <v>620</v>
       </c>
       <c r="B621" t="n">
-        <v>3.74601362654864</v>
+        <v>3.74601362654802</v>
       </c>
       <c r="C621" t="n">
         <v>0.229</v>
@@ -7377,7 +7377,7 @@
         <v>621</v>
       </c>
       <c r="B622" t="n">
-        <v>3.04173890681225</v>
+        <v>3.04173890723832</v>
       </c>
       <c r="C622" t="n">
         <v>0.557</v>
@@ -7388,7 +7388,7 @@
         <v>622</v>
       </c>
       <c r="B623" t="n">
-        <v>2.93674834702019</v>
+        <v>2.93674834698682</v>
       </c>
       <c r="C623" t="n">
         <v>0.473</v>
@@ -7399,7 +7399,7 @@
         <v>623</v>
       </c>
       <c r="B624" t="n">
-        <v>1.06228263370688</v>
+        <v>1.06228263377389</v>
       </c>
       <c r="C624" t="n">
         <v>0.949</v>
@@ -7410,7 +7410,7 @@
         <v>624</v>
       </c>
       <c r="B625" t="n">
-        <v>2.63667894644516</v>
+        <v>2.63667894645189</v>
       </c>
       <c r="C625" t="n">
         <v>0.573</v>
@@ -7421,7 +7421,7 @@
         <v>625</v>
       </c>
       <c r="B626" t="n">
-        <v>3.44911238684603</v>
+        <v>3.44911238601459</v>
       </c>
       <c r="C626" t="n">
         <v>0.354</v>
@@ -7432,7 +7432,7 @@
         <v>626</v>
       </c>
       <c r="B627" t="n">
-        <v>2.77651320922137</v>
+        <v>2.7765132092242</v>
       </c>
       <c r="C627" t="n">
         <v>0.57</v>
@@ -7443,7 +7443,7 @@
         <v>627</v>
       </c>
       <c r="B628" t="n">
-        <v>1.94303463478183</v>
+        <v>1.9430346346915</v>
       </c>
       <c r="C628" t="n">
         <v>0.669</v>
@@ -7454,7 +7454,7 @@
         <v>628</v>
       </c>
       <c r="B629" t="n">
-        <v>3.1238553585961</v>
+        <v>3.12385535856519</v>
       </c>
       <c r="C629" t="n">
         <v>0.437</v>
@@ -7465,7 +7465,7 @@
         <v>629</v>
       </c>
       <c r="B630" t="n">
-        <v>2.79785994248487</v>
+        <v>2.79785994248348</v>
       </c>
       <c r="C630" t="n">
         <v>0.553</v>
@@ -7476,7 +7476,7 @@
         <v>630</v>
       </c>
       <c r="B631" t="n">
-        <v>7.56690148684527</v>
+        <v>7.56690148683878</v>
       </c>
       <c r="C631" t="n">
         <v>0.036</v>
@@ -7487,7 +7487,7 @@
         <v>631</v>
       </c>
       <c r="B632" t="n">
-        <v>2.78316255788307</v>
+        <v>2.78316255843859</v>
       </c>
       <c r="C632" t="n">
         <v>0.573</v>
@@ -7498,7 +7498,7 @@
         <v>632</v>
       </c>
       <c r="B633" t="n">
-        <v>2.2209248775235</v>
+        <v>2.22092487753085</v>
       </c>
       <c r="C633" t="n">
         <v>0.771</v>
@@ -7509,7 +7509,7 @@
         <v>633</v>
       </c>
       <c r="B634" t="n">
-        <v>4.93330656919147</v>
+        <v>4.93330656919587</v>
       </c>
       <c r="C634" t="n">
         <v>0.258</v>
@@ -7520,7 +7520,7 @@
         <v>634</v>
       </c>
       <c r="B635" t="n">
-        <v>1.8070056353813</v>
+        <v>1.80700563540418</v>
       </c>
       <c r="C635" t="n">
         <v>0.748</v>
@@ -7531,7 +7531,7 @@
         <v>635</v>
       </c>
       <c r="B636" t="n">
-        <v>2.30560751804876</v>
+        <v>2.30560751809431</v>
       </c>
       <c r="C636" t="n">
         <v>0.644</v>
@@ -7542,7 +7542,7 @@
         <v>636</v>
       </c>
       <c r="B637" t="n">
-        <v>4.90975931346687</v>
+        <v>4.90975931346881</v>
       </c>
       <c r="C637" t="n">
         <v>0.17</v>
@@ -7553,7 +7553,7 @@
         <v>637</v>
       </c>
       <c r="B638" t="n">
-        <v>2.18350007935979</v>
+        <v>2.18350007928422</v>
       </c>
       <c r="C638" t="n">
         <v>0.701</v>
@@ -7564,7 +7564,7 @@
         <v>638</v>
       </c>
       <c r="B639" t="n">
-        <v>2.22910346500728</v>
+        <v>2.22910346501057</v>
       </c>
       <c r="C639" t="n">
         <v>0.658</v>
@@ -7575,7 +7575,7 @@
         <v>639</v>
       </c>
       <c r="B640" t="n">
-        <v>2.78818351067446</v>
+        <v>2.78818351068692</v>
       </c>
       <c r="C640" t="n">
         <v>0.584</v>
@@ -7586,7 +7586,7 @@
         <v>640</v>
       </c>
       <c r="B641" t="n">
-        <v>4.48158056585245</v>
+        <v>4.48158056564806</v>
       </c>
       <c r="C641" t="n">
         <v>0.26</v>
@@ -7597,7 +7597,7 @@
         <v>641</v>
       </c>
       <c r="B642" t="n">
-        <v>0.99999768868553</v>
+        <v>0.999997688685531</v>
       </c>
       <c r="C642" t="n">
         <v>0.972</v>
@@ -7608,7 +7608,7 @@
         <v>642</v>
       </c>
       <c r="B643" t="n">
-        <v>4.6576244427027</v>
+        <v>4.65762444242538</v>
       </c>
       <c r="C643" t="n">
         <v>0.181</v>
@@ -7619,7 +7619,7 @@
         <v>643</v>
       </c>
       <c r="B644" t="n">
-        <v>3.73876895554474</v>
+        <v>3.73876895553311</v>
       </c>
       <c r="C644" t="n">
         <v>0.49</v>
@@ -7630,7 +7630,7 @@
         <v>644</v>
       </c>
       <c r="B645" t="n">
-        <v>3.35469947904502</v>
+        <v>3.35469947892222</v>
       </c>
       <c r="C645" t="n">
         <v>0.439</v>
@@ -7641,7 +7641,7 @@
         <v>645</v>
       </c>
       <c r="B646" t="n">
-        <v>1.37994810668939</v>
+        <v>1.37994810557079</v>
       </c>
       <c r="C646" t="n">
         <v>0.794</v>
@@ -7652,7 +7652,7 @@
         <v>646</v>
       </c>
       <c r="B647" t="n">
-        <v>2.51758734182759</v>
+        <v>2.51758734178726</v>
       </c>
       <c r="C647" t="n">
         <v>0.684</v>
@@ -7663,7 +7663,7 @@
         <v>647</v>
       </c>
       <c r="B648" t="n">
-        <v>2.46000839554481</v>
+        <v>2.46000839554415</v>
       </c>
       <c r="C648" t="n">
         <v>0.669</v>
@@ -7674,7 +7674,7 @@
         <v>648</v>
       </c>
       <c r="B649" t="n">
-        <v>2.25747744892883</v>
+        <v>2.25747744893427</v>
       </c>
       <c r="C649" t="n">
         <v>0.812</v>
@@ -7685,7 +7685,7 @@
         <v>649</v>
       </c>
       <c r="B650" t="n">
-        <v>2.78419687074257</v>
+        <v>2.78419687082633</v>
       </c>
       <c r="C650" t="n">
         <v>0.577</v>
@@ -7696,7 +7696,7 @@
         <v>650</v>
       </c>
       <c r="B651" t="n">
-        <v>1.99937425862738</v>
+        <v>1.99937425862735</v>
       </c>
       <c r="C651" t="n">
         <v>0.937</v>
@@ -7707,7 +7707,7 @@
         <v>651</v>
       </c>
       <c r="B652" t="n">
-        <v>3.19829670101689</v>
+        <v>3.19829670097345</v>
       </c>
       <c r="C652" t="n">
         <v>0.392</v>
@@ -7718,7 +7718,7 @@
         <v>652</v>
       </c>
       <c r="B653" t="n">
-        <v>2.88665658699082</v>
+        <v>2.8866565869025</v>
       </c>
       <c r="C653" t="n">
         <v>0.448</v>
@@ -7729,7 +7729,7 @@
         <v>653</v>
       </c>
       <c r="B654" t="n">
-        <v>2.80518367821672</v>
+        <v>2.80518367821818</v>
       </c>
       <c r="C654" t="n">
         <v>0.63</v>
@@ -7740,7 +7740,7 @@
         <v>654</v>
       </c>
       <c r="B655" t="n">
-        <v>2.15368327134383</v>
+        <v>2.15368327140879</v>
       </c>
       <c r="C655" t="n">
         <v>0.755</v>
@@ -7751,7 +7751,7 @@
         <v>655</v>
       </c>
       <c r="B656" t="n">
-        <v>3.46134689217364</v>
+        <v>3.46134689214687</v>
       </c>
       <c r="C656" t="n">
         <v>0.301</v>
@@ -7762,7 +7762,7 @@
         <v>656</v>
       </c>
       <c r="B657" t="n">
-        <v>2.55365890926832</v>
+        <v>2.55365890924939</v>
       </c>
       <c r="C657" t="n">
         <v>0.476</v>
@@ -7773,7 +7773,7 @@
         <v>657</v>
       </c>
       <c r="B658" t="n">
-        <v>2.30634583028524</v>
+        <v>2.30634582944715</v>
       </c>
       <c r="C658" t="n">
         <v>0.794</v>
@@ -7795,7 +7795,7 @@
         <v>659</v>
       </c>
       <c r="B660" t="n">
-        <v>2.9628092139449</v>
+        <v>2.96280921395796</v>
       </c>
       <c r="C660" t="n">
         <v>0.439</v>
@@ -7806,7 +7806,7 @@
         <v>660</v>
       </c>
       <c r="B661" t="n">
-        <v>2.58551611270744</v>
+        <v>2.58551611270094</v>
       </c>
       <c r="C661" t="n">
         <v>0.546</v>
@@ -7817,7 +7817,7 @@
         <v>661</v>
       </c>
       <c r="B662" t="n">
-        <v>2.33942170232454</v>
+        <v>2.33942170236988</v>
       </c>
       <c r="C662" t="n">
         <v>0.632</v>
@@ -7828,7 +7828,7 @@
         <v>662</v>
       </c>
       <c r="B663" t="n">
-        <v>2.35073922048986</v>
+        <v>2.35073922052196</v>
       </c>
       <c r="C663" t="n">
         <v>0.502</v>
@@ -7850,7 +7850,7 @@
         <v>664</v>
       </c>
       <c r="B665" t="n">
-        <v>3.07624720174045</v>
+        <v>3.07624720176732</v>
       </c>
       <c r="C665" t="n">
         <v>0.491</v>
@@ -7861,7 +7861,7 @@
         <v>665</v>
       </c>
       <c r="B666" t="n">
-        <v>2.78544647059237</v>
+        <v>2.78544647060274</v>
       </c>
       <c r="C666" t="n">
         <v>0.504</v>
@@ -7872,7 +7872,7 @@
         <v>666</v>
       </c>
       <c r="B667" t="n">
-        <v>1.7442557594538</v>
+        <v>1.7442557594497</v>
       </c>
       <c r="C667" t="n">
         <v>0.718</v>
@@ -7883,7 +7883,7 @@
         <v>667</v>
       </c>
       <c r="B668" t="n">
-        <v>8.08728418567244</v>
+        <v>8.08728418569896</v>
       </c>
       <c r="C668" t="n">
         <v>0.02</v>
@@ -7894,7 +7894,7 @@
         <v>668</v>
       </c>
       <c r="B669" t="n">
-        <v>2.13361935379687</v>
+        <v>2.13361935379821</v>
       </c>
       <c r="C669" t="n">
         <v>0.823</v>
@@ -7905,7 +7905,7 @@
         <v>669</v>
       </c>
       <c r="B670" t="n">
-        <v>3.09610062091212</v>
+        <v>3.09610062520258</v>
       </c>
       <c r="C670" t="n">
         <v>0.408</v>
@@ -7916,7 +7916,7 @@
         <v>670</v>
       </c>
       <c r="B671" t="n">
-        <v>5.63107751497918</v>
+        <v>5.63107751498959</v>
       </c>
       <c r="C671" t="n">
         <v>0.125</v>
@@ -7927,7 +7927,7 @@
         <v>671</v>
       </c>
       <c r="B672" t="n">
-        <v>4.87164167581613</v>
+        <v>4.87164167582207</v>
       </c>
       <c r="C672" t="n">
         <v>0.183</v>
@@ -7938,7 +7938,7 @@
         <v>672</v>
       </c>
       <c r="B673" t="n">
-        <v>4.93921360926632</v>
+        <v>4.93921360934489</v>
       </c>
       <c r="C673" t="n">
         <v>0.314</v>
@@ -7949,7 +7949,7 @@
         <v>673</v>
       </c>
       <c r="B674" t="n">
-        <v>2.90138452378685</v>
+        <v>2.90138452377513</v>
       </c>
       <c r="C674" t="n">
         <v>0.506</v>
@@ -7960,7 +7960,7 @@
         <v>674</v>
       </c>
       <c r="B675" t="n">
-        <v>3.41500843900182</v>
+        <v>3.41500843904919</v>
       </c>
       <c r="C675" t="n">
         <v>0.467</v>
@@ -7971,7 +7971,7 @@
         <v>675</v>
       </c>
       <c r="B676" t="n">
-        <v>2.72492711330033</v>
+        <v>2.7249271132482</v>
       </c>
       <c r="C676" t="n">
         <v>0.596</v>
@@ -7982,7 +7982,7 @@
         <v>676</v>
       </c>
       <c r="B677" t="n">
-        <v>4.66867992308109</v>
+        <v>4.66867992308258</v>
       </c>
       <c r="C677" t="n">
         <v>0.235</v>
@@ -7993,7 +7993,7 @@
         <v>677</v>
       </c>
       <c r="B678" t="n">
-        <v>2.54863486695701</v>
+        <v>2.54863486695686</v>
       </c>
       <c r="C678" t="n">
         <v>0.582</v>
@@ -8004,7 +8004,7 @@
         <v>678</v>
       </c>
       <c r="B679" t="n">
-        <v>1.68846929584329</v>
+        <v>1.68846929585403</v>
       </c>
       <c r="C679" t="n">
         <v>0.933</v>
@@ -8015,7 +8015,7 @@
         <v>679</v>
       </c>
       <c r="B680" t="n">
-        <v>6.21452998695886</v>
+        <v>6.21452998718578</v>
       </c>
       <c r="C680" t="n">
         <v>0.086</v>
@@ -8026,7 +8026,7 @@
         <v>680</v>
       </c>
       <c r="B681" t="n">
-        <v>5.80030543630704</v>
+        <v>5.80030543629947</v>
       </c>
       <c r="C681" t="n">
         <v>0.167</v>
@@ -8037,7 +8037,7 @@
         <v>681</v>
       </c>
       <c r="B682" t="n">
-        <v>4.38149078699417</v>
+        <v>4.38149078883998</v>
       </c>
       <c r="C682" t="n">
         <v>0.274</v>
@@ -8048,7 +8048,7 @@
         <v>682</v>
       </c>
       <c r="B683" t="n">
-        <v>1.64149507714109</v>
+        <v>1.64149507719517</v>
       </c>
       <c r="C683" t="n">
         <v>0.864</v>
@@ -8059,7 +8059,7 @@
         <v>683</v>
       </c>
       <c r="B684" t="n">
-        <v>4.70505758961836</v>
+        <v>4.7050575896736</v>
       </c>
       <c r="C684" t="n">
         <v>0.152</v>
@@ -8070,7 +8070,7 @@
         <v>684</v>
       </c>
       <c r="B685" t="n">
-        <v>2.14277148718329</v>
+        <v>2.1427714872116</v>
       </c>
       <c r="C685" t="n">
         <v>0.747</v>
@@ -8081,7 +8081,7 @@
         <v>685</v>
       </c>
       <c r="B686" t="n">
-        <v>5.13202798368219</v>
+        <v>5.13202798329314</v>
       </c>
       <c r="C686" t="n">
         <v>0.134</v>
@@ -8092,7 +8092,7 @@
         <v>686</v>
       </c>
       <c r="B687" t="n">
-        <v>2.07308655631978</v>
+        <v>2.07308655645648</v>
       </c>
       <c r="C687" t="n">
         <v>0.813</v>
@@ -8103,7 +8103,7 @@
         <v>687</v>
       </c>
       <c r="B688" t="n">
-        <v>3.7103521992522</v>
+        <v>3.71035219924981</v>
       </c>
       <c r="C688" t="n">
         <v>0.373</v>
@@ -8114,7 +8114,7 @@
         <v>688</v>
       </c>
       <c r="B689" t="n">
-        <v>3.4594154920354</v>
+        <v>3.45941549201856</v>
       </c>
       <c r="C689" t="n">
         <v>0.379</v>
@@ -8125,7 +8125,7 @@
         <v>689</v>
       </c>
       <c r="B690" t="n">
-        <v>2.23427738177494</v>
+        <v>2.23427738177898</v>
       </c>
       <c r="C690" t="n">
         <v>0.618</v>
@@ -8136,7 +8136,7 @@
         <v>690</v>
       </c>
       <c r="B691" t="n">
-        <v>2.13167030120264</v>
+        <v>2.13167030116434</v>
       </c>
       <c r="C691" t="n">
         <v>0.737</v>
@@ -8147,7 +8147,7 @@
         <v>691</v>
       </c>
       <c r="B692" t="n">
-        <v>4.17142139152684</v>
+        <v>4.17142139149555</v>
       </c>
       <c r="C692" t="n">
         <v>0.33</v>
@@ -8158,7 +8158,7 @@
         <v>692</v>
       </c>
       <c r="B693" t="n">
-        <v>1.99855186681089</v>
+        <v>1.99855186681046</v>
       </c>
       <c r="C693" t="n">
         <v>0.958</v>
@@ -8169,7 +8169,7 @@
         <v>693</v>
       </c>
       <c r="B694" t="n">
-        <v>2.82051172450883</v>
+        <v>2.82051172425191</v>
       </c>
       <c r="C694" t="n">
         <v>0.57</v>
@@ -8180,7 +8180,7 @@
         <v>694</v>
       </c>
       <c r="B695" t="n">
-        <v>2.66513161739759</v>
+        <v>2.66513161754398</v>
       </c>
       <c r="C695" t="n">
         <v>0.63</v>
@@ -8202,7 +8202,7 @@
         <v>696</v>
       </c>
       <c r="B697" t="n">
-        <v>1.00699898577614</v>
+        <v>1.00699898569381</v>
       </c>
       <c r="C697" t="n">
         <v>0.929</v>
@@ -8213,7 +8213,7 @@
         <v>697</v>
       </c>
       <c r="B698" t="n">
-        <v>3.26968228614488</v>
+        <v>3.26968228614641</v>
       </c>
       <c r="C698" t="n">
         <v>0.416</v>
@@ -8224,7 +8224,7 @@
         <v>698</v>
       </c>
       <c r="B699" t="n">
-        <v>8.23703570389715</v>
+        <v>8.23703570350796</v>
       </c>
       <c r="C699" t="n">
         <v>0.027</v>
@@ -8235,7 +8235,7 @@
         <v>699</v>
       </c>
       <c r="B700" t="n">
-        <v>3.69008366046911</v>
+        <v>3.69008366055888</v>
       </c>
       <c r="C700" t="n">
         <v>0.607</v>
@@ -8246,7 +8246,7 @@
         <v>700</v>
       </c>
       <c r="B701" t="n">
-        <v>2.63941399106383</v>
+        <v>2.63941399116212</v>
       </c>
       <c r="C701" t="n">
         <v>0.478</v>
@@ -8268,7 +8268,7 @@
         <v>702</v>
       </c>
       <c r="B703" t="n">
-        <v>2.60248119608904</v>
+        <v>2.6024811960948</v>
       </c>
       <c r="C703" t="n">
         <v>0.559</v>
@@ -8279,7 +8279,7 @@
         <v>703</v>
       </c>
       <c r="B704" t="n">
-        <v>3.41571390627399</v>
+        <v>3.41571390624633</v>
       </c>
       <c r="C704" t="n">
         <v>0.461</v>
@@ -8290,7 +8290,7 @@
         <v>704</v>
       </c>
       <c r="B705" t="n">
-        <v>3.34891274388232</v>
+        <v>3.34891274388331</v>
       </c>
       <c r="C705" t="n">
         <v>0.366</v>
@@ -8301,7 +8301,7 @@
         <v>705</v>
       </c>
       <c r="B706" t="n">
-        <v>2.0983936193776</v>
+        <v>2.09839361939543</v>
       </c>
       <c r="C706" t="n">
         <v>0.79</v>
@@ -8312,7 +8312,7 @@
         <v>706</v>
       </c>
       <c r="B707" t="n">
-        <v>2.50622166829298</v>
+        <v>2.50622166834763</v>
       </c>
       <c r="C707" t="n">
         <v>0.657</v>
@@ -8323,7 +8323,7 @@
         <v>707</v>
       </c>
       <c r="B708" t="n">
-        <v>2.30656152840709</v>
+        <v>2.30656152842499</v>
       </c>
       <c r="C708" t="n">
         <v>0.725</v>
@@ -8334,7 +8334,7 @@
         <v>708</v>
       </c>
       <c r="B709" t="n">
-        <v>4.9802859894901</v>
+        <v>4.98028598954767</v>
       </c>
       <c r="C709" t="n">
         <v>0.185</v>
@@ -8345,7 +8345,7 @@
         <v>709</v>
       </c>
       <c r="B710" t="n">
-        <v>2.02746757110046</v>
+        <v>2.02746757112529</v>
       </c>
       <c r="C710" t="n">
         <v>0.693</v>
@@ -8356,7 +8356,7 @@
         <v>710</v>
       </c>
       <c r="B711" t="n">
-        <v>2.06595657852644</v>
+        <v>2.06595657852429</v>
       </c>
       <c r="C711" t="n">
         <v>0.742</v>
@@ -8367,7 +8367,7 @@
         <v>711</v>
       </c>
       <c r="B712" t="n">
-        <v>3.77466982472211</v>
+        <v>3.77466982459711</v>
       </c>
       <c r="C712" t="n">
         <v>0.3</v>
@@ -8378,7 +8378,7 @@
         <v>712</v>
       </c>
       <c r="B713" t="n">
-        <v>3.23635142831647</v>
+        <v>3.23635142653722</v>
       </c>
       <c r="C713" t="n">
         <v>0.576</v>
@@ -8389,7 +8389,7 @@
         <v>713</v>
       </c>
       <c r="B714" t="n">
-        <v>3.68170543457681</v>
+        <v>3.6817054341017</v>
       </c>
       <c r="C714" t="n">
         <v>0.335</v>
@@ -8400,7 +8400,7 @@
         <v>714</v>
       </c>
       <c r="B715" t="n">
-        <v>3.00634272684515</v>
+        <v>3.00634272711301</v>
       </c>
       <c r="C715" t="n">
         <v>0.439</v>
@@ -8411,7 +8411,7 @@
         <v>715</v>
       </c>
       <c r="B716" t="n">
-        <v>4.08781491737705</v>
+        <v>4.0878149173097</v>
       </c>
       <c r="C716" t="n">
         <v>0.211</v>
@@ -8422,7 +8422,7 @@
         <v>716</v>
       </c>
       <c r="B717" t="n">
-        <v>3.40164456977192</v>
+        <v>3.40164456997638</v>
       </c>
       <c r="C717" t="n">
         <v>0.311</v>
@@ -8433,7 +8433,7 @@
         <v>717</v>
       </c>
       <c r="B718" t="n">
-        <v>2.09865203190548</v>
+        <v>2.09865203197771</v>
       </c>
       <c r="C718" t="n">
         <v>0.67</v>
@@ -8444,7 +8444,7 @@
         <v>718</v>
       </c>
       <c r="B719" t="n">
-        <v>2.6668621524946</v>
+        <v>2.66686215251223</v>
       </c>
       <c r="C719" t="n">
         <v>0.51</v>
@@ -8455,7 +8455,7 @@
         <v>719</v>
       </c>
       <c r="B720" t="n">
-        <v>3.2512275420495</v>
+        <v>3.25122754204626</v>
       </c>
       <c r="C720" t="n">
         <v>0.451</v>
@@ -8466,7 +8466,7 @@
         <v>720</v>
       </c>
       <c r="B721" t="n">
-        <v>6.36288699177693</v>
+        <v>6.36288699034773</v>
       </c>
       <c r="C721" t="n">
         <v>0.056</v>
@@ -8477,7 +8477,7 @@
         <v>721</v>
       </c>
       <c r="B722" t="n">
-        <v>3.74399552800702</v>
+        <v>3.74399552800852</v>
       </c>
       <c r="C722" t="n">
         <v>0.4</v>
@@ -8488,7 +8488,7 @@
         <v>722</v>
       </c>
       <c r="B723" t="n">
-        <v>5.66289370370324</v>
+        <v>5.6628937019372</v>
       </c>
       <c r="C723" t="n">
         <v>0.137</v>
@@ -8499,7 +8499,7 @@
         <v>723</v>
       </c>
       <c r="B724" t="n">
-        <v>5.51789674950936</v>
+        <v>5.51789674942002</v>
       </c>
       <c r="C724" t="n">
         <v>0.106</v>
@@ -8510,7 +8510,7 @@
         <v>724</v>
       </c>
       <c r="B725" t="n">
-        <v>2.15968477127312</v>
+        <v>2.15968477122822</v>
       </c>
       <c r="C725" t="n">
         <v>0.707</v>
@@ -8521,7 +8521,7 @@
         <v>725</v>
       </c>
       <c r="B726" t="n">
-        <v>1.99995829569907</v>
+        <v>1.99995829569908</v>
       </c>
       <c r="C726" t="n">
         <v>0.913</v>
@@ -8532,7 +8532,7 @@
         <v>726</v>
       </c>
       <c r="B727" t="n">
-        <v>7.0971335228162</v>
+        <v>7.0971335224381</v>
       </c>
       <c r="C727" t="n">
         <v>0.049</v>
@@ -8543,7 +8543,7 @@
         <v>727</v>
       </c>
       <c r="B728" t="n">
-        <v>6.91830923090182</v>
+        <v>6.91830923087642</v>
       </c>
       <c r="C728" t="n">
         <v>0.034</v>
@@ -8565,7 +8565,7 @@
         <v>729</v>
       </c>
       <c r="B730" t="n">
-        <v>2.95621209912242</v>
+        <v>2.95621209911883</v>
       </c>
       <c r="C730" t="n">
         <v>0.561</v>
@@ -8576,7 +8576,7 @@
         <v>730</v>
       </c>
       <c r="B731" t="n">
-        <v>2.99000852779529</v>
+        <v>2.99000852779523</v>
       </c>
       <c r="C731" t="n">
         <v>0.358</v>
@@ -8587,7 +8587,7 @@
         <v>731</v>
       </c>
       <c r="B732" t="n">
-        <v>3.69130488704224</v>
+        <v>3.69130488705442</v>
       </c>
       <c r="C732" t="n">
         <v>0.32</v>
@@ -8598,7 +8598,7 @@
         <v>732</v>
       </c>
       <c r="B733" t="n">
-        <v>3.93842999895328</v>
+        <v>3.93842999888788</v>
       </c>
       <c r="C733" t="n">
         <v>0.268</v>
@@ -8609,7 +8609,7 @@
         <v>733</v>
       </c>
       <c r="B734" t="n">
-        <v>3.06639183528024</v>
+        <v>3.06639183531983</v>
       </c>
       <c r="C734" t="n">
         <v>0.464</v>
@@ -8620,7 +8620,7 @@
         <v>734</v>
       </c>
       <c r="B735" t="n">
-        <v>1.83885622690272</v>
+        <v>1.83885622693507</v>
       </c>
       <c r="C735" t="n">
         <v>0.652</v>
@@ -8631,7 +8631,7 @@
         <v>735</v>
       </c>
       <c r="B736" t="n">
-        <v>5.82157377575355</v>
+        <v>5.82157377617257</v>
       </c>
       <c r="C736" t="n">
         <v>0.149</v>
@@ -8642,7 +8642,7 @@
         <v>736</v>
       </c>
       <c r="B737" t="n">
-        <v>4.01500599503268</v>
+        <v>4.01500599504532</v>
       </c>
       <c r="C737" t="n">
         <v>0.156</v>
@@ -8653,7 +8653,7 @@
         <v>737</v>
       </c>
       <c r="B738" t="n">
-        <v>2.14683409979542</v>
+        <v>2.14683409976971</v>
       </c>
       <c r="C738" t="n">
         <v>0.671</v>
@@ -8664,7 +8664,7 @@
         <v>738</v>
       </c>
       <c r="B739" t="n">
-        <v>4.14267992972973</v>
+        <v>4.14267992973645</v>
       </c>
       <c r="C739" t="n">
         <v>0.335</v>
@@ -8675,7 +8675,7 @@
         <v>739</v>
       </c>
       <c r="B740" t="n">
-        <v>3.7073719414883</v>
+        <v>3.70737194149822</v>
       </c>
       <c r="C740" t="n">
         <v>0.362</v>
@@ -8686,7 +8686,7 @@
         <v>740</v>
       </c>
       <c r="B741" t="n">
-        <v>3.63495340385551</v>
+        <v>3.63495340387165</v>
       </c>
       <c r="C741" t="n">
         <v>0.255</v>
@@ -8697,7 +8697,7 @@
         <v>741</v>
       </c>
       <c r="B742" t="n">
-        <v>3.23148804461182</v>
+        <v>3.2314880446131</v>
       </c>
       <c r="C742" t="n">
         <v>0.399</v>
@@ -8708,7 +8708,7 @@
         <v>742</v>
       </c>
       <c r="B743" t="n">
-        <v>2.67893149446335</v>
+        <v>2.67893149446631</v>
       </c>
       <c r="C743" t="n">
         <v>0.632</v>
@@ -8719,7 +8719,7 @@
         <v>743</v>
       </c>
       <c r="B744" t="n">
-        <v>2.127676203066</v>
+        <v>2.12767620305763</v>
       </c>
       <c r="C744" t="n">
         <v>0.794</v>
@@ -8741,7 +8741,7 @@
         <v>745</v>
       </c>
       <c r="B746" t="n">
-        <v>1.27574928998599</v>
+        <v>1.27574929000653</v>
       </c>
       <c r="C746" t="n">
         <v>0.967</v>
@@ -8752,7 +8752,7 @@
         <v>746</v>
       </c>
       <c r="B747" t="n">
-        <v>7.6963990558637</v>
+        <v>7.69639905590108</v>
       </c>
       <c r="C747" t="n">
         <v>0.071</v>
@@ -8763,7 +8763,7 @@
         <v>747</v>
       </c>
       <c r="B748" t="n">
-        <v>1.33804462728977</v>
+        <v>1.33804462727902</v>
       </c>
       <c r="C748" t="n">
         <v>0.881</v>
@@ -8774,7 +8774,7 @@
         <v>748</v>
       </c>
       <c r="B749" t="n">
-        <v>2.88537270371338</v>
+        <v>2.88537270362548</v>
       </c>
       <c r="C749" t="n">
         <v>0.536</v>
@@ -8796,7 +8796,7 @@
         <v>750</v>
       </c>
       <c r="B751" t="n">
-        <v>2.82992245469788</v>
+        <v>2.82992245490984</v>
       </c>
       <c r="C751" t="n">
         <v>0.659</v>
@@ -8807,7 +8807,7 @@
         <v>751</v>
       </c>
       <c r="B752" t="n">
-        <v>0.999988942046927</v>
+        <v>0.999988942046926</v>
       </c>
       <c r="C752" t="n">
         <v>0.982</v>
@@ -8818,7 +8818,7 @@
         <v>752</v>
       </c>
       <c r="B753" t="n">
-        <v>2.99447583183525</v>
+        <v>2.99447583181247</v>
       </c>
       <c r="C753" t="n">
         <v>0.474</v>
@@ -8829,7 +8829,7 @@
         <v>753</v>
       </c>
       <c r="B754" t="n">
-        <v>2.62101742710924</v>
+        <v>2.621017427117</v>
       </c>
       <c r="C754" t="n">
         <v>0.487</v>
@@ -8840,7 +8840,7 @@
         <v>754</v>
       </c>
       <c r="B755" t="n">
-        <v>1.27516457116459</v>
+        <v>1.27516457108313</v>
       </c>
       <c r="C755" t="n">
         <v>0.906</v>
@@ -8862,7 +8862,7 @@
         <v>756</v>
       </c>
       <c r="B757" t="n">
-        <v>5.09091465508468</v>
+        <v>5.09091465489557</v>
       </c>
       <c r="C757" t="n">
         <v>0.258</v>
@@ -8873,7 +8873,7 @@
         <v>757</v>
       </c>
       <c r="B758" t="n">
-        <v>3.48882679016957</v>
+        <v>3.48882679015372</v>
       </c>
       <c r="C758" t="n">
         <v>0.255</v>
@@ -8884,7 +8884,7 @@
         <v>758</v>
       </c>
       <c r="B759" t="n">
-        <v>1.44981164898417</v>
+        <v>1.44981164888605</v>
       </c>
       <c r="C759" t="n">
         <v>0.897</v>
@@ -8895,7 +8895,7 @@
         <v>759</v>
       </c>
       <c r="B760" t="n">
-        <v>2.73541085980886</v>
+        <v>2.73541086343761</v>
       </c>
       <c r="C760" t="n">
         <v>0.701</v>
@@ -8906,7 +8906,7 @@
         <v>760</v>
       </c>
       <c r="B761" t="n">
-        <v>4.26460950765782</v>
+        <v>4.26460950767713</v>
       </c>
       <c r="C761" t="n">
         <v>0.254</v>
@@ -8928,7 +8928,7 @@
         <v>762</v>
       </c>
       <c r="B763" t="n">
-        <v>2.66135652053053</v>
+        <v>2.66135652055497</v>
       </c>
       <c r="C763" t="n">
         <v>0.63</v>
@@ -8939,7 +8939,7 @@
         <v>763</v>
       </c>
       <c r="B764" t="n">
-        <v>4.330338903765</v>
+        <v>4.33033890383814</v>
       </c>
       <c r="C764" t="n">
         <v>0.312</v>
@@ -8950,7 +8950,7 @@
         <v>764</v>
       </c>
       <c r="B765" t="n">
-        <v>2.20936422091606</v>
+        <v>2.20936422091817</v>
       </c>
       <c r="C765" t="n">
         <v>0.66</v>
@@ -8961,7 +8961,7 @@
         <v>765</v>
       </c>
       <c r="B766" t="n">
-        <v>3.55160253712347</v>
+        <v>3.55160253703032</v>
       </c>
       <c r="C766" t="n">
         <v>0.403</v>
@@ -8972,7 +8972,7 @@
         <v>766</v>
       </c>
       <c r="B767" t="n">
-        <v>3.70944079160535</v>
+        <v>3.70944079216751</v>
       </c>
       <c r="C767" t="n">
         <v>0.372</v>
@@ -8983,7 +8983,7 @@
         <v>767</v>
       </c>
       <c r="B768" t="n">
-        <v>1.84720992608203</v>
+        <v>1.84720992604761</v>
       </c>
       <c r="C768" t="n">
         <v>0.776</v>
@@ -8994,7 +8994,7 @@
         <v>768</v>
       </c>
       <c r="B769" t="n">
-        <v>6.31728162272196</v>
+        <v>6.31728162277682</v>
       </c>
       <c r="C769" t="n">
         <v>0.038</v>
@@ -9005,7 +9005,7 @@
         <v>769</v>
       </c>
       <c r="B770" t="n">
-        <v>4.58453033215426</v>
+        <v>4.58453033214402</v>
       </c>
       <c r="C770" t="n">
         <v>0.219</v>
@@ -9016,7 +9016,7 @@
         <v>770</v>
       </c>
       <c r="B771" t="n">
-        <v>4.09030660277995</v>
+        <v>4.09030660276318</v>
       </c>
       <c r="C771" t="n">
         <v>0.278</v>
@@ -9027,7 +9027,7 @@
         <v>771</v>
       </c>
       <c r="B772" t="n">
-        <v>15.339616964924</v>
+        <v>15.3396169648603</v>
       </c>
       <c r="C772" t="n">
         <v>0</v>
@@ -9038,7 +9038,7 @@
         <v>772</v>
       </c>
       <c r="B773" t="n">
-        <v>2.48240791087034</v>
+        <v>2.48240790457403</v>
       </c>
       <c r="C773" t="n">
         <v>0.568</v>
@@ -9049,7 +9049,7 @@
         <v>773</v>
       </c>
       <c r="B774" t="n">
-        <v>3.88323943878544</v>
+        <v>3.88323943850154</v>
       </c>
       <c r="C774" t="n">
         <v>0.245</v>
@@ -9060,7 +9060,7 @@
         <v>774</v>
       </c>
       <c r="B775" t="n">
-        <v>1.0782746933884</v>
+        <v>1.07827469353707</v>
       </c>
       <c r="C775" t="n">
         <v>0.947</v>
@@ -9071,7 +9071,7 @@
         <v>775</v>
       </c>
       <c r="B776" t="n">
-        <v>1.3483752669583</v>
+        <v>1.34837526695961</v>
       </c>
       <c r="C776" t="n">
         <v>0.957</v>
@@ -9082,7 +9082,7 @@
         <v>776</v>
       </c>
       <c r="B777" t="n">
-        <v>1.11290513966562</v>
+        <v>1.11290513966898</v>
       </c>
       <c r="C777" t="n">
         <v>0.956</v>
@@ -9093,7 +9093,7 @@
         <v>777</v>
       </c>
       <c r="B778" t="n">
-        <v>2.34714573295756</v>
+        <v>2.34714573295439</v>
       </c>
       <c r="C778" t="n">
         <v>0.713</v>
@@ -9104,7 +9104,7 @@
         <v>778</v>
       </c>
       <c r="B779" t="n">
-        <v>2.80591901810721</v>
+        <v>2.8059190181836</v>
       </c>
       <c r="C779" t="n">
         <v>0.461</v>
@@ -9115,7 +9115,7 @@
         <v>779</v>
       </c>
       <c r="B780" t="n">
-        <v>2.67839804537336</v>
+        <v>2.67839804533819</v>
       </c>
       <c r="C780" t="n">
         <v>0.68</v>
@@ -9126,7 +9126,7 @@
         <v>780</v>
       </c>
       <c r="B781" t="n">
-        <v>1.65098711374777</v>
+        <v>1.65098711392455</v>
       </c>
       <c r="C781" t="n">
         <v>0.883</v>
@@ -9137,7 +9137,7 @@
         <v>781</v>
       </c>
       <c r="B782" t="n">
-        <v>1.69754016881473</v>
+        <v>1.69754016871235</v>
       </c>
       <c r="C782" t="n">
         <v>0.93</v>
@@ -9148,7 +9148,7 @@
         <v>782</v>
       </c>
       <c r="B783" t="n">
-        <v>3.86699425101915</v>
+        <v>3.86699425102989</v>
       </c>
       <c r="C783" t="n">
         <v>0.28</v>
@@ -9159,7 +9159,7 @@
         <v>783</v>
       </c>
       <c r="B784" t="n">
-        <v>4.04462279998584</v>
+        <v>4.04462279990239</v>
       </c>
       <c r="C784" t="n">
         <v>0.317</v>
@@ -9170,7 +9170,7 @@
         <v>784</v>
       </c>
       <c r="B785" t="n">
-        <v>3.40220259089563</v>
+        <v>3.40220259093962</v>
       </c>
       <c r="C785" t="n">
         <v>0.466</v>
@@ -9181,7 +9181,7 @@
         <v>785</v>
       </c>
       <c r="B786" t="n">
-        <v>4.60597503256866</v>
+        <v>4.60597503260405</v>
       </c>
       <c r="C786" t="n">
         <v>0.272</v>
@@ -9192,7 +9192,7 @@
         <v>786</v>
       </c>
       <c r="B787" t="n">
-        <v>3.25870417109892</v>
+        <v>3.25870417168685</v>
       </c>
       <c r="C787" t="n">
         <v>0.379</v>
@@ -9203,7 +9203,7 @@
         <v>787</v>
       </c>
       <c r="B788" t="n">
-        <v>2.37906431098279</v>
+        <v>2.37906431095199</v>
       </c>
       <c r="C788" t="n">
         <v>0.638</v>
@@ -9214,7 +9214,7 @@
         <v>788</v>
       </c>
       <c r="B789" t="n">
-        <v>5.28440364894771</v>
+        <v>5.2844036490666</v>
       </c>
       <c r="C789" t="n">
         <v>0.156</v>
@@ -9225,7 +9225,7 @@
         <v>789</v>
       </c>
       <c r="B790" t="n">
-        <v>10.5391536060378</v>
+        <v>10.539153605842</v>
       </c>
       <c r="C790" t="n">
         <v>0.004</v>
@@ -9247,7 +9247,7 @@
         <v>791</v>
       </c>
       <c r="B792" t="n">
-        <v>2.9752858188899</v>
+        <v>2.97528581888897</v>
       </c>
       <c r="C792" t="n">
         <v>0.594</v>
@@ -9258,7 +9258,7 @@
         <v>792</v>
       </c>
       <c r="B793" t="n">
-        <v>2.20599181684299</v>
+        <v>2.20599181686718</v>
       </c>
       <c r="C793" t="n">
         <v>0.768</v>
@@ -9269,7 +9269,7 @@
         <v>793</v>
       </c>
       <c r="B794" t="n">
-        <v>3.4202693183779</v>
+        <v>3.42026931825739</v>
       </c>
       <c r="C794" t="n">
         <v>0.32</v>
@@ -9280,7 +9280,7 @@
         <v>794</v>
       </c>
       <c r="B795" t="n">
-        <v>2.40905562684034</v>
+        <v>2.40905562678557</v>
       </c>
       <c r="C795" t="n">
         <v>0.539</v>
@@ -9291,7 +9291,7 @@
         <v>795</v>
       </c>
       <c r="B796" t="n">
-        <v>3.24561722845073</v>
+        <v>3.24561722846118</v>
       </c>
       <c r="C796" t="n">
         <v>0.439</v>
@@ -9302,7 +9302,7 @@
         <v>796</v>
       </c>
       <c r="B797" t="n">
-        <v>6.83676228277876</v>
+        <v>6.83676228279719</v>
       </c>
       <c r="C797" t="n">
         <v>0.029</v>
@@ -9313,7 +9313,7 @@
         <v>797</v>
       </c>
       <c r="B798" t="n">
-        <v>3.85965580811923</v>
+        <v>3.85965580834042</v>
       </c>
       <c r="C798" t="n">
         <v>0.35</v>
@@ -9324,7 +9324,7 @@
         <v>798</v>
       </c>
       <c r="B799" t="n">
-        <v>5.03356181296601</v>
+        <v>5.03356181302185</v>
       </c>
       <c r="C799" t="n">
         <v>0.216</v>
@@ -9335,7 +9335,7 @@
         <v>799</v>
       </c>
       <c r="B800" t="n">
-        <v>2.84151438250913</v>
+        <v>2.84151438196819</v>
       </c>
       <c r="C800" t="n">
         <v>0.562</v>
@@ -9346,7 +9346,7 @@
         <v>800</v>
       </c>
       <c r="B801" t="n">
-        <v>4.26948801570349</v>
+        <v>4.26948801568471</v>
       </c>
       <c r="C801" t="n">
         <v>0.279</v>
@@ -9357,7 +9357,7 @@
         <v>801</v>
       </c>
       <c r="B802" t="n">
-        <v>2.65701352613492</v>
+        <v>2.65701352613645</v>
       </c>
       <c r="C802" t="n">
         <v>0.685</v>
@@ -9368,7 +9368,7 @@
         <v>802</v>
       </c>
       <c r="B803" t="n">
-        <v>3.48452036786987</v>
+        <v>3.48452036786985</v>
       </c>
       <c r="C803" t="n">
         <v>0.32</v>
@@ -9379,7 +9379,7 @@
         <v>803</v>
       </c>
       <c r="B804" t="n">
-        <v>4.54985360624793</v>
+        <v>4.54985360646501</v>
       </c>
       <c r="C804" t="n">
         <v>0.251</v>
@@ -9390,7 +9390,7 @@
         <v>804</v>
       </c>
       <c r="B805" t="n">
-        <v>4.20176445403239</v>
+        <v>4.20176445415893</v>
       </c>
       <c r="C805" t="n">
         <v>0.238</v>
@@ -9401,7 +9401,7 @@
         <v>805</v>
       </c>
       <c r="B806" t="n">
-        <v>2.12150571572506</v>
+        <v>2.12150571572109</v>
       </c>
       <c r="C806" t="n">
         <v>0.644</v>
@@ -9412,7 +9412,7 @@
         <v>806</v>
       </c>
       <c r="B807" t="n">
-        <v>5.53711957475789</v>
+        <v>5.53711957480005</v>
       </c>
       <c r="C807" t="n">
         <v>0.141</v>
@@ -9423,7 +9423,7 @@
         <v>807</v>
       </c>
       <c r="B808" t="n">
-        <v>4.29599850365971</v>
+        <v>4.29599850363139</v>
       </c>
       <c r="C808" t="n">
         <v>0.233</v>
@@ -9434,7 +9434,7 @@
         <v>808</v>
       </c>
       <c r="B809" t="n">
-        <v>2.74138120988241</v>
+        <v>2.74138120987666</v>
       </c>
       <c r="C809" t="n">
         <v>0.644</v>
@@ -9445,7 +9445,7 @@
         <v>809</v>
       </c>
       <c r="B810" t="n">
-        <v>7.65820213170108</v>
+        <v>7.65820213165476</v>
       </c>
       <c r="C810" t="n">
         <v>0.023</v>
@@ -9456,7 +9456,7 @@
         <v>810</v>
       </c>
       <c r="B811" t="n">
-        <v>3.27982970951231</v>
+        <v>3.27982970965715</v>
       </c>
       <c r="C811" t="n">
         <v>0.451</v>
@@ -9467,7 +9467,7 @@
         <v>811</v>
       </c>
       <c r="B812" t="n">
-        <v>1.68272398709464</v>
+        <v>1.68272398706906</v>
       </c>
       <c r="C812" t="n">
         <v>0.809</v>
@@ -9478,7 +9478,7 @@
         <v>812</v>
       </c>
       <c r="B813" t="n">
-        <v>4.96095779764023</v>
+        <v>4.96095779764699</v>
       </c>
       <c r="C813" t="n">
         <v>0.15</v>
@@ -9489,7 +9489,7 @@
         <v>813</v>
       </c>
       <c r="B814" t="n">
-        <v>1.50797703030498</v>
+        <v>1.50797703034261</v>
       </c>
       <c r="C814" t="n">
         <v>0.83</v>
@@ -9500,7 +9500,7 @@
         <v>814</v>
       </c>
       <c r="B815" t="n">
-        <v>1.61092610460082</v>
+        <v>1.6109261045772</v>
       </c>
       <c r="C815" t="n">
         <v>0.86</v>
@@ -9511,7 +9511,7 @@
         <v>815</v>
       </c>
       <c r="B816" t="n">
-        <v>1.90002336514797</v>
+        <v>1.90002336505759</v>
       </c>
       <c r="C816" t="n">
         <v>0.844</v>
@@ -9522,7 +9522,7 @@
         <v>816</v>
       </c>
       <c r="B817" t="n">
-        <v>3.56904562593646</v>
+        <v>3.56904562592439</v>
       </c>
       <c r="C817" t="n">
         <v>0.399</v>
@@ -9533,7 +9533,7 @@
         <v>817</v>
       </c>
       <c r="B818" t="n">
-        <v>2.67588708542885</v>
+        <v>2.67588708538563</v>
       </c>
       <c r="C818" t="n">
         <v>0.473</v>
@@ -9544,7 +9544,7 @@
         <v>818</v>
       </c>
       <c r="B819" t="n">
-        <v>3.75349213433278</v>
+        <v>3.75349213444538</v>
       </c>
       <c r="C819" t="n">
         <v>0.319</v>
@@ -9555,7 +9555,7 @@
         <v>819</v>
       </c>
       <c r="B820" t="n">
-        <v>2.69883608942603</v>
+        <v>2.69883608953491</v>
       </c>
       <c r="C820" t="n">
         <v>0.555</v>
@@ -9566,7 +9566,7 @@
         <v>820</v>
       </c>
       <c r="B821" t="n">
-        <v>2.29324853916015</v>
+        <v>2.29324853915529</v>
       </c>
       <c r="C821" t="n">
         <v>0.746</v>
@@ -9577,7 +9577,7 @@
         <v>821</v>
       </c>
       <c r="B822" t="n">
-        <v>3.25684400411185</v>
+        <v>3.25684400414939</v>
       </c>
       <c r="C822" t="n">
         <v>0.416</v>
@@ -9588,7 +9588,7 @@
         <v>822</v>
       </c>
       <c r="B823" t="n">
-        <v>2.60981289676035</v>
+        <v>2.60981289592182</v>
       </c>
       <c r="C823" t="n">
         <v>0.574</v>
@@ -9599,7 +9599,7 @@
         <v>823</v>
       </c>
       <c r="B824" t="n">
-        <v>5.28784146996077</v>
+        <v>5.28784146995979</v>
       </c>
       <c r="C824" t="n">
         <v>0.141</v>
@@ -9621,7 +9621,7 @@
         <v>825</v>
       </c>
       <c r="B826" t="n">
-        <v>3.22703477695206</v>
+        <v>3.22703477663377</v>
       </c>
       <c r="C826" t="n">
         <v>0.374</v>
@@ -9632,7 +9632,7 @@
         <v>826</v>
       </c>
       <c r="B827" t="n">
-        <v>5.05093058736335</v>
+        <v>5.05093058737566</v>
       </c>
       <c r="C827" t="n">
         <v>0.28</v>
@@ -9643,7 +9643,7 @@
         <v>827</v>
       </c>
       <c r="B828" t="n">
-        <v>1.80314920051748</v>
+        <v>1.80314920051047</v>
       </c>
       <c r="C828" t="n">
         <v>0.804</v>
@@ -9654,7 +9654,7 @@
         <v>828</v>
       </c>
       <c r="B829" t="n">
-        <v>3.71056167663792</v>
+        <v>3.71056167660794</v>
       </c>
       <c r="C829" t="n">
         <v>0.283</v>
@@ -9665,7 +9665,7 @@
         <v>829</v>
       </c>
       <c r="B830" t="n">
-        <v>6.54432267309856</v>
+        <v>6.54432267315523</v>
       </c>
       <c r="C830" t="n">
         <v>0.053</v>
@@ -9676,7 +9676,7 @@
         <v>830</v>
       </c>
       <c r="B831" t="n">
-        <v>2.34010404892</v>
+        <v>2.34010404891631</v>
       </c>
       <c r="C831" t="n">
         <v>0.693</v>
@@ -9687,7 +9687,7 @@
         <v>831</v>
       </c>
       <c r="B832" t="n">
-        <v>2.71369236689859</v>
+        <v>2.7136923669677</v>
       </c>
       <c r="C832" t="n">
         <v>0.598</v>
@@ -9698,7 +9698,7 @@
         <v>832</v>
       </c>
       <c r="B833" t="n">
-        <v>2.94601700094101</v>
+        <v>2.94601700094107</v>
       </c>
       <c r="C833" t="n">
         <v>0.428</v>
@@ -9720,7 +9720,7 @@
         <v>834</v>
       </c>
       <c r="B835" t="n">
-        <v>4.57018044291784</v>
+        <v>4.57018044027525</v>
       </c>
       <c r="C835" t="n">
         <v>0.122</v>
@@ -9731,7 +9731,7 @@
         <v>835</v>
       </c>
       <c r="B836" t="n">
-        <v>3.16141294222558</v>
+        <v>3.1614129443566</v>
       </c>
       <c r="C836" t="n">
         <v>0.507</v>
@@ -9742,7 +9742,7 @@
         <v>836</v>
       </c>
       <c r="B837" t="n">
-        <v>2.67599146743569</v>
+        <v>2.67599146737602</v>
       </c>
       <c r="C837" t="n">
         <v>0.789</v>
@@ -9753,7 +9753,7 @@
         <v>837</v>
       </c>
       <c r="B838" t="n">
-        <v>1.93090337243684</v>
+        <v>1.93090337249256</v>
       </c>
       <c r="C838" t="n">
         <v>0.789</v>
@@ -9764,7 +9764,7 @@
         <v>838</v>
       </c>
       <c r="B839" t="n">
-        <v>2.34270995281382</v>
+        <v>2.34270995275964</v>
       </c>
       <c r="C839" t="n">
         <v>0.577</v>
@@ -9775,7 +9775,7 @@
         <v>839</v>
       </c>
       <c r="B840" t="n">
-        <v>4.84978777952147</v>
+        <v>4.8497877795343</v>
       </c>
       <c r="C840" t="n">
         <v>0.181</v>
@@ -9786,7 +9786,7 @@
         <v>840</v>
       </c>
       <c r="B841" t="n">
-        <v>5.57726582783243</v>
+        <v>5.57726582770156</v>
       </c>
       <c r="C841" t="n">
         <v>0.169</v>
@@ -9797,7 +9797,7 @@
         <v>841</v>
       </c>
       <c r="B842" t="n">
-        <v>4.91278921969938</v>
+        <v>4.91278921965411</v>
       </c>
       <c r="C842" t="n">
         <v>0.181</v>
@@ -9808,7 +9808,7 @@
         <v>842</v>
       </c>
       <c r="B843" t="n">
-        <v>6.23392767565434</v>
+        <v>6.23392767565227</v>
       </c>
       <c r="C843" t="n">
         <v>0.074</v>
@@ -9819,7 +9819,7 @@
         <v>843</v>
       </c>
       <c r="B844" t="n">
-        <v>1.99981227483713</v>
+        <v>1.9998122748371</v>
       </c>
       <c r="C844" t="n">
         <v>0.926</v>
@@ -9830,7 +9830,7 @@
         <v>844</v>
       </c>
       <c r="B845" t="n">
-        <v>2.07425120030663</v>
+        <v>2.0742512003426</v>
       </c>
       <c r="C845" t="n">
         <v>0.665</v>
@@ -9841,7 +9841,7 @@
         <v>845</v>
       </c>
       <c r="B846" t="n">
-        <v>2.05051302238706</v>
+        <v>2.05051302272025</v>
       </c>
       <c r="C846" t="n">
         <v>0.668</v>
@@ -9852,7 +9852,7 @@
         <v>846</v>
       </c>
       <c r="B847" t="n">
-        <v>4.35247483663255</v>
+        <v>4.35247483661551</v>
       </c>
       <c r="C847" t="n">
         <v>0.236</v>
@@ -9863,7 +9863,7 @@
         <v>847</v>
       </c>
       <c r="B848" t="n">
-        <v>2.60373997002097</v>
+        <v>2.60373996858449</v>
       </c>
       <c r="C848" t="n">
         <v>0.609</v>
@@ -9885,7 +9885,7 @@
         <v>849</v>
       </c>
       <c r="B850" t="n">
-        <v>4.06742149528724</v>
+        <v>4.06742149622983</v>
       </c>
       <c r="C850" t="n">
         <v>0.186</v>
@@ -9896,7 +9896,7 @@
         <v>850</v>
       </c>
       <c r="B851" t="n">
-        <v>2.20901755473208</v>
+        <v>2.20901755470604</v>
       </c>
       <c r="C851" t="n">
         <v>0.564</v>
@@ -9907,7 +9907,7 @@
         <v>851</v>
       </c>
       <c r="B852" t="n">
-        <v>3.02332875025368</v>
+        <v>3.02332875029428</v>
       </c>
       <c r="C852" t="n">
         <v>0.418</v>
@@ -9918,7 +9918,7 @@
         <v>852</v>
       </c>
       <c r="B853" t="n">
-        <v>3.47345718500315</v>
+        <v>3.47345718502006</v>
       </c>
       <c r="C853" t="n">
         <v>0.498</v>
@@ -9929,7 +9929,7 @@
         <v>853</v>
       </c>
       <c r="B854" t="n">
-        <v>0.999704661170121</v>
+        <v>0.999704661169957</v>
       </c>
       <c r="C854" t="n">
         <v>1</v>
@@ -9940,7 +9940,7 @@
         <v>854</v>
       </c>
       <c r="B855" t="n">
-        <v>3.02923934910573</v>
+        <v>3.02923934914758</v>
       </c>
       <c r="C855" t="n">
         <v>0.528</v>
@@ -9951,7 +9951,7 @@
         <v>855</v>
       </c>
       <c r="B856" t="n">
-        <v>3.14316152386361</v>
+        <v>3.1431615238482</v>
       </c>
       <c r="C856" t="n">
         <v>0.482</v>
@@ -9962,7 +9962,7 @@
         <v>856</v>
       </c>
       <c r="B857" t="n">
-        <v>2.6460212233916</v>
+        <v>2.64602122339195</v>
       </c>
       <c r="C857" t="n">
         <v>0.624</v>
@@ -9973,7 +9973,7 @@
         <v>857</v>
       </c>
       <c r="B858" t="n">
-        <v>3.93667535847475</v>
+        <v>3.93667535839819</v>
       </c>
       <c r="C858" t="n">
         <v>0.29</v>
@@ -9984,7 +9984,7 @@
         <v>858</v>
       </c>
       <c r="B859" t="n">
-        <v>5.49852231882438</v>
+        <v>5.49852231859973</v>
       </c>
       <c r="C859" t="n">
         <v>0.081</v>
@@ -9995,7 +9995,7 @@
         <v>859</v>
       </c>
       <c r="B860" t="n">
-        <v>4.18323535659569</v>
+        <v>4.1832353565021</v>
       </c>
       <c r="C860" t="n">
         <v>0.338</v>
@@ -10006,7 +10006,7 @@
         <v>860</v>
       </c>
       <c r="B861" t="n">
-        <v>1.75263827378657</v>
+        <v>1.75263827376659</v>
       </c>
       <c r="C861" t="n">
         <v>0.741</v>
@@ -10017,7 +10017,7 @@
         <v>861</v>
       </c>
       <c r="B862" t="n">
-        <v>3.29978190404278</v>
+        <v>3.29978190403595</v>
       </c>
       <c r="C862" t="n">
         <v>0.327</v>
@@ -10028,7 +10028,7 @@
         <v>862</v>
       </c>
       <c r="B863" t="n">
-        <v>5.6431329135957</v>
+        <v>5.64313291333779</v>
       </c>
       <c r="C863" t="n">
         <v>0.131</v>
@@ -10039,7 +10039,7 @@
         <v>863</v>
       </c>
       <c r="B864" t="n">
-        <v>0.999672656515767</v>
+        <v>0.999672656515755</v>
       </c>
       <c r="C864" t="n">
         <v>0.999</v>
@@ -10050,7 +10050,7 @@
         <v>864</v>
       </c>
       <c r="B865" t="n">
-        <v>3.85797282424118</v>
+        <v>3.85797282426915</v>
       </c>
       <c r="C865" t="n">
         <v>0.395</v>
@@ -10061,7 +10061,7 @@
         <v>865</v>
       </c>
       <c r="B866" t="n">
-        <v>1.1144000377775</v>
+        <v>1.1144000377745</v>
       </c>
       <c r="C866" t="n">
         <v>0.947</v>
@@ -10072,7 +10072,7 @@
         <v>866</v>
       </c>
       <c r="B867" t="n">
-        <v>3.66929207066022</v>
+        <v>3.66929207081404</v>
       </c>
       <c r="C867" t="n">
         <v>0.345</v>
@@ -10083,7 +10083,7 @@
         <v>867</v>
       </c>
       <c r="B868" t="n">
-        <v>2.94804746347625</v>
+        <v>2.9480474634853</v>
       </c>
       <c r="C868" t="n">
         <v>0.496</v>
@@ -10094,7 +10094,7 @@
         <v>868</v>
       </c>
       <c r="B869" t="n">
-        <v>3.85827986668102</v>
+        <v>3.85827986665642</v>
       </c>
       <c r="C869" t="n">
         <v>0.338</v>
@@ -10105,7 +10105,7 @@
         <v>869</v>
       </c>
       <c r="B870" t="n">
-        <v>0.999932679948082</v>
+        <v>0.999932679948081</v>
       </c>
       <c r="C870" t="n">
         <v>0.995</v>
@@ -10116,7 +10116,7 @@
         <v>870</v>
       </c>
       <c r="B871" t="n">
-        <v>3.73994982350427</v>
+        <v>3.73994982350745</v>
       </c>
       <c r="C871" t="n">
         <v>0.351</v>
@@ -10127,7 +10127,7 @@
         <v>871</v>
       </c>
       <c r="B872" t="n">
-        <v>2.09498828681974</v>
+        <v>2.09498828678053</v>
       </c>
       <c r="C872" t="n">
         <v>0.742</v>
@@ -10138,7 +10138,7 @@
         <v>872</v>
       </c>
       <c r="B873" t="n">
-        <v>3.08545428413213</v>
+        <v>3.08545428402283</v>
       </c>
       <c r="C873" t="n">
         <v>0.521</v>
@@ -10149,7 +10149,7 @@
         <v>873</v>
       </c>
       <c r="B874" t="n">
-        <v>4.39112240984127</v>
+        <v>4.39112240984682</v>
       </c>
       <c r="C874" t="n">
         <v>0.249</v>
@@ -10171,7 +10171,7 @@
         <v>875</v>
       </c>
       <c r="B876" t="n">
-        <v>2.16269330961231</v>
+        <v>2.16269330956983</v>
       </c>
       <c r="C876" t="n">
         <v>0.637</v>
@@ -10182,7 +10182,7 @@
         <v>876</v>
       </c>
       <c r="B877" t="n">
-        <v>3.9374738013429</v>
+        <v>3.93747380135257</v>
       </c>
       <c r="C877" t="n">
         <v>0.41</v>
@@ -10193,7 +10193,7 @@
         <v>877</v>
       </c>
       <c r="B878" t="n">
-        <v>4.65848952256556</v>
+        <v>4.65848952247494</v>
       </c>
       <c r="C878" t="n">
         <v>0.203</v>
@@ -10204,7 +10204,7 @@
         <v>878</v>
       </c>
       <c r="B879" t="n">
-        <v>5.3683684517124</v>
+        <v>5.36836845242315</v>
       </c>
       <c r="C879" t="n">
         <v>0.105</v>
@@ -10215,7 +10215,7 @@
         <v>879</v>
       </c>
       <c r="B880" t="n">
-        <v>9.31489192963699</v>
+        <v>9.31489192933062</v>
       </c>
       <c r="C880" t="n">
         <v>0.007</v>
@@ -10226,7 +10226,7 @@
         <v>880</v>
       </c>
       <c r="B881" t="n">
-        <v>2.12898857717037</v>
+        <v>2.12898857733634</v>
       </c>
       <c r="C881" t="n">
         <v>0.778</v>
@@ -10237,7 +10237,7 @@
         <v>881</v>
       </c>
       <c r="B882" t="n">
-        <v>3.41904069493667</v>
+        <v>3.41904069491742</v>
       </c>
       <c r="C882" t="n">
         <v>0.56</v>
@@ -10259,7 +10259,7 @@
         <v>883</v>
       </c>
       <c r="B884" t="n">
-        <v>4.35884324343786</v>
+        <v>4.35884324343728</v>
       </c>
       <c r="C884" t="n">
         <v>0.175</v>
@@ -10270,7 +10270,7 @@
         <v>884</v>
       </c>
       <c r="B885" t="n">
-        <v>5.65870503304995</v>
+        <v>5.65870503306388</v>
       </c>
       <c r="C885" t="n">
         <v>0.14</v>
@@ -10303,7 +10303,7 @@
         <v>887</v>
       </c>
       <c r="B888" t="n">
-        <v>2.73938445114274</v>
+        <v>2.73938445117157</v>
       </c>
       <c r="C888" t="n">
         <v>0.582</v>
@@ -10314,7 +10314,7 @@
         <v>888</v>
       </c>
       <c r="B889" t="n">
-        <v>3.23579677968206</v>
+        <v>3.2357967796849</v>
       </c>
       <c r="C889" t="n">
         <v>0.539</v>
@@ -10325,7 +10325,7 @@
         <v>889</v>
       </c>
       <c r="B890" t="n">
-        <v>3.93471099929025</v>
+        <v>3.93471099936367</v>
       </c>
       <c r="C890" t="n">
         <v>0.296</v>
@@ -10336,7 +10336,7 @@
         <v>890</v>
       </c>
       <c r="B891" t="n">
-        <v>2.55085516286074</v>
+        <v>2.55085516287439</v>
       </c>
       <c r="C891" t="n">
         <v>0.596</v>
@@ -10347,7 +10347,7 @@
         <v>891</v>
       </c>
       <c r="B892" t="n">
-        <v>3.99176297329554</v>
+        <v>3.99176297322011</v>
       </c>
       <c r="C892" t="n">
         <v>0.309</v>
@@ -10358,7 +10358,7 @@
         <v>892</v>
       </c>
       <c r="B893" t="n">
-        <v>4.28583622706662</v>
+        <v>4.28583622706238</v>
       </c>
       <c r="C893" t="n">
         <v>0.232</v>
@@ -10369,7 +10369,7 @@
         <v>893</v>
       </c>
       <c r="B894" t="n">
-        <v>3.00659898385359</v>
+        <v>3.00659898385292</v>
       </c>
       <c r="C894" t="n">
         <v>0.385</v>
@@ -10380,7 +10380,7 @@
         <v>894</v>
       </c>
       <c r="B895" t="n">
-        <v>2.99051420696176</v>
+        <v>2.99051420700599</v>
       </c>
       <c r="C895" t="n">
         <v>0.553</v>
@@ -10391,7 +10391,7 @@
         <v>895</v>
       </c>
       <c r="B896" t="n">
-        <v>6.98465703248986</v>
+        <v>6.98465703256638</v>
       </c>
       <c r="C896" t="n">
         <v>0.113</v>
@@ -10402,7 +10402,7 @@
         <v>896</v>
       </c>
       <c r="B897" t="n">
-        <v>1.42717863681488</v>
+        <v>1.42717863680177</v>
       </c>
       <c r="C897" t="n">
         <v>0.89</v>
@@ -10413,7 +10413,7 @@
         <v>897</v>
       </c>
       <c r="B898" t="n">
-        <v>2.09501891476152</v>
+        <v>2.09501891483229</v>
       </c>
       <c r="C898" t="n">
         <v>0.774</v>
@@ -10424,7 +10424,7 @@
         <v>898</v>
       </c>
       <c r="B899" t="n">
-        <v>4.013766978543</v>
+        <v>4.01376697855051</v>
       </c>
       <c r="C899" t="n">
         <v>0.309</v>
@@ -10435,7 +10435,7 @@
         <v>899</v>
       </c>
       <c r="B900" t="n">
-        <v>6.06855401079556</v>
+        <v>6.06855401070145</v>
       </c>
       <c r="C900" t="n">
         <v>0.129</v>
@@ -10446,7 +10446,7 @@
         <v>900</v>
       </c>
       <c r="B901" t="n">
-        <v>4.64240917600579</v>
+        <v>4.64240917600396</v>
       </c>
       <c r="C901" t="n">
         <v>0.242</v>
@@ -10457,7 +10457,7 @@
         <v>901</v>
       </c>
       <c r="B902" t="n">
-        <v>2.97113501710979</v>
+        <v>2.97113501642591</v>
       </c>
       <c r="C902" t="n">
         <v>0.391</v>
@@ -10468,7 +10468,7 @@
         <v>902</v>
       </c>
       <c r="B903" t="n">
-        <v>1.99970319782756</v>
+        <v>1.99970319782755</v>
       </c>
       <c r="C903" t="n">
         <v>0.944</v>
@@ -10479,7 +10479,7 @@
         <v>903</v>
       </c>
       <c r="B904" t="n">
-        <v>6.4514205964534</v>
+        <v>6.45142059657418</v>
       </c>
       <c r="C904" t="n">
         <v>0.042</v>
@@ -10490,7 +10490,7 @@
         <v>904</v>
       </c>
       <c r="B905" t="n">
-        <v>1.67305561409208</v>
+        <v>1.67305561446598</v>
       </c>
       <c r="C905" t="n">
         <v>0.786</v>
@@ -10501,7 +10501,7 @@
         <v>905</v>
       </c>
       <c r="B906" t="n">
-        <v>1.89780961982143</v>
+        <v>1.8978096198252</v>
       </c>
       <c r="C906" t="n">
         <v>0.996</v>
@@ -10512,7 +10512,7 @@
         <v>906</v>
       </c>
       <c r="B907" t="n">
-        <v>1.09684604300571</v>
+        <v>1.09684604307006</v>
       </c>
       <c r="C907" t="n">
         <v>0.95</v>
@@ -10523,7 +10523,7 @@
         <v>907</v>
       </c>
       <c r="B908" t="n">
-        <v>3.52971670812234</v>
+        <v>3.52971670804136</v>
       </c>
       <c r="C908" t="n">
         <v>0.356</v>
@@ -10534,7 +10534,7 @@
         <v>908</v>
       </c>
       <c r="B909" t="n">
-        <v>2.74844246435064</v>
+        <v>2.7484424643519</v>
       </c>
       <c r="C909" t="n">
         <v>0.533</v>
@@ -10545,7 +10545,7 @@
         <v>909</v>
       </c>
       <c r="B910" t="n">
-        <v>3.26709827236294</v>
+        <v>3.26709827237291</v>
       </c>
       <c r="C910" t="n">
         <v>0.472</v>
@@ -10556,7 +10556,7 @@
         <v>910</v>
       </c>
       <c r="B911" t="n">
-        <v>4.34492555962965</v>
+        <v>4.34492555963136</v>
       </c>
       <c r="C911" t="n">
         <v>0.276</v>
@@ -10567,7 +10567,7 @@
         <v>911</v>
       </c>
       <c r="B912" t="n">
-        <v>5.01516117166434</v>
+        <v>5.01516117161428</v>
       </c>
       <c r="C912" t="n">
         <v>0.297</v>
@@ -10578,7 +10578,7 @@
         <v>912</v>
       </c>
       <c r="B913" t="n">
-        <v>3.29227156355992</v>
+        <v>3.29227156350786</v>
       </c>
       <c r="C913" t="n">
         <v>0.275</v>
@@ -10589,7 +10589,7 @@
         <v>913</v>
       </c>
       <c r="B914" t="n">
-        <v>6.68566937141003</v>
+        <v>6.68566937157961</v>
       </c>
       <c r="C914" t="n">
         <v>0.054</v>
@@ -10600,7 +10600,7 @@
         <v>914</v>
       </c>
       <c r="B915" t="n">
-        <v>1.33682474808114</v>
+        <v>1.33682474804218</v>
       </c>
       <c r="C915" t="n">
         <v>0.916</v>
@@ -10611,7 +10611,7 @@
         <v>915</v>
       </c>
       <c r="B916" t="n">
-        <v>1.09144500096935</v>
+        <v>1.09144500097416</v>
       </c>
       <c r="C916" t="n">
         <v>0.927</v>
@@ -10633,7 +10633,7 @@
         <v>917</v>
       </c>
       <c r="B918" t="n">
-        <v>2.19232157606931</v>
+        <v>2.19232157596163</v>
       </c>
       <c r="C918" t="n">
         <v>0.56</v>
@@ -10644,7 +10644,7 @@
         <v>918</v>
       </c>
       <c r="B919" t="n">
-        <v>2.22090669133057</v>
+        <v>2.22090669133066</v>
       </c>
       <c r="C919" t="n">
         <v>0.737</v>
@@ -10655,7 +10655,7 @@
         <v>919</v>
       </c>
       <c r="B920" t="n">
-        <v>2.62409956004145</v>
+        <v>2.62409955996114</v>
       </c>
       <c r="C920" t="n">
         <v>0.597</v>
@@ -10666,7 +10666,7 @@
         <v>920</v>
       </c>
       <c r="B921" t="n">
-        <v>7.61974241762721</v>
+        <v>7.61974241776534</v>
       </c>
       <c r="C921" t="n">
         <v>0.024</v>
@@ -10677,7 +10677,7 @@
         <v>921</v>
       </c>
       <c r="B922" t="n">
-        <v>1.99969405335089</v>
+        <v>1.99969405335053</v>
       </c>
       <c r="C922" t="n">
         <v>0.906</v>
@@ -10688,7 +10688,7 @@
         <v>922</v>
       </c>
       <c r="B923" t="n">
-        <v>1.99992279327002</v>
+        <v>1.99992279327003</v>
       </c>
       <c r="C923" t="n">
         <v>0.888</v>
@@ -10699,7 +10699,7 @@
         <v>923</v>
       </c>
       <c r="B924" t="n">
-        <v>6.53509672929819</v>
+        <v>6.53509674185251</v>
       </c>
       <c r="C924" t="n">
         <v>0.04</v>
@@ -10710,7 +10710,7 @@
         <v>924</v>
       </c>
       <c r="B925" t="n">
-        <v>3.59861728883882</v>
+        <v>3.59861728873275</v>
       </c>
       <c r="C925" t="n">
         <v>0.376</v>
@@ -10721,7 +10721,7 @@
         <v>925</v>
       </c>
       <c r="B926" t="n">
-        <v>2.96720897068801</v>
+        <v>2.96720897100974</v>
       </c>
       <c r="C926" t="n">
         <v>0.467</v>
@@ -10732,7 +10732,7 @@
         <v>926</v>
       </c>
       <c r="B927" t="n">
-        <v>2.81183300682179</v>
+        <v>2.81183300673306</v>
       </c>
       <c r="C927" t="n">
         <v>0.523</v>
@@ -10743,7 +10743,7 @@
         <v>927</v>
       </c>
       <c r="B928" t="n">
-        <v>2.92449171950883</v>
+        <v>2.92449171948947</v>
       </c>
       <c r="C928" t="n">
         <v>0.385</v>
@@ -10754,7 +10754,7 @@
         <v>928</v>
       </c>
       <c r="B929" t="n">
-        <v>3.61121023584504</v>
+        <v>3.61121023580535</v>
       </c>
       <c r="C929" t="n">
         <v>0.344</v>
@@ -10765,7 +10765,7 @@
         <v>929</v>
       </c>
       <c r="B930" t="n">
-        <v>2.40672206042451</v>
+        <v>2.40672206041125</v>
       </c>
       <c r="C930" t="n">
         <v>0.585</v>
@@ -10776,7 +10776,7 @@
         <v>930</v>
       </c>
       <c r="B931" t="n">
-        <v>6.04211995010964</v>
+        <v>6.04211995020316</v>
       </c>
       <c r="C931" t="n">
         <v>0.115</v>
@@ -10787,7 +10787,7 @@
         <v>931</v>
       </c>
       <c r="B932" t="n">
-        <v>2.15752547360551</v>
+        <v>2.15752547360527</v>
       </c>
       <c r="C932" t="n">
         <v>0.712</v>
@@ -10798,7 +10798,7 @@
         <v>932</v>
       </c>
       <c r="B933" t="n">
-        <v>4.2099146646581</v>
+        <v>4.20991466482844</v>
       </c>
       <c r="C933" t="n">
         <v>0.23</v>
@@ -10809,7 +10809,7 @@
         <v>933</v>
       </c>
       <c r="B934" t="n">
-        <v>1.99990600722073</v>
+        <v>1.99990600722076</v>
       </c>
       <c r="C934" t="n">
         <v>0.918</v>
@@ -10820,7 +10820,7 @@
         <v>934</v>
       </c>
       <c r="B935" t="n">
-        <v>4.21792205818897</v>
+        <v>4.21792205814779</v>
       </c>
       <c r="C935" t="n">
         <v>0.207</v>
@@ -10831,7 +10831,7 @@
         <v>935</v>
       </c>
       <c r="B936" t="n">
-        <v>3.40166810371946</v>
+        <v>3.40166810372659</v>
       </c>
       <c r="C936" t="n">
         <v>0.584</v>
@@ -10853,7 +10853,7 @@
         <v>937</v>
       </c>
       <c r="B938" t="n">
-        <v>2.50948072973336</v>
+        <v>2.50948072974423</v>
       </c>
       <c r="C938" t="n">
         <v>0.759</v>
@@ -10864,7 +10864,7 @@
         <v>938</v>
       </c>
       <c r="B939" t="n">
-        <v>2.72062255596246</v>
+        <v>2.72062255608056</v>
       </c>
       <c r="C939" t="n">
         <v>0.612</v>
@@ -10875,7 +10875,7 @@
         <v>939</v>
       </c>
       <c r="B940" t="n">
-        <v>7.20076745108581</v>
+        <v>7.20076745103262</v>
       </c>
       <c r="C940" t="n">
         <v>0.053</v>
@@ -10886,7 +10886,7 @@
         <v>940</v>
       </c>
       <c r="B941" t="n">
-        <v>4.86612627168281</v>
+        <v>4.86612627162677</v>
       </c>
       <c r="C941" t="n">
         <v>0.126</v>
@@ -10897,7 +10897,7 @@
         <v>941</v>
       </c>
       <c r="B942" t="n">
-        <v>2.01133913093416</v>
+        <v>2.01133913096163</v>
       </c>
       <c r="C942" t="n">
         <v>0.851</v>
@@ -10908,7 +10908,7 @@
         <v>942</v>
       </c>
       <c r="B943" t="n">
-        <v>3.0181149511469</v>
+        <v>3.01811495114648</v>
       </c>
       <c r="C943" t="n">
         <v>0.501</v>
@@ -10919,7 +10919,7 @@
         <v>943</v>
       </c>
       <c r="B944" t="n">
-        <v>2.89187881217647</v>
+        <v>2.89187881209852</v>
       </c>
       <c r="C944" t="n">
         <v>0.512</v>
@@ -10930,7 +10930,7 @@
         <v>944</v>
       </c>
       <c r="B945" t="n">
-        <v>5.18728625477702</v>
+        <v>5.18728625477747</v>
       </c>
       <c r="C945" t="n">
         <v>0.155</v>
@@ -10941,7 +10941,7 @@
         <v>945</v>
       </c>
       <c r="B946" t="n">
-        <v>1.8997685915673</v>
+        <v>1.89976859155517</v>
       </c>
       <c r="C946" t="n">
         <v>0.758</v>
@@ -10952,7 +10952,7 @@
         <v>946</v>
       </c>
       <c r="B947" t="n">
-        <v>1.89472374765561</v>
+        <v>1.89472374784296</v>
       </c>
       <c r="C947" t="n">
         <v>0.806</v>
@@ -10963,7 +10963,7 @@
         <v>947</v>
       </c>
       <c r="B948" t="n">
-        <v>2.83762193594675</v>
+        <v>2.83762193595925</v>
       </c>
       <c r="C948" t="n">
         <v>0.509</v>
@@ -10974,7 +10974,7 @@
         <v>948</v>
       </c>
       <c r="B949" t="n">
-        <v>4.56015606781466</v>
+        <v>4.56015606786238</v>
       </c>
       <c r="C949" t="n">
         <v>0.252</v>
@@ -10985,7 +10985,7 @@
         <v>949</v>
       </c>
       <c r="B950" t="n">
-        <v>5.38453752475282</v>
+        <v>5.3845375248036</v>
       </c>
       <c r="C950" t="n">
         <v>0.146</v>
@@ -10996,7 +10996,7 @@
         <v>950</v>
       </c>
       <c r="B951" t="n">
-        <v>5.7944370478265</v>
+        <v>5.79443704658763</v>
       </c>
       <c r="C951" t="n">
         <v>0.079</v>
@@ -11007,7 +11007,7 @@
         <v>951</v>
       </c>
       <c r="B952" t="n">
-        <v>1.65739862623623</v>
+        <v>1.65739862617915</v>
       </c>
       <c r="C952" t="n">
         <v>0.828</v>
@@ -11018,7 +11018,7 @@
         <v>952</v>
       </c>
       <c r="B953" t="n">
-        <v>4.10354263050694</v>
+        <v>4.10354263049807</v>
       </c>
       <c r="C953" t="n">
         <v>0.307</v>
@@ -11029,7 +11029,7 @@
         <v>953</v>
       </c>
       <c r="B954" t="n">
-        <v>0.99950759539537</v>
+        <v>0.999507595395382</v>
       </c>
       <c r="C954" t="n">
         <v>0.998</v>
@@ -11040,7 +11040,7 @@
         <v>954</v>
       </c>
       <c r="B955" t="n">
-        <v>5.32973772377786</v>
+        <v>5.32973772366479</v>
       </c>
       <c r="C955" t="n">
         <v>0.16</v>
@@ -11051,7 +11051,7 @@
         <v>955</v>
       </c>
       <c r="B956" t="n">
-        <v>2.45498811890364</v>
+        <v>2.45498811892434</v>
       </c>
       <c r="C956" t="n">
         <v>0.595</v>
@@ -11062,7 +11062,7 @@
         <v>956</v>
       </c>
       <c r="B957" t="n">
-        <v>4.10055103927713</v>
+        <v>4.1005510392597</v>
       </c>
       <c r="C957" t="n">
         <v>0.395</v>
@@ -11073,7 +11073,7 @@
         <v>957</v>
       </c>
       <c r="B958" t="n">
-        <v>1.95707248895271</v>
+        <v>1.95707248892259</v>
       </c>
       <c r="C958" t="n">
         <v>0.766</v>
@@ -11084,7 +11084,7 @@
         <v>958</v>
       </c>
       <c r="B959" t="n">
-        <v>3.13449100116574</v>
+        <v>3.13449100122711</v>
       </c>
       <c r="C959" t="n">
         <v>0.545</v>
@@ -11106,7 +11106,7 @@
         <v>960</v>
       </c>
       <c r="B961" t="n">
-        <v>4.33549929549205</v>
+        <v>4.33549929120851</v>
       </c>
       <c r="C961" t="n">
         <v>0.198</v>
@@ -11117,7 +11117,7 @@
         <v>961</v>
       </c>
       <c r="B962" t="n">
-        <v>1.70113109613801</v>
+        <v>1.70113109629873</v>
       </c>
       <c r="C962" t="n">
         <v>0.84</v>
@@ -11128,7 +11128,7 @@
         <v>962</v>
       </c>
       <c r="B963" t="n">
-        <v>2.10686702332767</v>
+        <v>2.10686702332537</v>
       </c>
       <c r="C963" t="n">
         <v>0.757</v>
@@ -11139,7 +11139,7 @@
         <v>963</v>
       </c>
       <c r="B964" t="n">
-        <v>0.999988920323262</v>
+        <v>0.99998892032326</v>
       </c>
       <c r="C964" t="n">
         <v>0.992</v>
@@ -11150,7 +11150,7 @@
         <v>964</v>
       </c>
       <c r="B965" t="n">
-        <v>1.59057024198123</v>
+        <v>1.59057024199701</v>
       </c>
       <c r="C965" t="n">
         <v>0.9</v>
@@ -11161,7 +11161,7 @@
         <v>965</v>
       </c>
       <c r="B966" t="n">
-        <v>4.4152958824554</v>
+        <v>4.41529588253231</v>
       </c>
       <c r="C966" t="n">
         <v>0.244</v>
@@ -11172,7 +11172,7 @@
         <v>966</v>
       </c>
       <c r="B967" t="n">
-        <v>2.68734905701937</v>
+        <v>2.68734905821787</v>
       </c>
       <c r="C967" t="n">
         <v>0.573</v>
@@ -11183,7 +11183,7 @@
         <v>967</v>
       </c>
       <c r="B968" t="n">
-        <v>4.88419224231555</v>
+        <v>4.88419224249977</v>
       </c>
       <c r="C968" t="n">
         <v>0.205</v>
@@ -11194,7 +11194,7 @@
         <v>968</v>
       </c>
       <c r="B969" t="n">
-        <v>1.37605410149535</v>
+        <v>1.37605410153042</v>
       </c>
       <c r="C969" t="n">
         <v>0.935</v>
@@ -11205,7 +11205,7 @@
         <v>969</v>
       </c>
       <c r="B970" t="n">
-        <v>4.46447420481509</v>
+        <v>4.46447420497189</v>
       </c>
       <c r="C970" t="n">
         <v>0.242</v>
@@ -11216,7 +11216,7 @@
         <v>970</v>
       </c>
       <c r="B971" t="n">
-        <v>8.28989877065483</v>
+        <v>8.28989877057868</v>
       </c>
       <c r="C971" t="n">
         <v>0.039</v>
@@ -11227,7 +11227,7 @@
         <v>971</v>
       </c>
       <c r="B972" t="n">
-        <v>2.80835527745442</v>
+        <v>2.8083552774179</v>
       </c>
       <c r="C972" t="n">
         <v>0.507</v>
@@ -11238,7 +11238,7 @@
         <v>972</v>
       </c>
       <c r="B973" t="n">
-        <v>2.01182481599493</v>
+        <v>2.01182481597836</v>
       </c>
       <c r="C973" t="n">
         <v>0.812</v>
@@ -11249,7 +11249,7 @@
         <v>973</v>
       </c>
       <c r="B974" t="n">
-        <v>3.83432426107954</v>
+        <v>3.8343242609611</v>
       </c>
       <c r="C974" t="n">
         <v>0.275</v>
@@ -11260,7 +11260,7 @@
         <v>974</v>
       </c>
       <c r="B975" t="n">
-        <v>1.99995869225111</v>
+        <v>1.9999586922511</v>
       </c>
       <c r="C975" t="n">
         <v>0.888</v>
@@ -11271,7 +11271,7 @@
         <v>975</v>
       </c>
       <c r="B976" t="n">
-        <v>3.02619871549635</v>
+        <v>3.02619871561235</v>
       </c>
       <c r="C976" t="n">
         <v>0.404</v>
@@ -11282,7 +11282,7 @@
         <v>976</v>
       </c>
       <c r="B977" t="n">
-        <v>5.19078184854179</v>
+        <v>5.19078184869379</v>
       </c>
       <c r="C977" t="n">
         <v>0.157</v>
@@ -11293,7 +11293,7 @@
         <v>977</v>
       </c>
       <c r="B978" t="n">
-        <v>2.15216473666124</v>
+        <v>2.15216473636961</v>
       </c>
       <c r="C978" t="n">
         <v>0.806</v>
@@ -11304,7 +11304,7 @@
         <v>978</v>
       </c>
       <c r="B979" t="n">
-        <v>3.16388752326209</v>
+        <v>3.16388752331823</v>
       </c>
       <c r="C979" t="n">
         <v>0.541</v>
@@ -11315,7 +11315,7 @@
         <v>979</v>
       </c>
       <c r="B980" t="n">
-        <v>3.50413813528737</v>
+        <v>3.50413813527789</v>
       </c>
       <c r="C980" t="n">
         <v>0.402</v>
@@ -11326,7 +11326,7 @@
         <v>980</v>
       </c>
       <c r="B981" t="n">
-        <v>3.69177637815909</v>
+        <v>3.69177637808612</v>
       </c>
       <c r="C981" t="n">
         <v>0.297</v>
@@ -11337,7 +11337,7 @@
         <v>981</v>
       </c>
       <c r="B982" t="n">
-        <v>4.83758721959327</v>
+        <v>4.83758721960272</v>
       </c>
       <c r="C982" t="n">
         <v>0.145</v>
@@ -11348,7 +11348,7 @@
         <v>982</v>
       </c>
       <c r="B983" t="n">
-        <v>2.51305524017078</v>
+        <v>2.51305524015819</v>
       </c>
       <c r="C983" t="n">
         <v>0.619</v>
@@ -11359,7 +11359,7 @@
         <v>983</v>
       </c>
       <c r="B984" t="n">
-        <v>2.92842012030975</v>
+        <v>2.92842012031099</v>
       </c>
       <c r="C984" t="n">
         <v>0.532</v>
@@ -11370,7 +11370,7 @@
         <v>984</v>
       </c>
       <c r="B985" t="n">
-        <v>1.99980051178805</v>
+        <v>1.99980051178807</v>
       </c>
       <c r="C985" t="n">
         <v>0.915</v>
@@ -11381,7 +11381,7 @@
         <v>985</v>
       </c>
       <c r="B986" t="n">
-        <v>3.91658702214891</v>
+        <v>3.91658702218236</v>
       </c>
       <c r="C986" t="n">
         <v>0.22</v>
@@ -11392,7 +11392,7 @@
         <v>986</v>
       </c>
       <c r="B987" t="n">
-        <v>3.99186868381842</v>
+        <v>3.99186868378282</v>
       </c>
       <c r="C987" t="n">
         <v>0.247</v>
@@ -11403,7 +11403,7 @@
         <v>987</v>
       </c>
       <c r="B988" t="n">
-        <v>4.31822572502342</v>
+        <v>4.31822572496385</v>
       </c>
       <c r="C988" t="n">
         <v>0.248</v>
@@ -11414,7 +11414,7 @@
         <v>988</v>
       </c>
       <c r="B989" t="n">
-        <v>3.68928006649321</v>
+        <v>3.68928006649431</v>
       </c>
       <c r="C989" t="n">
         <v>0.308</v>
@@ -11425,7 +11425,7 @@
         <v>989</v>
       </c>
       <c r="B990" t="n">
-        <v>1.57872430234086</v>
+        <v>1.57872430223451</v>
       </c>
       <c r="C990" t="n">
         <v>0.802</v>
@@ -11436,7 +11436,7 @@
         <v>990</v>
       </c>
       <c r="B991" t="n">
-        <v>2.45752499824916</v>
+        <v>2.45752499827373</v>
       </c>
       <c r="C991" t="n">
         <v>0.601</v>
@@ -11447,7 +11447,7 @@
         <v>991</v>
       </c>
       <c r="B992" t="n">
-        <v>5.88599908219425</v>
+        <v>5.8859990820166</v>
       </c>
       <c r="C992" t="n">
         <v>0.076</v>
@@ -11458,7 +11458,7 @@
         <v>992</v>
       </c>
       <c r="B993" t="n">
-        <v>3.36932069857955</v>
+        <v>3.36932069851053</v>
       </c>
       <c r="C993" t="n">
         <v>0.268</v>
@@ -11469,7 +11469,7 @@
         <v>993</v>
       </c>
       <c r="B994" t="n">
-        <v>5.3875625054232</v>
+        <v>5.38756250545019</v>
       </c>
       <c r="C994" t="n">
         <v>0.108</v>
@@ -11480,7 +11480,7 @@
         <v>994</v>
       </c>
       <c r="B995" t="n">
-        <v>3.10561744021162</v>
+        <v>3.10561744025356</v>
       </c>
       <c r="C995" t="n">
         <v>0.413</v>
@@ -11491,7 +11491,7 @@
         <v>995</v>
       </c>
       <c r="B996" t="n">
-        <v>3.74285983739454</v>
+        <v>3.74285983727279</v>
       </c>
       <c r="C996" t="n">
         <v>0.348</v>
@@ -11502,7 +11502,7 @@
         <v>996</v>
       </c>
       <c r="B997" t="n">
-        <v>3.86515963822874</v>
+        <v>3.86515963823629</v>
       </c>
       <c r="C997" t="n">
         <v>0.395</v>
@@ -11513,7 +11513,7 @@
         <v>997</v>
       </c>
       <c r="B998" t="n">
-        <v>3.24292645978487</v>
+        <v>3.24292645980232</v>
       </c>
       <c r="C998" t="n">
         <v>0.471</v>
@@ -11524,7 +11524,7 @@
         <v>998</v>
       </c>
       <c r="B999" t="n">
-        <v>3.15394764150788</v>
+        <v>3.15394764150276</v>
       </c>
       <c r="C999" t="n">
         <v>0.374</v>
@@ -11546,7 +11546,7 @@
         <v>1000</v>
       </c>
       <c r="B1001" t="n">
-        <v>3.2710357204077</v>
+        <v>3.27103572037151</v>
       </c>
       <c r="C1001" t="n">
         <v>0.516</v>
